--- a/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
+++ b/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F43BF9B-6BDA-412C-863E-4C84D8004346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C13D6CE-4760-432D-BB87-63F3049BBCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -428,19 +428,19 @@
     <t>EDESUR:</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS septiembre 2025</t>
-  </si>
-  <si>
     <t>AYSA - septiembre</t>
   </si>
   <si>
-    <t>Honorarios Administracion - septiembre</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - septiembre</t>
-  </si>
-  <si>
     <t>Edesur - septiembre</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1452,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1728,8 +1728,52 @@
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1749,52 +1793,8 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1811,6 +1811,12 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1820,12 +1826,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2196,16 +2197,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2213,68 +2214,68 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="169" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
@@ -2285,7 +2286,7 @@
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
       <c r="C18" s="60">
@@ -2293,16 +2294,16 @@
         <v>91854.86</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="90"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="91"/>
       <c r="C20" s="84">
@@ -2310,17 +2311,17 @@
       </c>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B21" s="91"/>
-      <c r="C21" s="84">
+      <c r="C21" s="213">
         <v>36534.6</v>
       </c>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="75" t="s">
         <v>124</v>
       </c>
@@ -2330,7 +2331,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="88"/>
       <c r="B23" s="89"/>
       <c r="C23" s="60">
@@ -2339,7 +2340,7 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>78</v>
       </c>
@@ -2350,40 +2351,40 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C25" s="61"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="61"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="75"/>
       <c r="B27" s="75"/>
       <c r="C27" s="84"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="75"/>
       <c r="B28" s="75"/>
       <c r="C28" s="85"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="75"/>
       <c r="B29" s="75"/>
       <c r="C29" s="85"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="63"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -2394,7 +2395,7 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>15</v>
       </c>
@@ -2404,15 +2405,15 @@
         <v>165389.46000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="146" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="147"/>
       <c r="C35" s="148"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="144" t="s">
         <v>10</v>
       </c>
@@ -2423,7 +2424,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2434,9 +2435,9 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C38" s="93">
         <v>-229765.65</v>
@@ -2444,7 +2445,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -2453,7 +2454,7 @@
         <v>-165389.46000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>16</v>
       </c>
@@ -2464,23 +2465,23 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="18"/>
       <c r="C41" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
       <c r="F42" s="94"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
       <c r="B43" s="18"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="73" t="s">
         <v>57</v>
       </c>
@@ -2489,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="75" t="s">
         <v>63</v>
       </c>
@@ -2499,17 +2500,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="75"/>
       <c r="B46" s="75"/>
       <c r="C46" s="82"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="83"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="79" t="s">
         <v>4</v>
       </c>
@@ -2519,22 +2520,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -2556,37 +2557,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="14">
         <v>165389.46000000002</v>
       </c>
-      <c r="H1" s="175" t="s">
+      <c r="H1" s="202" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="175"/>
+      <c r="I1" s="202"/>
       <c r="J1" s="14"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2603,15 +2604,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="178"/>
+      <c r="C3" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="175" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2620,52 +2621,52 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="186" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="191" t="s">
+      <c r="J3" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="189" t="s">
+      <c r="K3" s="186" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="179"/>
+      <c r="B4" s="180"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
+      <c r="G4" s="187"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="196"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="190"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="189"/>
+      <c r="K4" s="187"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="181">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="182"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -2698,11 +2699,11 @@
         <v>66016.406332382612</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="181">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -2737,11 +2738,11 @@
         <v>57228.795481850429</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -2776,11 +2777,11 @@
         <v>60017.321216528711</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="182"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -2815,11 +2816,11 @@
         <v>70907.619939826094</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -2854,11 +2855,11 @@
         <v>59120.864767624356</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -2891,11 +2892,11 @@
         <v>59466.18976478609</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -2928,11 +2929,11 @@
         <v>87074.54727204176</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="181" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="182"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2966,11 +2967,11 @@
         <v>6267.7014636800004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="182"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3004,11 +3005,11 @@
         <v>6174.1536806399999</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="182"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3042,7 +3043,7 @@
         <v>6174.1536806399999</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>478447.75360000005</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -3105,7 +3106,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3137,7 +3138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3163,7 +3164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3197,7 +3198,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3266,7 +3267,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3359,7 +3360,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3393,7 +3394,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3427,7 +3428,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3460,44 +3461,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="195"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="195"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -3514,7 +3515,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -3530,7 +3531,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -3544,23 +3545,23 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="200"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="201"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -3574,7 +3575,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -3593,13 +3594,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -3617,7 +3618,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -3627,11 +3628,11 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -3650,7 +3651,7 @@
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -3669,7 +3670,7 @@
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -3688,7 +3689,7 @@
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -3702,7 +3703,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -3716,7 +3717,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -3729,7 +3730,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -3743,7 +3744,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -3757,7 +3758,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -3776,7 +3777,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -3790,58 +3791,58 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="194">
         <f>SUM(J42:J51)</f>
         <v>60093.121216528714</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="195"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="197"/>
+      <c r="G56" s="197"/>
+      <c r="H56" s="197"/>
+      <c r="I56" s="197"/>
+      <c r="J56" s="197"/>
+      <c r="K56" s="195"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
+      <c r="H57" s="197"/>
+      <c r="I57" s="197"/>
+      <c r="J57" s="197"/>
+      <c r="K57" s="195"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -3855,7 +3856,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -3868,7 +3869,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -3879,20 +3880,20 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="201"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -3903,7 +3904,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -3920,12 +3921,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="184"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -3940,7 +3941,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -3948,10 +3949,10 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -3967,7 +3968,7 @@
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -3983,7 +3984,7 @@
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -3999,7 +4000,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -4010,7 +4011,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -4021,7 +4022,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -4031,7 +4032,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -4042,7 +4043,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -4053,7 +4054,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -4064,7 +4065,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -4075,50 +4076,50 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="193"/>
+      <c r="G76" s="193"/>
+      <c r="H76" s="193"/>
+      <c r="I76" s="193"/>
+      <c r="J76" s="194">
         <f>SUM(J66:J75)</f>
         <v>24394.945350000002</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="195"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="197"/>
+      <c r="G83" s="197"/>
+      <c r="H83" s="197"/>
+      <c r="I83" s="197"/>
+      <c r="J83" s="197"/>
+      <c r="K83" s="195"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="197"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="197"/>
+      <c r="I84" s="197"/>
+      <c r="J84" s="197"/>
+      <c r="K84" s="195"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -4132,7 +4133,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -4145,7 +4146,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -4156,20 +4157,20 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="200"/>
+      <c r="G88" s="200"/>
+      <c r="H88" s="200"/>
+      <c r="I88" s="200"/>
+      <c r="J88" s="200"/>
+      <c r="K88" s="201"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -4180,7 +4181,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -4197,12 +4198,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="184"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -4217,7 +4218,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -4225,10 +4226,10 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -4244,7 +4245,7 @@
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -4260,7 +4261,7 @@
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -4275,7 +4276,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -4286,7 +4287,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -4297,7 +4298,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -4307,7 +4308,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -4318,7 +4319,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -4329,7 +4330,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -4340,7 +4341,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -4351,50 +4352,50 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="193"/>
+      <c r="G103" s="193"/>
+      <c r="H103" s="193"/>
+      <c r="I103" s="193"/>
+      <c r="J103" s="194">
         <f>SUM(J93:J102)</f>
         <v>20664.494608000001</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="195"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="197"/>
+      <c r="G108" s="197"/>
+      <c r="H108" s="197"/>
+      <c r="I108" s="197"/>
+      <c r="J108" s="197"/>
+      <c r="K108" s="195"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="197"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="195"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -4408,7 +4409,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -4421,7 +4422,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -4432,20 +4433,20 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="200"/>
+      <c r="G113" s="200"/>
+      <c r="H113" s="200"/>
+      <c r="I113" s="200"/>
+      <c r="J113" s="200"/>
+      <c r="K113" s="201"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -4456,7 +4457,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -4473,12 +4474,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="184"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -4493,7 +4494,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -4501,10 +4502,10 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -4520,7 +4521,7 @@
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -4536,7 +4537,7 @@
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -4552,7 +4553,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -4563,7 +4564,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -4574,7 +4575,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -4584,7 +4585,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -4595,7 +4596,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -4606,7 +4607,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -4617,7 +4618,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -4628,24 +4629,54 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="193"/>
+      <c r="G128" s="193"/>
+      <c r="H128" s="193"/>
+      <c r="I128" s="193"/>
+      <c r="J128" s="194">
         <f>SUM(J118:J127)</f>
         <v>22771.405480000005</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="195"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A5:B5"/>
@@ -4662,36 +4693,6 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4702,16 +4703,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B1" s="111" t="s">
         <v>79</v>
       </c>
@@ -4731,12 +4732,12 @@
       <c r="K1" s="114"/>
       <c r="L1" s="115"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H2" s="116"/>
       <c r="I2" s="116"/>
       <c r="J2" s="116"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="117" t="s">
         <v>82</v>
       </c>
@@ -4763,7 +4764,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="119"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="117"/>
       <c r="C4" s="111" t="s">
         <v>88</v>
@@ -4780,7 +4781,7 @@
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
@@ -4813,7 +4814,7 @@
       <c r="L5" s="122"/>
       <c r="M5" s="123"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -4846,7 +4847,7 @@
       <c r="L6" s="122"/>
       <c r="M6" s="123"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
@@ -4878,7 +4879,7 @@
       <c r="L7" s="122"/>
       <c r="M7" s="123"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
@@ -4911,7 +4912,7 @@
       <c r="L8" s="122"/>
       <c r="M8" s="123"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
@@ -4944,7 +4945,7 @@
       <c r="L9" s="122"/>
       <c r="M9" s="123"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
@@ -4977,7 +4978,7 @@
       <c r="L10" s="122"/>
       <c r="M10" s="123"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
@@ -5010,7 +5011,7 @@
       <c r="L11" s="122"/>
       <c r="M11" s="123"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="125"/>
       <c r="C12" s="126">
         <f>SUM(C5:C11)</f>
@@ -5038,13 +5039,13 @@
       <c r="K12" s="125"/>
       <c r="L12" s="128"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="129"/>
       <c r="H13" s="117"/>
       <c r="I13" s="117"/>
       <c r="J13" s="117"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>97</v>
       </c>
@@ -5056,7 +5057,7 @@
       <c r="I14" s="117"/>
       <c r="J14" s="117"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>98</v>
       </c>
@@ -5064,7 +5065,7 @@
       <c r="I15" s="117"/>
       <c r="J15" s="117"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="117"/>
       <c r="C16" s="111"/>
       <c r="D16" s="111"/>
@@ -5075,7 +5076,7 @@
       <c r="J16" s="111"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="117"/>
       <c r="C17" s="111"/>
       <c r="D17" s="111"/>
@@ -5085,12 +5086,12 @@
       <c r="I17" s="120"/>
       <c r="J17" s="120"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="117"/>
       <c r="I18" s="117"/>
       <c r="J18" s="117"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C19" s="131"/>
       <c r="D19" s="132"/>
       <c r="E19" s="132"/>
@@ -5103,7 +5104,7 @@
       <c r="L19" s="132"/>
       <c r="M19" s="134"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C20" s="135"/>
       <c r="E20" t="s">
         <v>99</v>
@@ -5119,7 +5120,7 @@
       </c>
       <c r="M20" s="137"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C21" s="135"/>
       <c r="D21" t="s">
         <v>101</v>
@@ -5141,7 +5142,7 @@
       </c>
       <c r="M21" s="137"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="138"/>
       <c r="D22" s="139"/>
       <c r="E22" s="139"/>
@@ -5154,16 +5155,16 @@
       <c r="L22" s="139"/>
       <c r="M22" s="140"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K25" s="141" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G26" s="5"/>
       <c r="K26" s="119"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I27" t="s">
         <v>105</v>
       </c>
@@ -5174,7 +5175,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>95</v>
@@ -5190,7 +5191,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J31" t="s">
         <v>107</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J32" t="s">
         <v>108</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J33" s="119" t="s">
         <v>109</v>
       </c>
@@ -5214,7 +5215,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K34" s="113">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5229,22 +5230,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D1" s="55">
         <v>50000</v>
       </c>
@@ -5254,14 +5255,14 @@
       <c r="I1" s="207"/>
       <c r="J1" s="207"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>56</v>
       </c>
@@ -5284,7 +5285,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5327,7 +5328,7 @@
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5358,7 +5359,7 @@
       <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5406,7 +5407,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5454,7 +5455,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5502,7 +5503,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5550,7 +5551,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5598,7 +5599,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5646,7 +5647,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5694,7 +5695,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5742,7 +5743,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5808,42 +5809,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="s">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="211" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="209" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="211" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="210">
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="212">
         <v>800000</v>
       </c>
-      <c r="J1" s="210"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J1" s="212"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97"/>
       <c r="B2" s="98"/>
       <c r="C2" s="99"/>
@@ -5857,15 +5858,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="178"/>
+      <c r="C3" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="175" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5874,50 +5875,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="186" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="189" t="s">
+      <c r="H3" s="186" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="197" t="s">
+      <c r="J3" s="175" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="211" t="s">
+      <c r="L3" s="208" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="179"/>
+      <c r="B4" s="180"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="198"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="176"/>
       <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="212"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+      <c r="L4" s="209"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="181">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="182"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -5953,11 +5954,11 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="181">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -5995,11 +5996,11 @@
         <v>64880.003495999961</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -6037,11 +6038,11 @@
         <v>99680</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="182"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -6079,11 +6080,11 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -6121,11 +6122,11 @@
         <v>99279.992624999984</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -6161,11 +6162,11 @@
         <v>94999.311648000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -6201,11 +6202,11 @@
         <v>146080.00000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="181" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="182"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6242,11 +6243,11 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="182"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6283,11 +6284,11 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="182"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6324,7 +6325,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -6364,7 +6365,7 @@
         <v>765159.30776899995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -6372,7 +6373,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -6390,7 +6391,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6422,7 +6423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6448,7 +6449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6482,7 +6483,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6516,7 +6517,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6551,7 +6552,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6582,7 +6583,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6613,7 +6614,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6644,7 +6645,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -6745,44 +6746,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="195"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="195"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -6799,7 +6800,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -6815,7 +6816,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -6829,23 +6830,23 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="200"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="201"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -6859,7 +6860,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -6878,13 +6879,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -6902,7 +6903,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -6912,11 +6913,11 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -6935,7 +6936,7 @@
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -6954,7 +6955,7 @@
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -6973,7 +6974,7 @@
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -6987,7 +6988,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -7001,7 +7002,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -7014,7 +7015,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -7028,7 +7029,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -7042,7 +7043,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -7061,7 +7062,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -7075,58 +7076,58 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="194">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="195"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="197"/>
+      <c r="G56" s="197"/>
+      <c r="H56" s="197"/>
+      <c r="I56" s="197"/>
+      <c r="J56" s="197"/>
+      <c r="K56" s="195"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
+      <c r="H57" s="197"/>
+      <c r="I57" s="197"/>
+      <c r="J57" s="197"/>
+      <c r="K57" s="195"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -7140,7 +7141,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -7153,7 +7154,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -7164,20 +7165,20 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="201"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -7188,7 +7189,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -7205,12 +7206,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="184"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -7225,7 +7226,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -7233,10 +7234,10 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -7252,7 +7253,7 @@
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -7268,7 +7269,7 @@
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -7284,7 +7285,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -7295,7 +7296,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -7306,7 +7307,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -7316,7 +7317,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -7327,7 +7328,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -7338,7 +7339,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -7349,7 +7350,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -7360,50 +7361,50 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="193"/>
+      <c r="G76" s="193"/>
+      <c r="H76" s="193"/>
+      <c r="I76" s="193"/>
+      <c r="J76" s="194">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="195"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="197"/>
+      <c r="G83" s="197"/>
+      <c r="H83" s="197"/>
+      <c r="I83" s="197"/>
+      <c r="J83" s="197"/>
+      <c r="K83" s="195"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="197"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="197"/>
+      <c r="I84" s="197"/>
+      <c r="J84" s="197"/>
+      <c r="K84" s="195"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -7417,7 +7418,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -7430,7 +7431,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -7441,20 +7442,20 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="200"/>
+      <c r="G88" s="200"/>
+      <c r="H88" s="200"/>
+      <c r="I88" s="200"/>
+      <c r="J88" s="200"/>
+      <c r="K88" s="201"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -7465,7 +7466,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -7482,12 +7483,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="184"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -7502,7 +7503,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -7510,10 +7511,10 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -7529,7 +7530,7 @@
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -7545,7 +7546,7 @@
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -7560,7 +7561,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -7571,7 +7572,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -7582,7 +7583,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -7592,7 +7593,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -7603,7 +7604,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -7614,7 +7615,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -7625,7 +7626,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -7636,50 +7637,50 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="193"/>
+      <c r="G103" s="193"/>
+      <c r="H103" s="193"/>
+      <c r="I103" s="193"/>
+      <c r="J103" s="194">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="195"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="197"/>
+      <c r="G108" s="197"/>
+      <c r="H108" s="197"/>
+      <c r="I108" s="197"/>
+      <c r="J108" s="197"/>
+      <c r="K108" s="195"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="197"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="195"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -7693,7 +7694,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -7706,7 +7707,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -7717,20 +7718,20 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="200"/>
+      <c r="G113" s="200"/>
+      <c r="H113" s="200"/>
+      <c r="I113" s="200"/>
+      <c r="J113" s="200"/>
+      <c r="K113" s="201"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -7741,7 +7742,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -7758,12 +7759,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="184"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -7778,7 +7779,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -7786,10 +7787,10 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -7805,7 +7806,7 @@
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -7821,7 +7822,7 @@
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -7837,7 +7838,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -7848,7 +7849,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -7859,7 +7860,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -7869,7 +7870,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -7880,7 +7881,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -7891,7 +7892,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -7902,7 +7903,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -7913,24 +7914,58 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="193"/>
+      <c r="G128" s="193"/>
+      <c r="H128" s="193"/>
+      <c r="I128" s="193"/>
+      <c r="J128" s="194">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="195"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -7947,40 +7982,6 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
+++ b/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C13D6CE-4760-432D-BB87-63F3049BBCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C405EBA-D93E-4BE8-A346-92F452FDD0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,12 +428,6 @@
     <t>EDESUR:</t>
   </si>
   <si>
-    <t>AYSA - septiembre</t>
-  </si>
-  <si>
-    <t>Edesur - septiembre</t>
-  </si>
-  <si>
     <t>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</t>
   </si>
   <si>
@@ -441,6 +435,12 @@
   </si>
   <si>
     <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593</t>
+  </si>
+  <si>
+    <t>AYSA - NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Edesur - NOVIEMBRE</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1452,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1599,9 +1599,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1725,9 +1722,29 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1746,45 +1763,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1793,6 +1782,11 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1826,7 +1820,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2230,8 +2231,8 @@
       <c r="C5" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="169" t="s">
-        <v>134</v>
+      <c r="A7" s="168" t="s">
+        <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
@@ -2275,13 +2276,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="174">
-        <v>91854.86</v>
+      <c r="C17" s="211">
+        <v>86076.01</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
@@ -2289,9 +2290,9 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="60">
+      <c r="C18" s="212">
         <f>SUM(C17:C17)</f>
-        <v>91854.86</v>
+        <v>86076.01</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2299,24 +2300,24 @@
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
-      <c r="C19" s="90"/>
+      <c r="C19" s="213"/>
     </row>
     <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="91"/>
-      <c r="C20" s="84">
+        <v>133</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="214">
         <v>37000</v>
       </c>
       <c r="F20" s="22"/>
     </row>
     <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="213">
+        <v>134</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="214">
         <v>36534.6</v>
       </c>
       <c r="F21" s="22"/>
@@ -2345,9 +2346,9 @@
         <v>78</v>
       </c>
       <c r="B24" s="79"/>
-      <c r="C24" s="92">
+      <c r="C24" s="91">
         <f>+C23+C18</f>
-        <v>165389.46000000002</v>
+        <v>159610.60999999999</v>
       </c>
       <c r="F24" s="22"/>
     </row>
@@ -2402,24 +2403,24 @@
       <c r="B33" s="34"/>
       <c r="C33" s="35">
         <f>+C31+C24</f>
-        <v>165389.46000000002</v>
+        <v>159610.60999999999</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="146" t="s">
+      <c r="A35" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="147"/>
-      <c r="C35" s="148"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="147"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="143" t="s">
         <v>10</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="145">
-        <v>-406759.6</v>
+      <c r="C36" s="144">
+        <v>-728212.36639999994</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -2430,17 +2431,17 @@
       </c>
       <c r="C37" s="32">
         <f>'prorrateo '!F15</f>
-        <v>0</v>
+        <v>404745.41000000015</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="93">
-        <v>-229765.65</v>
+        <v>136</v>
+      </c>
+      <c r="C38" s="92">
+        <v>-172630.83</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
@@ -2449,9 +2450,9 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="93">
-        <f>-(C24-C22)</f>
-        <v>-165389.46000000002</v>
+      <c r="C39" s="92">
+        <f>-C24</f>
+        <v>-159610.60999999999</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2461,7 +2462,7 @@
       <c r="B40" s="33"/>
       <c r="C40" s="40">
         <f>SUM(C36:C39)</f>
-        <v>-801914.71</v>
+        <v>-655708.39639999974</v>
       </c>
       <c r="D40" s="6"/>
     </row>
@@ -2474,7 +2475,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
-      <c r="F42" s="94"/>
+      <c r="F42" s="93"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
@@ -2579,40 +2580,42 @@
         <v>48</v>
       </c>
       <c r="E1" s="14">
-        <v>165389.46000000002</v>
-      </c>
-      <c r="H1" s="202" t="s">
+        <v>159610.60999999999</v>
+      </c>
+      <c r="H1" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="14"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="14">
+        <v>172630.83</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="97">
+      <c r="A2" s="96">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="101"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="177" t="s">
+      <c r="A3" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="178"/>
-      <c r="C3" s="186" t="s">
+      <c r="B3" s="185"/>
+      <c r="C3" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="175" t="s">
+      <c r="D3" s="182" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2621,19 +2624,19 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="177" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="190" t="s">
+      <c r="I3" s="173" t="s">
         <v>7</v>
       </c>
       <c r="J3" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="186" t="s">
+      <c r="K3" s="177" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
@@ -2641,443 +2644,473 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="179"/>
-      <c r="B4" s="180"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="176"/>
+      <c r="A4" s="186"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="183"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="187"/>
+      <c r="G4" s="178"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="191"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="189"/>
-      <c r="K4" s="187"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="181">
+      <c r="A5" s="175">
         <v>1</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="110" t="s">
+      <c r="B5" s="176"/>
+      <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="58"/>
-      <c r="E5" s="149">
-        <v>41531.40466575251</v>
-      </c>
-      <c r="F5" s="150"/>
-      <c r="G5" s="151">
+      <c r="E5" s="148">
+        <v>55854.866580000002</v>
+      </c>
+      <c r="F5" s="149">
+        <f>E5</f>
+        <v>55854.866580000002</v>
+      </c>
+      <c r="G5" s="150">
         <f>E5-F5</f>
-        <v>41531.40466575251</v>
-      </c>
-      <c r="H5" s="151">
+        <v>0</v>
+      </c>
+      <c r="H5" s="150">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>1661.2561866301005</v>
-      </c>
-      <c r="I5" s="95">
+        <v>0</v>
+      </c>
+      <c r="I5" s="94">
         <v>13.8</v>
       </c>
-      <c r="J5" s="96">
+      <c r="J5" s="95">
         <f>E$1*I5/100</f>
-        <v>22823.745480000005</v>
-      </c>
-      <c r="K5" s="142">
+        <v>22026.264180000002</v>
+      </c>
+      <c r="K5" s="141">
         <f>J$1*I5/100</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="103">
+        <v>23823.054539999997</v>
+      </c>
+      <c r="L5" s="102">
         <f>G5+H5+J5+K5</f>
-        <v>66016.406332382612</v>
+        <v>45849.318719999996</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="181">
+      <c r="A6" s="175">
         <v>2</v>
       </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="110" t="s">
+      <c r="B6" s="176"/>
+      <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D6" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="149">
-        <v>36166.928390240799</v>
-      </c>
-      <c r="F6" s="150"/>
-      <c r="G6" s="151">
-        <f t="shared" ref="G6:G14" si="0">E6-F6</f>
-        <v>36166.928390240799</v>
-      </c>
-      <c r="H6" s="151">
-        <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*4%,0)</f>
-        <v>1446.6771356096319</v>
-      </c>
-      <c r="I6" s="95">
+      <c r="E6" s="148">
+        <v>48002.805626000001</v>
+      </c>
+      <c r="F6" s="149">
+        <f t="shared" ref="F6:F14" si="0">E6</f>
+        <v>48002.805626000001</v>
+      </c>
+      <c r="G6" s="150">
+        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="150">
+        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="94">
         <v>11.86</v>
       </c>
-      <c r="J6" s="96">
-        <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
-        <v>19615.189956000002</v>
-      </c>
-      <c r="K6" s="142">
-        <f t="shared" ref="K6:K14" si="3">J$1*I6/100</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="103">
-        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>57228.795481850429</v>
+      <c r="J6" s="95">
+        <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
+        <v>18929.818345999996</v>
+      </c>
+      <c r="K6" s="141">
+        <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
+        <v>20474.016437999999</v>
+      </c>
+      <c r="L6" s="102">
+        <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
+        <v>39403.834783999991</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
+      <c r="A7" s="175">
         <v>3</v>
       </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="110" t="s">
+      <c r="B7" s="176"/>
+      <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D7" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="149">
-        <v>37894.033173585289</v>
-      </c>
-      <c r="F7" s="150"/>
-      <c r="G7" s="151">
+      <c r="E7" s="148">
+        <v>50431.278086000006</v>
+      </c>
+      <c r="F7" s="149">
         <f t="shared" si="0"/>
-        <v>37894.033173585289</v>
-      </c>
-      <c r="H7" s="151">
+        <v>50431.278086000006</v>
+      </c>
+      <c r="G7" s="150">
         <f t="shared" si="1"/>
-        <v>1515.7613269434116</v>
-      </c>
-      <c r="I7" s="95">
+        <v>0</v>
+      </c>
+      <c r="H7" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="94">
         <v>12.46</v>
       </c>
-      <c r="J7" s="96">
-        <f t="shared" si="2"/>
-        <v>20607.526716000004</v>
-      </c>
-      <c r="K7" s="142">
+      <c r="J7" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="103">
+        <v>19887.482005999998</v>
+      </c>
+      <c r="K7" s="141">
         <f t="shared" si="4"/>
-        <v>60017.321216528711</v>
+        <v>21509.801417999999</v>
+      </c>
+      <c r="L7" s="102">
+        <f t="shared" si="5"/>
+        <v>41397.283423999994</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="181">
+      <c r="A8" s="175">
         <v>4</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="110" t="s">
+      <c r="B8" s="176"/>
+      <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="149">
-        <v>44723.725567140471</v>
-      </c>
-      <c r="F8" s="150"/>
-      <c r="G8" s="151">
+      <c r="E8" s="148">
+        <v>59699.947975000003</v>
+      </c>
+      <c r="F8" s="149">
         <f t="shared" si="0"/>
-        <v>44723.725567140471</v>
-      </c>
-      <c r="H8" s="151">
+        <v>59699.947975000003</v>
+      </c>
+      <c r="G8" s="150">
         <f t="shared" si="1"/>
-        <v>1788.949022685619</v>
-      </c>
-      <c r="I8" s="95">
+        <v>0</v>
+      </c>
+      <c r="H8" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="94">
         <v>14.75</v>
       </c>
-      <c r="J8" s="96">
-        <f t="shared" si="2"/>
-        <v>24394.945350000002</v>
-      </c>
-      <c r="K8" s="142">
+      <c r="J8" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="103">
+        <v>23542.564974999998</v>
+      </c>
+      <c r="K8" s="141">
         <f t="shared" si="4"/>
-        <v>70907.619939826094</v>
+        <v>25463.047424999997</v>
+      </c>
+      <c r="L8" s="102">
+        <f t="shared" si="5"/>
+        <v>49005.612399999998</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="181">
+      <c r="A9" s="175">
         <v>5</v>
       </c>
-      <c r="B9" s="182"/>
-      <c r="C9" s="110" t="s">
+      <c r="B9" s="176"/>
+      <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="149">
-        <v>37111.569982331108</v>
-      </c>
-      <c r="F9" s="150"/>
-      <c r="G9" s="151">
+      <c r="E9" s="148">
+        <v>50228.905381000004</v>
+      </c>
+      <c r="F9" s="149">
         <f t="shared" si="0"/>
-        <v>37111.569982331108</v>
-      </c>
-      <c r="H9" s="151">
+        <v>50228.905381000004</v>
+      </c>
+      <c r="G9" s="150">
         <f t="shared" si="1"/>
-        <v>1484.4627992932444</v>
-      </c>
-      <c r="I9" s="95">
+        <v>0</v>
+      </c>
+      <c r="H9" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="94">
         <v>12.41</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="95">
+        <f t="shared" si="3"/>
+        <v>19807.676700999997</v>
+      </c>
+      <c r="K9" s="141">
+        <f t="shared" si="4"/>
+        <v>21423.486003000002</v>
+      </c>
+      <c r="L9" s="102">
+        <f>G9+H9+J9+K9</f>
+        <v>41231.162704000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175">
+        <v>6</v>
+      </c>
+      <c r="B10" s="176"/>
+      <c r="C10" s="109" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="72"/>
+      <c r="E10" s="148">
+        <v>50512.227168000012</v>
+      </c>
+      <c r="F10" s="149">
+        <f t="shared" si="0"/>
+        <v>50512.227168000012</v>
+      </c>
+      <c r="G10" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="150">
         <f t="shared" si="2"/>
-        <v>20524.831986000001</v>
-      </c>
-      <c r="K9" s="142">
+        <v>0</v>
+      </c>
+      <c r="I10" s="94">
+        <v>12.48</v>
+      </c>
+      <c r="J10" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="103">
-        <f>G9+H9+J9+K9</f>
-        <v>59120.864767624356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="181">
-        <v>6</v>
-      </c>
-      <c r="B10" s="182"/>
-      <c r="C10" s="110" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="72"/>
-      <c r="E10" s="149">
-        <v>37332.293419986621</v>
-      </c>
-      <c r="F10" s="150"/>
-      <c r="G10" s="151">
+        <v>19919.404127999998</v>
+      </c>
+      <c r="K10" s="141">
+        <f t="shared" si="4"/>
+        <v>21544.327583999999</v>
+      </c>
+      <c r="L10" s="102">
+        <f t="shared" si="5"/>
+        <v>41463.731711999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175">
+        <v>7</v>
+      </c>
+      <c r="B11" s="176"/>
+      <c r="C11" s="109" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="148">
+        <v>73906.511866000015</v>
+      </c>
+      <c r="F11" s="149">
         <f t="shared" si="0"/>
-        <v>37332.293419986621</v>
-      </c>
-      <c r="H10" s="151">
+        <v>73906.511866000015</v>
+      </c>
+      <c r="G11" s="150">
         <f t="shared" si="1"/>
-        <v>1493.2917367994648</v>
-      </c>
-      <c r="I10" s="95">
-        <v>12.48</v>
-      </c>
-      <c r="J10" s="96">
+        <v>0</v>
+      </c>
+      <c r="H11" s="150">
         <f t="shared" si="2"/>
-        <v>20640.604608000001</v>
-      </c>
-      <c r="K10" s="142">
+        <v>0</v>
+      </c>
+      <c r="I11" s="94">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="J11" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="103">
+        <v>29144.897385999997</v>
+      </c>
+      <c r="K11" s="141">
         <f t="shared" si="4"/>
-        <v>59466.18976478609</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="181">
-        <v>7</v>
-      </c>
-      <c r="B11" s="182"/>
-      <c r="C11" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="72"/>
-      <c r="E11" s="149">
-        <v>54686.953726963213</v>
-      </c>
-      <c r="F11" s="150"/>
-      <c r="G11" s="151">
-        <f t="shared" si="0"/>
-        <v>54686.953726963213</v>
-      </c>
-      <c r="H11" s="151">
-        <f t="shared" si="1"/>
-        <v>2187.4781490785285</v>
-      </c>
-      <c r="I11" s="95">
-        <v>18.260000000000002</v>
-      </c>
-      <c r="J11" s="96">
-        <f t="shared" si="2"/>
-        <v>30200.115396000008</v>
-      </c>
-      <c r="K11" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="103">
-        <f t="shared" si="4"/>
-        <v>87074.54727204176</v>
+        <v>31522.389558000003</v>
+      </c>
+      <c r="L11" s="102">
+        <f t="shared" si="5"/>
+        <v>60667.286943999999</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="181" t="s">
+      <c r="A12" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="182"/>
-      <c r="C12" s="110" t="str">
+      <c r="B12" s="176"/>
+      <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="72"/>
-      <c r="E12" s="149">
-        <v>3895.6564420000004</v>
-      </c>
-      <c r="F12" s="150"/>
-      <c r="G12" s="151">
+      <c r="E12" s="148">
+        <v>5423.5884940000014</v>
+      </c>
+      <c r="F12" s="149">
         <f t="shared" si="0"/>
-        <v>3895.6564420000004</v>
-      </c>
-      <c r="H12" s="151">
+        <v>5423.5884940000014</v>
+      </c>
+      <c r="G12" s="150">
         <f t="shared" si="1"/>
-        <v>155.82625768000003</v>
-      </c>
-      <c r="I12" s="95">
+        <v>0</v>
+      </c>
+      <c r="H12" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="94">
         <v>1.34</v>
       </c>
-      <c r="J12" s="96">
-        <f t="shared" si="2"/>
-        <v>2216.2187640000002</v>
-      </c>
-      <c r="K12" s="142">
+      <c r="J12" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="103">
+        <v>2138.7821739999999</v>
+      </c>
+      <c r="K12" s="141">
         <f t="shared" si="4"/>
-        <v>6267.7014636800004</v>
+        <v>2313.2531220000001</v>
+      </c>
+      <c r="L12" s="102">
+        <f t="shared" si="5"/>
+        <v>4452.035296</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="182"/>
-      <c r="C13" s="110" t="str">
+      <c r="B13" s="176"/>
+      <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="72"/>
-      <c r="E13" s="149">
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="F13" s="150"/>
-      <c r="G13" s="151">
+      <c r="E13" s="148">
+        <v>5342.6394120000004</v>
+      </c>
+      <c r="F13" s="149">
         <f t="shared" si="0"/>
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="H13" s="151">
+        <v>5342.6394120000004</v>
+      </c>
+      <c r="G13" s="150">
         <f t="shared" si="1"/>
-        <v>153.50049264</v>
-      </c>
-      <c r="I13" s="95">
+        <v>0</v>
+      </c>
+      <c r="H13" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="94">
         <v>1.32</v>
       </c>
-      <c r="J13" s="96">
-        <f t="shared" si="2"/>
-        <v>2183.1408720000004</v>
-      </c>
-      <c r="K13" s="142">
+      <c r="J13" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="103">
+        <v>2106.860052</v>
+      </c>
+      <c r="K13" s="141">
         <f t="shared" si="4"/>
-        <v>6174.1536806399999</v>
+        <v>2278.726956</v>
+      </c>
+      <c r="L13" s="102">
+        <f t="shared" si="5"/>
+        <v>4385.5870080000004</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="181" t="s">
+      <c r="A14" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="182"/>
+      <c r="B14" s="176"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="72"/>
-      <c r="E14" s="149">
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="F14" s="150"/>
-      <c r="G14" s="151">
+      <c r="E14" s="148">
+        <v>5342.6394120000004</v>
+      </c>
+      <c r="F14" s="149">
         <f t="shared" si="0"/>
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="H14" s="151">
+        <v>5342.6394120000004</v>
+      </c>
+      <c r="G14" s="150">
         <f t="shared" si="1"/>
-        <v>153.50049264</v>
-      </c>
-      <c r="I14" s="95">
+        <v>0</v>
+      </c>
+      <c r="H14" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="94">
         <v>1.32</v>
       </c>
-      <c r="J14" s="96">
-        <f t="shared" si="2"/>
-        <v>2183.1408720000004</v>
-      </c>
-      <c r="K14" s="142">
+      <c r="J14" s="95">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="103">
+        <v>2106.860052</v>
+      </c>
+      <c r="K14" s="141">
         <f t="shared" si="4"/>
-        <v>6174.1536806399999</v>
+        <v>2278.726956</v>
+      </c>
+      <c r="L14" s="102">
+        <f t="shared" si="5"/>
+        <v>4385.5870080000004</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>301017.59000000003</v>
-      </c>
-      <c r="F15" s="107">
+        <v>404745.41000000015</v>
+      </c>
+      <c r="F15" s="106">
         <f>SUM(F5:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="107"/>
-      <c r="H15" s="108">
+        <v>404745.41000000015</v>
+      </c>
+      <c r="G15" s="106"/>
+      <c r="H15" s="107">
         <f>SUM(H5:H14)</f>
-        <v>12040.703600000001</v>
-      </c>
-      <c r="I15" s="109">
-        <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="108">
+        <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>165389.46</v>
+        <v>159610.60999999999</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>0</v>
+        <v>165760.12296599997</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>478447.75360000005</v>
+        <v>332241.44</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -3223,7 +3256,7 @@
         <v>0.122</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" ref="J23:J29" si="6">0*I23</f>
+        <f t="shared" ref="J23:J29" si="7">0*I23</f>
         <v>0</v>
       </c>
       <c r="K23" s="41"/>
@@ -3258,7 +3291,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K24" s="41"/>
@@ -3289,7 +3322,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
@@ -3320,7 +3353,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K26" s="41"/>
@@ -3351,7 +3384,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K27" s="41"/>
@@ -3385,7 +3418,7 @@
         <v>0.127</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K28" s="41"/>
@@ -3419,7 +3452,7 @@
         <v>0.127</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="41"/>
@@ -3448,11 +3481,11 @@
         <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:J30" si="7">SUM(I22:I29)</f>
+        <f t="shared" ref="I30:J30" si="8">SUM(I22:I29)</f>
         <v>1</v>
       </c>
       <c r="J30" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K30" s="42"/>
@@ -3469,345 +3502,345 @@
     <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="196" t="s">
+      <c r="E32" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="197"/>
-      <c r="G32" s="197"/>
-      <c r="H32" s="197"/>
-      <c r="I32" s="197"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="195"/>
-      <c r="L32" s="152"/>
-      <c r="M32" s="153"/>
+      <c r="F32" s="191"/>
+      <c r="G32" s="191"/>
+      <c r="H32" s="191"/>
+      <c r="I32" s="191"/>
+      <c r="J32" s="191"/>
+      <c r="K32" s="192"/>
+      <c r="L32" s="151"/>
+      <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
     <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="198" t="s">
+      <c r="E33" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="197"/>
-      <c r="G33" s="197"/>
-      <c r="H33" s="197"/>
-      <c r="I33" s="197"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="195"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="155"/>
+      <c r="F33" s="191"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="192"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="157"/>
-      <c r="J34" s="157">
+      <c r="E34" s="151"/>
+      <c r="F34" s="155"/>
+      <c r="G34" s="155"/>
+      <c r="H34" s="155"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="155"/>
-      <c r="L34" s="154"/>
-      <c r="M34" s="155"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="153"/>
+      <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="154" t="s">
+      <c r="E35" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F35" s="157"/>
-      <c r="G35" s="157"/>
-      <c r="H35" s="157"/>
-      <c r="I35" s="157"/>
-      <c r="J35" s="157"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="154"/>
-      <c r="M35" s="155"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="156"/>
+      <c r="H35" s="156"/>
+      <c r="I35" s="156"/>
+      <c r="J35" s="156"/>
+      <c r="K35" s="154"/>
+      <c r="L35" s="153"/>
+      <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="158"/>
-      <c r="F36" s="159"/>
-      <c r="G36" s="159"/>
-      <c r="H36" s="159"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="159"/>
-      <c r="K36" s="160"/>
-      <c r="L36" s="154"/>
-      <c r="M36" s="155"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="158"/>
+      <c r="G36" s="158"/>
+      <c r="H36" s="158"/>
+      <c r="I36" s="158"/>
+      <c r="J36" s="158"/>
+      <c r="K36" s="159"/>
+      <c r="L36" s="153"/>
+      <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="199" t="s">
+      <c r="E37" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="200"/>
-      <c r="I37" s="200"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="201"/>
-      <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="195"/>
+      <c r="I37" s="195"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="196"/>
+      <c r="L37" s="153"/>
+      <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="154"/>
-      <c r="F38" s="157"/>
-      <c r="G38" s="157"/>
-      <c r="H38" s="157"/>
-      <c r="I38" s="157"/>
-      <c r="J38" s="157"/>
-      <c r="K38" s="155"/>
-      <c r="L38" s="154"/>
-      <c r="M38" s="155"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="156"/>
+      <c r="G38" s="156"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="156"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="154"/>
+      <c r="L38" s="153"/>
+      <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="154" t="s">
+      <c r="E39" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157" t="str">
+      <c r="F39" s="156"/>
+      <c r="G39" s="156" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="157"/>
-      <c r="I39" s="157" t="s">
+      <c r="H39" s="156"/>
+      <c r="I39" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J39" s="161">
+      <c r="J39" s="160">
         <v>45674</v>
       </c>
-      <c r="K39" s="155"/>
-      <c r="L39" s="183" t="s">
+      <c r="K39" s="154"/>
+      <c r="L39" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="184"/>
+      <c r="M39" s="180"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="154" t="s">
+      <c r="E40" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="162">
+      <c r="F40" s="161">
         <v>3</v>
       </c>
-      <c r="G40" s="157"/>
-      <c r="H40" s="157"/>
-      <c r="I40" s="157"/>
-      <c r="J40" s="157"/>
-      <c r="K40" s="155"/>
-      <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="154"/>
+      <c r="L40" s="153"/>
+      <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
-      <c r="I41" s="157"/>
-      <c r="J41" s="157"/>
-      <c r="K41" s="155"/>
-      <c r="L41" s="185"/>
-      <c r="M41" s="184"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="156"/>
+      <c r="I41" s="156"/>
+      <c r="J41" s="156"/>
+      <c r="K41" s="154"/>
+      <c r="L41" s="181"/>
+      <c r="M41" s="180"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="154" t="s">
+      <c r="E42" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="157"/>
-      <c r="J42" s="163">
+      <c r="F42" s="156"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="156"/>
+      <c r="I42" s="156"/>
+      <c r="J42" s="162">
         <f>J7</f>
-        <v>20607.526716000004</v>
-      </c>
-      <c r="K42" s="155"/>
-      <c r="L42" s="154"/>
-      <c r="M42" s="155"/>
+        <v>19887.482005999998</v>
+      </c>
+      <c r="K42" s="154"/>
+      <c r="L42" s="153"/>
+      <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="164" t="s">
+      <c r="E43" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="163">
+      <c r="F43" s="156"/>
+      <c r="G43" s="156"/>
+      <c r="H43" s="156"/>
+      <c r="I43" s="156"/>
+      <c r="J43" s="162">
         <f>K7</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="155"/>
-      <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+        <v>21509.801417999999</v>
+      </c>
+      <c r="K43" s="154"/>
+      <c r="L43" s="153"/>
+      <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="164" t="s">
+      <c r="E44" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="157"/>
-      <c r="G44" s="157"/>
-      <c r="H44" s="157"/>
-      <c r="I44" s="157"/>
-      <c r="J44" s="163">
+      <c r="F44" s="156"/>
+      <c r="G44" s="156"/>
+      <c r="H44" s="156"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="162">
         <f>G7+H7</f>
-        <v>39409.794500528704</v>
-      </c>
-      <c r="K44" s="155"/>
-      <c r="L44" s="154"/>
-      <c r="M44" s="155"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="154"/>
+      <c r="L44" s="153"/>
+      <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
     <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="164"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="157"/>
-      <c r="I45" s="157"/>
-      <c r="J45" s="163"/>
-      <c r="K45" s="155"/>
-      <c r="L45" s="154"/>
-      <c r="M45" s="155"/>
+      <c r="E45" s="163"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
+      <c r="H45" s="156"/>
+      <c r="I45" s="156"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="154"/>
+      <c r="L45" s="153"/>
+      <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
     <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="164"/>
-      <c r="F46" s="157"/>
-      <c r="G46" s="157"/>
-      <c r="H46" s="157"/>
-      <c r="I46" s="157"/>
-      <c r="J46" s="163"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="154"/>
-      <c r="M46" s="155"/>
+      <c r="E46" s="163"/>
+      <c r="F46" s="156"/>
+      <c r="G46" s="156"/>
+      <c r="H46" s="156"/>
+      <c r="I46" s="156"/>
+      <c r="J46" s="162"/>
+      <c r="K46" s="154"/>
+      <c r="L46" s="153"/>
+      <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
     <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="157"/>
-      <c r="G47" s="157"/>
-      <c r="H47" s="157"/>
-      <c r="I47" s="157"/>
-      <c r="J47" s="163"/>
-      <c r="K47" s="155"/>
-      <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="F47" s="156"/>
+      <c r="G47" s="156"/>
+      <c r="H47" s="156"/>
+      <c r="I47" s="156"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="154"/>
+      <c r="L47" s="153"/>
+      <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
     <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="164"/>
-      <c r="F48" s="157"/>
-      <c r="G48" s="157"/>
-      <c r="H48" s="157"/>
-      <c r="I48" s="157"/>
-      <c r="J48" s="163"/>
-      <c r="K48" s="155"/>
-      <c r="L48" s="154"/>
-      <c r="M48" s="155"/>
+      <c r="E48" s="163"/>
+      <c r="F48" s="156"/>
+      <c r="G48" s="156"/>
+      <c r="H48" s="156"/>
+      <c r="I48" s="156"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="154"/>
+      <c r="L48" s="153"/>
+      <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
     <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="154"/>
-      <c r="F49" s="157"/>
-      <c r="G49" s="157"/>
-      <c r="H49" s="157"/>
-      <c r="I49" s="157"/>
-      <c r="J49" s="157"/>
-      <c r="K49" s="155"/>
-      <c r="L49" s="154"/>
-      <c r="M49" s="155"/>
+      <c r="E49" s="153"/>
+      <c r="F49" s="156"/>
+      <c r="G49" s="156"/>
+      <c r="H49" s="156"/>
+      <c r="I49" s="156"/>
+      <c r="J49" s="156"/>
+      <c r="K49" s="154"/>
+      <c r="L49" s="153"/>
+      <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="154" t="s">
+      <c r="E50" s="153" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="157"/>
-      <c r="G50" s="157"/>
-      <c r="H50" s="157"/>
-      <c r="I50" s="157"/>
-      <c r="J50" s="157">
+      <c r="F50" s="156"/>
+      <c r="G50" s="156"/>
+      <c r="H50" s="156"/>
+      <c r="I50" s="156"/>
+      <c r="J50" s="156">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="155"/>
-      <c r="L50" s="154"/>
-      <c r="M50" s="155"/>
+      <c r="K50" s="154"/>
+      <c r="L50" s="153"/>
+      <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
     <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="154"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="157"/>
-      <c r="I51" s="157"/>
-      <c r="J51" s="157"/>
-      <c r="K51" s="155"/>
-      <c r="L51" s="165"/>
-      <c r="M51" s="166"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="156"/>
+      <c r="G51" s="156"/>
+      <c r="H51" s="156"/>
+      <c r="I51" s="156"/>
+      <c r="J51" s="156"/>
+      <c r="K51" s="154"/>
+      <c r="L51" s="164"/>
+      <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
     <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="192" t="s">
+      <c r="E52" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="194">
+      <c r="F52" s="198"/>
+      <c r="G52" s="198"/>
+      <c r="H52" s="198"/>
+      <c r="I52" s="198"/>
+      <c r="J52" s="199">
         <f>SUM(J42:J51)</f>
-        <v>60093.121216528714</v>
-      </c>
-      <c r="K52" s="195"/>
-      <c r="L52" s="167"/>
-      <c r="M52" s="168"/>
+        <v>41473.083423999997</v>
+      </c>
+      <c r="K52" s="192"/>
+      <c r="L52" s="166"/>
+      <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.3">
@@ -3817,833 +3850,833 @@
     </row>
     <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="196" t="s">
+      <c r="E56" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="197"/>
-      <c r="G56" s="197"/>
-      <c r="H56" s="197"/>
-      <c r="I56" s="197"/>
-      <c r="J56" s="197"/>
-      <c r="K56" s="195"/>
-      <c r="L56" s="152"/>
-      <c r="M56" s="153"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="191"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="191"/>
+      <c r="J56" s="191"/>
+      <c r="K56" s="192"/>
+      <c r="L56" s="151"/>
+      <c r="M56" s="152"/>
     </row>
     <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="198" t="s">
+      <c r="E57" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="197"/>
-      <c r="G57" s="197"/>
-      <c r="H57" s="197"/>
-      <c r="I57" s="197"/>
-      <c r="J57" s="197"/>
-      <c r="K57" s="195"/>
-      <c r="L57" s="154"/>
-      <c r="M57" s="155"/>
+      <c r="F57" s="191"/>
+      <c r="G57" s="191"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="191"/>
+      <c r="J57" s="191"/>
+      <c r="K57" s="192"/>
+      <c r="L57" s="153"/>
+      <c r="M57" s="154"/>
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E58" s="152"/>
-      <c r="F58" s="156"/>
-      <c r="G58" s="156"/>
-      <c r="H58" s="156"/>
-      <c r="I58" s="157"/>
-      <c r="J58" s="157">
+      <c r="E58" s="151"/>
+      <c r="F58" s="155"/>
+      <c r="G58" s="155"/>
+      <c r="H58" s="155"/>
+      <c r="I58" s="156"/>
+      <c r="J58" s="156">
         <f>J34</f>
         <v>0</v>
       </c>
-      <c r="K58" s="155"/>
-      <c r="L58" s="154"/>
-      <c r="M58" s="155"/>
+      <c r="K58" s="154"/>
+      <c r="L58" s="153"/>
+      <c r="M58" s="154"/>
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E59" s="154" t="s">
+      <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F59" s="157"/>
-      <c r="G59" s="157"/>
-      <c r="H59" s="157"/>
-      <c r="I59" s="157"/>
-      <c r="J59" s="157"/>
-      <c r="K59" s="155"/>
-      <c r="L59" s="154"/>
-      <c r="M59" s="155"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="154"/>
+      <c r="L59" s="153"/>
+      <c r="M59" s="154"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E60" s="158"/>
-      <c r="F60" s="159"/>
-      <c r="G60" s="159"/>
-      <c r="H60" s="159"/>
-      <c r="I60" s="159"/>
-      <c r="J60" s="159"/>
-      <c r="K60" s="160"/>
-      <c r="L60" s="154"/>
-      <c r="M60" s="155"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="158"/>
+      <c r="G60" s="158"/>
+      <c r="H60" s="158"/>
+      <c r="I60" s="158"/>
+      <c r="J60" s="158"/>
+      <c r="K60" s="159"/>
+      <c r="L60" s="153"/>
+      <c r="M60" s="154"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="199" t="s">
+      <c r="E61" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="200"/>
-      <c r="G61" s="200"/>
-      <c r="H61" s="200"/>
-      <c r="I61" s="200"/>
-      <c r="J61" s="200"/>
-      <c r="K61" s="201"/>
-      <c r="L61" s="154"/>
-      <c r="M61" s="155"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="195"/>
+      <c r="I61" s="195"/>
+      <c r="J61" s="195"/>
+      <c r="K61" s="196"/>
+      <c r="L61" s="153"/>
+      <c r="M61" s="154"/>
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E62" s="154"/>
-      <c r="F62" s="157"/>
-      <c r="G62" s="157"/>
-      <c r="H62" s="157"/>
-      <c r="I62" s="157"/>
-      <c r="J62" s="157"/>
-      <c r="K62" s="155"/>
-      <c r="L62" s="154"/>
-      <c r="M62" s="155"/>
+      <c r="E62" s="153"/>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="156"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="154"/>
+      <c r="L62" s="153"/>
+      <c r="M62" s="154"/>
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E63" s="154" t="s">
+      <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F63" s="157"/>
-      <c r="G63" s="162" t="str">
+      <c r="F63" s="156"/>
+      <c r="G63" s="161" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="157"/>
-      <c r="I63" s="157" t="s">
+      <c r="H63" s="156"/>
+      <c r="I63" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J63" s="161">
+      <c r="J63" s="160">
         <v>45674</v>
       </c>
-      <c r="K63" s="155"/>
-      <c r="L63" s="183" t="s">
+      <c r="K63" s="154"/>
+      <c r="L63" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="184"/>
+      <c r="M63" s="180"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E64" s="154" t="s">
+      <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F64" s="162">
+      <c r="F64" s="161">
         <v>4</v>
       </c>
-      <c r="G64" s="157"/>
-      <c r="H64" s="157"/>
-      <c r="I64" s="157"/>
-      <c r="J64" s="157"/>
-      <c r="K64" s="155"/>
-      <c r="L64" s="154"/>
-      <c r="M64" s="155"/>
+      <c r="G64" s="156"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="156"/>
+      <c r="J64" s="156"/>
+      <c r="K64" s="154"/>
+      <c r="L64" s="153"/>
+      <c r="M64" s="154"/>
     </row>
     <row r="65" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E65" s="154"/>
-      <c r="F65" s="157"/>
-      <c r="G65" s="157"/>
-      <c r="H65" s="157"/>
-      <c r="I65" s="157"/>
-      <c r="J65" s="157"/>
-      <c r="K65" s="155"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="184"/>
+      <c r="E65" s="153"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="154"/>
+      <c r="L65" s="181"/>
+      <c r="M65" s="180"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E66" s="154" t="s">
+      <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="157"/>
-      <c r="G66" s="157"/>
-      <c r="H66" s="157"/>
-      <c r="I66" s="157"/>
-      <c r="J66" s="163">
+      <c r="F66" s="156"/>
+      <c r="G66" s="156"/>
+      <c r="H66" s="156"/>
+      <c r="I66" s="156"/>
+      <c r="J66" s="162">
         <f>J8</f>
-        <v>24394.945350000002</v>
-      </c>
-      <c r="K66" s="155"/>
-      <c r="L66" s="154"/>
-      <c r="M66" s="155"/>
+        <v>23542.564974999998</v>
+      </c>
+      <c r="K66" s="154"/>
+      <c r="L66" s="153"/>
+      <c r="M66" s="154"/>
     </row>
     <row r="67" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E67" s="164" t="s">
+      <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F67" s="157"/>
-      <c r="G67" s="157"/>
-      <c r="H67" s="157"/>
-      <c r="I67" s="157"/>
-      <c r="J67" s="163">
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="162">
         <f>K8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="155"/>
-      <c r="L67" s="154"/>
-      <c r="M67" s="155"/>
+        <v>25463.047424999997</v>
+      </c>
+      <c r="K67" s="154"/>
+      <c r="L67" s="153"/>
+      <c r="M67" s="154"/>
     </row>
     <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="164" t="s">
+      <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="F68" s="157"/>
-      <c r="G68" s="157"/>
-      <c r="H68" s="157"/>
-      <c r="I68" s="157"/>
-      <c r="J68" s="163">
+      <c r="F68" s="156"/>
+      <c r="G68" s="156"/>
+      <c r="H68" s="156"/>
+      <c r="I68" s="156"/>
+      <c r="J68" s="162">
         <f>G29+H29</f>
         <v>0</v>
       </c>
-      <c r="K68" s="155"/>
-      <c r="L68" s="154"/>
-      <c r="M68" s="155"/>
+      <c r="K68" s="154"/>
+      <c r="L68" s="153"/>
+      <c r="M68" s="154"/>
     </row>
     <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="164"/>
-      <c r="F69" s="157"/>
-      <c r="G69" s="157"/>
-      <c r="H69" s="157"/>
-      <c r="I69" s="157"/>
-      <c r="J69" s="163"/>
-      <c r="K69" s="155"/>
-      <c r="L69" s="154"/>
-      <c r="M69" s="155"/>
+      <c r="E69" s="163"/>
+      <c r="F69" s="156"/>
+      <c r="G69" s="156"/>
+      <c r="H69" s="156"/>
+      <c r="I69" s="156"/>
+      <c r="J69" s="162"/>
+      <c r="K69" s="154"/>
+      <c r="L69" s="153"/>
+      <c r="M69" s="154"/>
     </row>
     <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="164"/>
-      <c r="F70" s="157"/>
-      <c r="G70" s="157"/>
-      <c r="H70" s="157"/>
-      <c r="I70" s="157"/>
-      <c r="J70" s="163"/>
-      <c r="K70" s="155"/>
-      <c r="L70" s="154"/>
-      <c r="M70" s="155"/>
+      <c r="E70" s="163"/>
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="156"/>
+      <c r="I70" s="156"/>
+      <c r="J70" s="162"/>
+      <c r="K70" s="154"/>
+      <c r="L70" s="153"/>
+      <c r="M70" s="154"/>
     </row>
     <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="F71" s="157"/>
-      <c r="G71" s="157"/>
-      <c r="H71" s="157"/>
-      <c r="I71" s="157"/>
-      <c r="J71" s="163"/>
-      <c r="K71" s="155"/>
-      <c r="L71" s="154"/>
-      <c r="M71" s="155"/>
+      <c r="F71" s="156"/>
+      <c r="G71" s="156"/>
+      <c r="H71" s="156"/>
+      <c r="I71" s="156"/>
+      <c r="J71" s="162"/>
+      <c r="K71" s="154"/>
+      <c r="L71" s="153"/>
+      <c r="M71" s="154"/>
     </row>
     <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E72" s="164"/>
-      <c r="F72" s="157"/>
-      <c r="G72" s="157"/>
-      <c r="H72" s="157"/>
-      <c r="I72" s="157"/>
-      <c r="J72" s="163"/>
-      <c r="K72" s="155"/>
-      <c r="L72" s="154"/>
-      <c r="M72" s="155"/>
+      <c r="E72" s="163"/>
+      <c r="F72" s="156"/>
+      <c r="G72" s="156"/>
+      <c r="H72" s="156"/>
+      <c r="I72" s="156"/>
+      <c r="J72" s="162"/>
+      <c r="K72" s="154"/>
+      <c r="L72" s="153"/>
+      <c r="M72" s="154"/>
     </row>
     <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E73" s="154"/>
-      <c r="F73" s="157"/>
-      <c r="G73" s="157"/>
-      <c r="H73" s="157"/>
-      <c r="I73" s="157"/>
-      <c r="J73" s="157"/>
-      <c r="K73" s="155"/>
-      <c r="L73" s="154"/>
-      <c r="M73" s="155"/>
+      <c r="E73" s="153"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="156"/>
+      <c r="H73" s="156"/>
+      <c r="I73" s="156"/>
+      <c r="J73" s="156"/>
+      <c r="K73" s="154"/>
+      <c r="L73" s="153"/>
+      <c r="M73" s="154"/>
     </row>
     <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E74" s="154"/>
-      <c r="F74" s="157"/>
-      <c r="G74" s="157"/>
-      <c r="H74" s="157"/>
-      <c r="I74" s="157"/>
-      <c r="J74" s="157"/>
-      <c r="K74" s="155"/>
-      <c r="L74" s="154"/>
-      <c r="M74" s="155"/>
+      <c r="E74" s="153"/>
+      <c r="F74" s="156"/>
+      <c r="G74" s="156"/>
+      <c r="H74" s="156"/>
+      <c r="I74" s="156"/>
+      <c r="J74" s="156"/>
+      <c r="K74" s="154"/>
+      <c r="L74" s="153"/>
+      <c r="M74" s="154"/>
     </row>
     <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E75" s="154"/>
-      <c r="F75" s="157"/>
-      <c r="G75" s="157"/>
-      <c r="H75" s="157"/>
-      <c r="I75" s="157"/>
-      <c r="J75" s="157"/>
-      <c r="K75" s="155"/>
-      <c r="L75" s="165"/>
-      <c r="M75" s="166"/>
+      <c r="E75" s="153"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
+      <c r="H75" s="156"/>
+      <c r="I75" s="156"/>
+      <c r="J75" s="156"/>
+      <c r="K75" s="154"/>
+      <c r="L75" s="164"/>
+      <c r="M75" s="165"/>
     </row>
     <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="192" t="s">
+      <c r="E76" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="193"/>
-      <c r="G76" s="193"/>
-      <c r="H76" s="193"/>
-      <c r="I76" s="193"/>
-      <c r="J76" s="194">
+      <c r="F76" s="198"/>
+      <c r="G76" s="198"/>
+      <c r="H76" s="198"/>
+      <c r="I76" s="198"/>
+      <c r="J76" s="199">
         <f>SUM(J66:J75)</f>
-        <v>24394.945350000002</v>
-      </c>
-      <c r="K76" s="195"/>
-      <c r="L76" s="167"/>
-      <c r="M76" s="168"/>
+        <v>49005.612399999998</v>
+      </c>
+      <c r="K76" s="192"/>
+      <c r="L76" s="166"/>
+      <c r="M76" s="167"/>
     </row>
     <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="196" t="s">
+      <c r="E83" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="197"/>
-      <c r="G83" s="197"/>
-      <c r="H83" s="197"/>
-      <c r="I83" s="197"/>
-      <c r="J83" s="197"/>
-      <c r="K83" s="195"/>
-      <c r="L83" s="152"/>
-      <c r="M83" s="153"/>
+      <c r="F83" s="191"/>
+      <c r="G83" s="191"/>
+      <c r="H83" s="191"/>
+      <c r="I83" s="191"/>
+      <c r="J83" s="191"/>
+      <c r="K83" s="192"/>
+      <c r="L83" s="151"/>
+      <c r="M83" s="152"/>
     </row>
     <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="198" t="s">
+      <c r="E84" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="197"/>
-      <c r="G84" s="197"/>
-      <c r="H84" s="197"/>
-      <c r="I84" s="197"/>
-      <c r="J84" s="197"/>
-      <c r="K84" s="195"/>
-      <c r="L84" s="154"/>
-      <c r="M84" s="155"/>
+      <c r="F84" s="191"/>
+      <c r="G84" s="191"/>
+      <c r="H84" s="191"/>
+      <c r="I84" s="191"/>
+      <c r="J84" s="191"/>
+      <c r="K84" s="192"/>
+      <c r="L84" s="153"/>
+      <c r="M84" s="154"/>
     </row>
     <row r="85" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E85" s="152"/>
-      <c r="F85" s="156"/>
-      <c r="G85" s="156"/>
-      <c r="H85" s="156"/>
-      <c r="I85" s="157"/>
-      <c r="J85" s="157">
+      <c r="E85" s="151"/>
+      <c r="F85" s="155"/>
+      <c r="G85" s="155"/>
+      <c r="H85" s="155"/>
+      <c r="I85" s="156"/>
+      <c r="J85" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K85" s="155"/>
-      <c r="L85" s="154"/>
-      <c r="M85" s="155"/>
+      <c r="K85" s="154"/>
+      <c r="L85" s="153"/>
+      <c r="M85" s="154"/>
     </row>
     <row r="86" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E86" s="154" t="s">
+      <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F86" s="157"/>
-      <c r="G86" s="157"/>
-      <c r="H86" s="157"/>
-      <c r="I86" s="157"/>
-      <c r="J86" s="157"/>
-      <c r="K86" s="155"/>
-      <c r="L86" s="154"/>
-      <c r="M86" s="155"/>
+      <c r="F86" s="156"/>
+      <c r="G86" s="156"/>
+      <c r="H86" s="156"/>
+      <c r="I86" s="156"/>
+      <c r="J86" s="156"/>
+      <c r="K86" s="154"/>
+      <c r="L86" s="153"/>
+      <c r="M86" s="154"/>
     </row>
     <row r="87" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E87" s="158"/>
-      <c r="F87" s="159"/>
-      <c r="G87" s="159"/>
-      <c r="H87" s="159"/>
-      <c r="I87" s="159"/>
-      <c r="J87" s="159"/>
-      <c r="K87" s="160"/>
-      <c r="L87" s="154"/>
-      <c r="M87" s="155"/>
+      <c r="E87" s="157"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="158"/>
+      <c r="H87" s="158"/>
+      <c r="I87" s="158"/>
+      <c r="J87" s="158"/>
+      <c r="K87" s="159"/>
+      <c r="L87" s="153"/>
+      <c r="M87" s="154"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="199" t="s">
+      <c r="E88" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="200"/>
-      <c r="G88" s="200"/>
-      <c r="H88" s="200"/>
-      <c r="I88" s="200"/>
-      <c r="J88" s="200"/>
-      <c r="K88" s="201"/>
-      <c r="L88" s="154"/>
-      <c r="M88" s="155"/>
+      <c r="F88" s="195"/>
+      <c r="G88" s="195"/>
+      <c r="H88" s="195"/>
+      <c r="I88" s="195"/>
+      <c r="J88" s="195"/>
+      <c r="K88" s="196"/>
+      <c r="L88" s="153"/>
+      <c r="M88" s="154"/>
     </row>
     <row r="89" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E89" s="154"/>
-      <c r="F89" s="157"/>
-      <c r="G89" s="157"/>
-      <c r="H89" s="157"/>
-      <c r="I89" s="157"/>
-      <c r="J89" s="157"/>
-      <c r="K89" s="155"/>
-      <c r="L89" s="154"/>
-      <c r="M89" s="155"/>
+      <c r="E89" s="153"/>
+      <c r="F89" s="156"/>
+      <c r="G89" s="156"/>
+      <c r="H89" s="156"/>
+      <c r="I89" s="156"/>
+      <c r="J89" s="156"/>
+      <c r="K89" s="154"/>
+      <c r="L89" s="153"/>
+      <c r="M89" s="154"/>
     </row>
     <row r="90" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E90" s="154" t="s">
+      <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F90" s="157"/>
-      <c r="G90" s="162" t="str">
+      <c r="F90" s="156"/>
+      <c r="G90" s="161" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="157"/>
-      <c r="I90" s="157" t="s">
+      <c r="H90" s="156"/>
+      <c r="I90" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="161">
+      <c r="J90" s="160">
         <v>45674</v>
       </c>
-      <c r="K90" s="155"/>
-      <c r="L90" s="183" t="s">
+      <c r="K90" s="154"/>
+      <c r="L90" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="184"/>
+      <c r="M90" s="180"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E91" s="154" t="s">
+      <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F91" s="162">
+      <c r="F91" s="161">
         <v>6</v>
       </c>
-      <c r="G91" s="157"/>
-      <c r="H91" s="157"/>
-      <c r="I91" s="157"/>
-      <c r="J91" s="157"/>
-      <c r="K91" s="155"/>
-      <c r="L91" s="154"/>
-      <c r="M91" s="155"/>
+      <c r="G91" s="156"/>
+      <c r="H91" s="156"/>
+      <c r="I91" s="156"/>
+      <c r="J91" s="156"/>
+      <c r="K91" s="154"/>
+      <c r="L91" s="153"/>
+      <c r="M91" s="154"/>
     </row>
     <row r="92" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E92" s="154"/>
-      <c r="F92" s="157"/>
-      <c r="G92" s="157"/>
-      <c r="H92" s="157"/>
-      <c r="I92" s="157"/>
-      <c r="J92" s="157"/>
-      <c r="K92" s="155"/>
-      <c r="L92" s="185"/>
-      <c r="M92" s="184"/>
+      <c r="E92" s="153"/>
+      <c r="F92" s="156"/>
+      <c r="G92" s="156"/>
+      <c r="H92" s="156"/>
+      <c r="I92" s="156"/>
+      <c r="J92" s="156"/>
+      <c r="K92" s="154"/>
+      <c r="L92" s="181"/>
+      <c r="M92" s="180"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E93" s="154" t="s">
+      <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F93" s="157"/>
-      <c r="G93" s="157"/>
-      <c r="H93" s="157"/>
-      <c r="I93" s="157"/>
-      <c r="J93" s="163">
+      <c r="F93" s="156"/>
+      <c r="G93" s="156"/>
+      <c r="H93" s="156"/>
+      <c r="I93" s="156"/>
+      <c r="J93" s="162">
         <f>J10</f>
-        <v>20640.604608000001</v>
-      </c>
-      <c r="K93" s="155"/>
-      <c r="L93" s="154"/>
-      <c r="M93" s="155"/>
+        <v>19919.404127999998</v>
+      </c>
+      <c r="K93" s="154"/>
+      <c r="L93" s="153"/>
+      <c r="M93" s="154"/>
     </row>
     <row r="94" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E94" s="164" t="s">
+      <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="157"/>
-      <c r="G94" s="157"/>
-      <c r="H94" s="157"/>
-      <c r="I94" s="157"/>
-      <c r="J94" s="163">
+      <c r="F94" s="156"/>
+      <c r="G94" s="156"/>
+      <c r="H94" s="156"/>
+      <c r="I94" s="156"/>
+      <c r="J94" s="162">
         <f>K10</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="155"/>
-      <c r="L94" s="154"/>
-      <c r="M94" s="155"/>
+        <v>21544.327583999999</v>
+      </c>
+      <c r="K94" s="154"/>
+      <c r="L94" s="153"/>
+      <c r="M94" s="154"/>
     </row>
     <row r="95" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E95" s="164" t="s">
+      <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="157"/>
-      <c r="G95" s="157"/>
-      <c r="H95" s="157"/>
-      <c r="I95" s="157"/>
-      <c r="J95" s="163">
+      <c r="F95" s="156"/>
+      <c r="G95" s="156"/>
+      <c r="H95" s="156"/>
+      <c r="I95" s="156"/>
+      <c r="J95" s="162">
         <v>23.89</v>
       </c>
-      <c r="K95" s="155"/>
-      <c r="L95" s="154"/>
-      <c r="M95" s="155"/>
+      <c r="K95" s="154"/>
+      <c r="L95" s="153"/>
+      <c r="M95" s="154"/>
     </row>
     <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="164"/>
-      <c r="F96" s="157"/>
-      <c r="G96" s="157"/>
-      <c r="H96" s="157"/>
-      <c r="I96" s="157"/>
-      <c r="J96" s="163"/>
-      <c r="K96" s="155"/>
-      <c r="L96" s="154"/>
-      <c r="M96" s="155"/>
+      <c r="E96" s="163"/>
+      <c r="F96" s="156"/>
+      <c r="G96" s="156"/>
+      <c r="H96" s="156"/>
+      <c r="I96" s="156"/>
+      <c r="J96" s="162"/>
+      <c r="K96" s="154"/>
+      <c r="L96" s="153"/>
+      <c r="M96" s="154"/>
     </row>
     <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E97" s="164"/>
-      <c r="F97" s="157"/>
-      <c r="G97" s="157"/>
-      <c r="H97" s="157"/>
-      <c r="I97" s="157"/>
-      <c r="J97" s="163"/>
-      <c r="K97" s="155"/>
-      <c r="L97" s="154"/>
-      <c r="M97" s="155"/>
+      <c r="E97" s="163"/>
+      <c r="F97" s="156"/>
+      <c r="G97" s="156"/>
+      <c r="H97" s="156"/>
+      <c r="I97" s="156"/>
+      <c r="J97" s="162"/>
+      <c r="K97" s="154"/>
+      <c r="L97" s="153"/>
+      <c r="M97" s="154"/>
     </row>
     <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F98" s="157"/>
-      <c r="G98" s="157"/>
-      <c r="H98" s="157"/>
-      <c r="I98" s="157"/>
-      <c r="J98" s="163"/>
-      <c r="K98" s="155"/>
-      <c r="L98" s="154"/>
-      <c r="M98" s="155"/>
+      <c r="F98" s="156"/>
+      <c r="G98" s="156"/>
+      <c r="H98" s="156"/>
+      <c r="I98" s="156"/>
+      <c r="J98" s="162"/>
+      <c r="K98" s="154"/>
+      <c r="L98" s="153"/>
+      <c r="M98" s="154"/>
     </row>
     <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E99" s="164"/>
-      <c r="F99" s="157"/>
-      <c r="G99" s="157"/>
-      <c r="H99" s="157"/>
-      <c r="I99" s="157"/>
-      <c r="J99" s="163"/>
-      <c r="K99" s="155"/>
-      <c r="L99" s="154"/>
-      <c r="M99" s="155"/>
+      <c r="E99" s="163"/>
+      <c r="F99" s="156"/>
+      <c r="G99" s="156"/>
+      <c r="H99" s="156"/>
+      <c r="I99" s="156"/>
+      <c r="J99" s="162"/>
+      <c r="K99" s="154"/>
+      <c r="L99" s="153"/>
+      <c r="M99" s="154"/>
     </row>
     <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E100" s="154"/>
-      <c r="F100" s="157"/>
-      <c r="G100" s="157"/>
-      <c r="H100" s="157"/>
-      <c r="I100" s="157"/>
-      <c r="J100" s="157"/>
-      <c r="K100" s="155"/>
-      <c r="L100" s="154"/>
-      <c r="M100" s="155"/>
+      <c r="E100" s="153"/>
+      <c r="F100" s="156"/>
+      <c r="G100" s="156"/>
+      <c r="H100" s="156"/>
+      <c r="I100" s="156"/>
+      <c r="J100" s="156"/>
+      <c r="K100" s="154"/>
+      <c r="L100" s="153"/>
+      <c r="M100" s="154"/>
     </row>
     <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E101" s="154"/>
-      <c r="F101" s="157"/>
-      <c r="G101" s="157"/>
-      <c r="H101" s="157"/>
-      <c r="I101" s="157"/>
-      <c r="J101" s="157"/>
-      <c r="K101" s="155"/>
-      <c r="L101" s="154"/>
-      <c r="M101" s="155"/>
+      <c r="E101" s="153"/>
+      <c r="F101" s="156"/>
+      <c r="G101" s="156"/>
+      <c r="H101" s="156"/>
+      <c r="I101" s="156"/>
+      <c r="J101" s="156"/>
+      <c r="K101" s="154"/>
+      <c r="L101" s="153"/>
+      <c r="M101" s="154"/>
     </row>
     <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="154"/>
-      <c r="F102" s="157"/>
-      <c r="G102" s="157"/>
-      <c r="H102" s="157"/>
-      <c r="I102" s="157"/>
-      <c r="J102" s="157"/>
-      <c r="K102" s="155"/>
-      <c r="L102" s="165"/>
-      <c r="M102" s="166"/>
+      <c r="E102" s="153"/>
+      <c r="F102" s="156"/>
+      <c r="G102" s="156"/>
+      <c r="H102" s="156"/>
+      <c r="I102" s="156"/>
+      <c r="J102" s="156"/>
+      <c r="K102" s="154"/>
+      <c r="L102" s="164"/>
+      <c r="M102" s="165"/>
     </row>
     <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="192" t="s">
+      <c r="E103" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="193"/>
-      <c r="G103" s="193"/>
-      <c r="H103" s="193"/>
-      <c r="I103" s="193"/>
-      <c r="J103" s="194">
+      <c r="F103" s="198"/>
+      <c r="G103" s="198"/>
+      <c r="H103" s="198"/>
+      <c r="I103" s="198"/>
+      <c r="J103" s="199">
         <f>SUM(J93:J102)</f>
-        <v>20664.494608000001</v>
-      </c>
-      <c r="K103" s="195"/>
-      <c r="L103" s="167"/>
-      <c r="M103" s="168"/>
+        <v>41487.621711999993</v>
+      </c>
+      <c r="K103" s="192"/>
+      <c r="L103" s="166"/>
+      <c r="M103" s="167"/>
     </row>
     <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="196" t="s">
+      <c r="E108" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="197"/>
-      <c r="G108" s="197"/>
-      <c r="H108" s="197"/>
-      <c r="I108" s="197"/>
-      <c r="J108" s="197"/>
-      <c r="K108" s="195"/>
-      <c r="L108" s="152"/>
-      <c r="M108" s="153"/>
+      <c r="F108" s="191"/>
+      <c r="G108" s="191"/>
+      <c r="H108" s="191"/>
+      <c r="I108" s="191"/>
+      <c r="J108" s="191"/>
+      <c r="K108" s="192"/>
+      <c r="L108" s="151"/>
+      <c r="M108" s="152"/>
     </row>
     <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="198" t="s">
+      <c r="E109" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="197"/>
-      <c r="G109" s="197"/>
-      <c r="H109" s="197"/>
-      <c r="I109" s="197"/>
-      <c r="J109" s="197"/>
-      <c r="K109" s="195"/>
-      <c r="L109" s="154"/>
-      <c r="M109" s="155"/>
+      <c r="F109" s="191"/>
+      <c r="G109" s="191"/>
+      <c r="H109" s="191"/>
+      <c r="I109" s="191"/>
+      <c r="J109" s="191"/>
+      <c r="K109" s="192"/>
+      <c r="L109" s="153"/>
+      <c r="M109" s="154"/>
     </row>
     <row r="110" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E110" s="152"/>
-      <c r="F110" s="156"/>
-      <c r="G110" s="156"/>
-      <c r="H110" s="156"/>
-      <c r="I110" s="157"/>
-      <c r="J110" s="157">
+      <c r="E110" s="151"/>
+      <c r="F110" s="155"/>
+      <c r="G110" s="155"/>
+      <c r="H110" s="155"/>
+      <c r="I110" s="156"/>
+      <c r="J110" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K110" s="155"/>
-      <c r="L110" s="154"/>
-      <c r="M110" s="155"/>
+      <c r="K110" s="154"/>
+      <c r="L110" s="153"/>
+      <c r="M110" s="154"/>
     </row>
     <row r="111" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E111" s="154" t="s">
+      <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F111" s="157"/>
-      <c r="G111" s="157"/>
-      <c r="H111" s="157"/>
-      <c r="I111" s="157"/>
-      <c r="J111" s="157"/>
-      <c r="K111" s="155"/>
-      <c r="L111" s="154"/>
-      <c r="M111" s="155"/>
+      <c r="F111" s="156"/>
+      <c r="G111" s="156"/>
+      <c r="H111" s="156"/>
+      <c r="I111" s="156"/>
+      <c r="J111" s="156"/>
+      <c r="K111" s="154"/>
+      <c r="L111" s="153"/>
+      <c r="M111" s="154"/>
     </row>
     <row r="112" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E112" s="158"/>
-      <c r="F112" s="159"/>
-      <c r="G112" s="159"/>
-      <c r="H112" s="159"/>
-      <c r="I112" s="159"/>
-      <c r="J112" s="159"/>
-      <c r="K112" s="160"/>
-      <c r="L112" s="154"/>
-      <c r="M112" s="155"/>
+      <c r="E112" s="157"/>
+      <c r="F112" s="158"/>
+      <c r="G112" s="158"/>
+      <c r="H112" s="158"/>
+      <c r="I112" s="158"/>
+      <c r="J112" s="158"/>
+      <c r="K112" s="159"/>
+      <c r="L112" s="153"/>
+      <c r="M112" s="154"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="199" t="s">
+      <c r="E113" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="200"/>
-      <c r="G113" s="200"/>
-      <c r="H113" s="200"/>
-      <c r="I113" s="200"/>
-      <c r="J113" s="200"/>
-      <c r="K113" s="201"/>
-      <c r="L113" s="154"/>
-      <c r="M113" s="155"/>
+      <c r="F113" s="195"/>
+      <c r="G113" s="195"/>
+      <c r="H113" s="195"/>
+      <c r="I113" s="195"/>
+      <c r="J113" s="195"/>
+      <c r="K113" s="196"/>
+      <c r="L113" s="153"/>
+      <c r="M113" s="154"/>
     </row>
     <row r="114" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E114" s="154"/>
-      <c r="F114" s="157"/>
-      <c r="G114" s="157"/>
-      <c r="H114" s="157"/>
-      <c r="I114" s="157"/>
-      <c r="J114" s="157"/>
-      <c r="K114" s="155"/>
-      <c r="L114" s="154"/>
-      <c r="M114" s="155"/>
+      <c r="E114" s="153"/>
+      <c r="F114" s="156"/>
+      <c r="G114" s="156"/>
+      <c r="H114" s="156"/>
+      <c r="I114" s="156"/>
+      <c r="J114" s="156"/>
+      <c r="K114" s="154"/>
+      <c r="L114" s="153"/>
+      <c r="M114" s="154"/>
     </row>
     <row r="115" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E115" s="154" t="s">
+      <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F115" s="157"/>
-      <c r="G115" s="162" t="str">
+      <c r="F115" s="156"/>
+      <c r="G115" s="161" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="157"/>
-      <c r="I115" s="157" t="s">
+      <c r="H115" s="156"/>
+      <c r="I115" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J115" s="161">
+      <c r="J115" s="160">
         <v>45674</v>
       </c>
-      <c r="K115" s="155"/>
-      <c r="L115" s="183" t="s">
+      <c r="K115" s="154"/>
+      <c r="L115" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="184"/>
+      <c r="M115" s="180"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E116" s="154" t="s">
+      <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F116" s="162">
+      <c r="F116" s="161">
         <v>1</v>
       </c>
-      <c r="G116" s="157"/>
-      <c r="H116" s="157"/>
-      <c r="I116" s="157"/>
-      <c r="J116" s="157"/>
-      <c r="K116" s="155"/>
-      <c r="L116" s="154"/>
-      <c r="M116" s="155"/>
+      <c r="G116" s="156"/>
+      <c r="H116" s="156"/>
+      <c r="I116" s="156"/>
+      <c r="J116" s="156"/>
+      <c r="K116" s="154"/>
+      <c r="L116" s="153"/>
+      <c r="M116" s="154"/>
     </row>
     <row r="117" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E117" s="154"/>
-      <c r="F117" s="157"/>
-      <c r="G117" s="157"/>
-      <c r="H117" s="157"/>
-      <c r="I117" s="157"/>
-      <c r="J117" s="157"/>
-      <c r="K117" s="155"/>
-      <c r="L117" s="185"/>
-      <c r="M117" s="184"/>
+      <c r="E117" s="153"/>
+      <c r="F117" s="156"/>
+      <c r="G117" s="156"/>
+      <c r="H117" s="156"/>
+      <c r="I117" s="156"/>
+      <c r="J117" s="156"/>
+      <c r="K117" s="154"/>
+      <c r="L117" s="181"/>
+      <c r="M117" s="180"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E118" s="154" t="s">
+      <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="157"/>
-      <c r="G118" s="157"/>
-      <c r="H118" s="157"/>
-      <c r="I118" s="157"/>
-      <c r="J118" s="163">
+      <c r="F118" s="156"/>
+      <c r="G118" s="156"/>
+      <c r="H118" s="156"/>
+      <c r="I118" s="156"/>
+      <c r="J118" s="162">
         <f>J5</f>
-        <v>22823.745480000005</v>
-      </c>
-      <c r="K118" s="155"/>
-      <c r="L118" s="154"/>
-      <c r="M118" s="155"/>
+        <v>22026.264180000002</v>
+      </c>
+      <c r="K118" s="154"/>
+      <c r="L118" s="153"/>
+      <c r="M118" s="154"/>
     </row>
     <row r="119" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E119" s="164" t="s">
+      <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F119" s="157"/>
-      <c r="G119" s="157"/>
-      <c r="H119" s="157"/>
-      <c r="I119" s="157"/>
-      <c r="J119" s="163">
+      <c r="F119" s="156"/>
+      <c r="G119" s="156"/>
+      <c r="H119" s="156"/>
+      <c r="I119" s="156"/>
+      <c r="J119" s="162">
         <f>K5</f>
-        <v>0</v>
-      </c>
-      <c r="K119" s="155"/>
-      <c r="L119" s="154"/>
-      <c r="M119" s="155"/>
+        <v>23823.054539999997</v>
+      </c>
+      <c r="K119" s="154"/>
+      <c r="L119" s="153"/>
+      <c r="M119" s="154"/>
     </row>
     <row r="120" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E120" s="164" t="s">
+      <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="157"/>
-      <c r="G120" s="157"/>
-      <c r="H120" s="157"/>
-      <c r="I120" s="157"/>
-      <c r="J120" s="163">
+      <c r="F120" s="156"/>
+      <c r="G120" s="156"/>
+      <c r="H120" s="156"/>
+      <c r="I120" s="156"/>
+      <c r="J120" s="162">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="155"/>
-      <c r="L120" s="154"/>
-      <c r="M120" s="155"/>
+      <c r="K120" s="154"/>
+      <c r="L120" s="153"/>
+      <c r="M120" s="154"/>
     </row>
     <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E121" s="164"/>
-      <c r="F121" s="157"/>
-      <c r="G121" s="157"/>
-      <c r="H121" s="157"/>
-      <c r="I121" s="157"/>
-      <c r="J121" s="163"/>
-      <c r="K121" s="155"/>
-      <c r="L121" s="154"/>
-      <c r="M121" s="155"/>
+      <c r="E121" s="163"/>
+      <c r="F121" s="156"/>
+      <c r="G121" s="156"/>
+      <c r="H121" s="156"/>
+      <c r="I121" s="156"/>
+      <c r="J121" s="162"/>
+      <c r="K121" s="154"/>
+      <c r="L121" s="153"/>
+      <c r="M121" s="154"/>
     </row>
     <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E122" s="164"/>
-      <c r="F122" s="157"/>
-      <c r="G122" s="157"/>
-      <c r="H122" s="157"/>
-      <c r="I122" s="157"/>
-      <c r="J122" s="163"/>
-      <c r="K122" s="155"/>
-      <c r="L122" s="154"/>
-      <c r="M122" s="155"/>
+      <c r="E122" s="163"/>
+      <c r="F122" s="156"/>
+      <c r="G122" s="156"/>
+      <c r="H122" s="156"/>
+      <c r="I122" s="156"/>
+      <c r="J122" s="162"/>
+      <c r="K122" s="154"/>
+      <c r="L122" s="153"/>
+      <c r="M122" s="154"/>
     </row>
     <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F123" s="157"/>
-      <c r="G123" s="157"/>
-      <c r="H123" s="157"/>
-      <c r="I123" s="157"/>
-      <c r="J123" s="163"/>
-      <c r="K123" s="155"/>
-      <c r="L123" s="154"/>
-      <c r="M123" s="155"/>
+      <c r="F123" s="156"/>
+      <c r="G123" s="156"/>
+      <c r="H123" s="156"/>
+      <c r="I123" s="156"/>
+      <c r="J123" s="162"/>
+      <c r="K123" s="154"/>
+      <c r="L123" s="153"/>
+      <c r="M123" s="154"/>
     </row>
     <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E124" s="164"/>
-      <c r="F124" s="157"/>
-      <c r="G124" s="157"/>
-      <c r="H124" s="157"/>
-      <c r="I124" s="157"/>
-      <c r="J124" s="163"/>
-      <c r="K124" s="155"/>
-      <c r="L124" s="154"/>
-      <c r="M124" s="155"/>
+      <c r="E124" s="163"/>
+      <c r="F124" s="156"/>
+      <c r="G124" s="156"/>
+      <c r="H124" s="156"/>
+      <c r="I124" s="156"/>
+      <c r="J124" s="162"/>
+      <c r="K124" s="154"/>
+      <c r="L124" s="153"/>
+      <c r="M124" s="154"/>
     </row>
     <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E125" s="154"/>
-      <c r="F125" s="157"/>
-      <c r="G125" s="157"/>
-      <c r="H125" s="157"/>
-      <c r="I125" s="157"/>
-      <c r="J125" s="157"/>
-      <c r="K125" s="155"/>
-      <c r="L125" s="154"/>
-      <c r="M125" s="155"/>
+      <c r="E125" s="153"/>
+      <c r="F125" s="156"/>
+      <c r="G125" s="156"/>
+      <c r="H125" s="156"/>
+      <c r="I125" s="156"/>
+      <c r="J125" s="156"/>
+      <c r="K125" s="154"/>
+      <c r="L125" s="153"/>
+      <c r="M125" s="154"/>
     </row>
     <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E126" s="154"/>
-      <c r="F126" s="157"/>
-      <c r="G126" s="157"/>
-      <c r="H126" s="157"/>
-      <c r="I126" s="157"/>
-      <c r="J126" s="157"/>
-      <c r="K126" s="155"/>
-      <c r="L126" s="154"/>
-      <c r="M126" s="155"/>
+      <c r="E126" s="153"/>
+      <c r="F126" s="156"/>
+      <c r="G126" s="156"/>
+      <c r="H126" s="156"/>
+      <c r="I126" s="156"/>
+      <c r="J126" s="156"/>
+      <c r="K126" s="154"/>
+      <c r="L126" s="153"/>
+      <c r="M126" s="154"/>
     </row>
     <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E127" s="154"/>
-      <c r="F127" s="157"/>
-      <c r="G127" s="157"/>
-      <c r="H127" s="157"/>
-      <c r="I127" s="157"/>
-      <c r="J127" s="157"/>
-      <c r="K127" s="155"/>
-      <c r="L127" s="165"/>
-      <c r="M127" s="166"/>
+      <c r="E127" s="153"/>
+      <c r="F127" s="156"/>
+      <c r="G127" s="156"/>
+      <c r="H127" s="156"/>
+      <c r="I127" s="156"/>
+      <c r="J127" s="156"/>
+      <c r="K127" s="154"/>
+      <c r="L127" s="164"/>
+      <c r="M127" s="165"/>
     </row>
     <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="192" t="s">
+      <c r="E128" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="193"/>
-      <c r="G128" s="193"/>
-      <c r="H128" s="193"/>
-      <c r="I128" s="193"/>
-      <c r="J128" s="194">
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="198"/>
+      <c r="I128" s="198"/>
+      <c r="J128" s="199">
         <f>SUM(J118:J127)</f>
-        <v>22771.405480000005</v>
-      </c>
-      <c r="K128" s="195"/>
-      <c r="L128" s="167"/>
-      <c r="M128" s="168"/>
+        <v>45796.978719999999</v>
+      </c>
+      <c r="K128" s="192"/>
+      <c r="L128" s="166"/>
+      <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -4713,415 +4746,415 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="112" t="s">
+      <c r="C1" s="111" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="113"/>
+      <c r="D1" s="112"/>
       <c r="F1" t="s">
         <v>42</v>
       </c>
       <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="143">
+      <c r="H1" s="142">
         <v>10296.959999999999</v>
       </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="115"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="114"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="111" t="s">
+      <c r="C3" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="111" t="s">
+      <c r="E3" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="111" t="s">
+      <c r="F3" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="111" t="s">
+      <c r="G3" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="118" t="s">
+      <c r="H3" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
       <c r="K3" s="5"/>
-      <c r="M3" s="119"/>
+      <c r="M3" s="118"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="117"/>
-      <c r="C4" s="111" t="s">
+      <c r="B4" s="116"/>
+      <c r="C4" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="H4" s="120">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="H4" s="119">
         <f>H1</f>
         <v>10296.959999999999</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="117">
+      <c r="B5" s="116">
         <v>1</v>
       </c>
       <c r="C5">
         <v>7735</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="112">
         <f>C5+82</f>
         <v>7817</v>
       </c>
-      <c r="E5" s="117">
+      <c r="E5" s="116">
         <f>D5-C5</f>
         <v>82</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="116">
         <f>E5*100/D14</f>
         <v>13.7123745819398</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="121">
+      <c r="H5" s="120">
         <f>H4*(F5/100)</f>
         <v>1411.9577257525084</v>
       </c>
-      <c r="I5" s="117"/>
+      <c r="I5" s="116"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="123"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="122"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="117">
+      <c r="B6" s="116">
         <v>2</v>
       </c>
       <c r="C6">
         <v>7076</v>
       </c>
-      <c r="D6" s="113">
+      <c r="D6" s="112">
         <f>C6+98</f>
         <v>7174</v>
       </c>
-      <c r="E6" s="117">
+      <c r="E6" s="116">
         <f>D6-C6</f>
         <v>98</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="116">
         <f>E6*100/D14</f>
         <v>16.387959866220736</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="121">
+      <c r="H6" s="120">
         <f>H4*(F6/100)</f>
         <v>1687.4616722408025</v>
       </c>
-      <c r="I6" s="117"/>
+      <c r="I6" s="116"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="123"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="122"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="117">
+      <c r="B7" s="116">
         <v>3</v>
       </c>
       <c r="C7">
         <v>7694</v>
       </c>
-      <c r="D7" s="113">
+      <c r="D7" s="112">
         <f>C7+97</f>
         <v>7791</v>
       </c>
-      <c r="E7" s="117">
+      <c r="E7" s="116">
         <f t="shared" ref="E7:E11" si="0">D7-C7</f>
         <v>97</v>
       </c>
-      <c r="F7" s="117">
+      <c r="F7" s="116">
         <f>E7*100/D14</f>
         <v>16.220735785953178</v>
       </c>
-      <c r="H7" s="124">
+      <c r="H7" s="123">
         <f>H4*(F7/100)</f>
         <v>1670.2426755852841</v>
       </c>
-      <c r="I7" s="111"/>
+      <c r="I7" s="110"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="123"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="122"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="117">
+      <c r="B8" s="116">
         <v>4</v>
       </c>
       <c r="C8">
         <v>9262</v>
       </c>
-      <c r="D8" s="113">
+      <c r="D8" s="112">
         <f>C8+107</f>
         <v>9369</v>
       </c>
-      <c r="E8" s="117">
+      <c r="E8" s="116">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="F8" s="117">
+      <c r="F8" s="116">
         <f>E8*100/D14</f>
         <v>17.892976588628763</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="121">
+      <c r="H8" s="120">
         <f>H4*(F8/100)</f>
         <v>1842.432642140468</v>
       </c>
-      <c r="I8" s="117"/>
+      <c r="I8" s="116"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="123"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="122"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="117">
+      <c r="B9" s="116">
         <v>5</v>
       </c>
       <c r="C9">
         <v>10635</v>
       </c>
-      <c r="D9" s="113">
+      <c r="D9" s="112">
         <f>C9+60</f>
         <v>10695</v>
       </c>
-      <c r="E9" s="117">
+      <c r="E9" s="116">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="F9" s="117">
+      <c r="F9" s="116">
         <f>E9*100/D14</f>
         <v>10.033444816053512</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="121">
+      <c r="H9" s="120">
         <f>H4*(F9/100)</f>
         <v>1033.1397993311036</v>
       </c>
-      <c r="I9" s="117"/>
+      <c r="I9" s="116"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="123"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="122"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="116">
         <v>6</v>
       </c>
       <c r="C10">
         <v>10706</v>
       </c>
-      <c r="D10" s="113">
+      <c r="D10" s="112">
         <f>C10+37+12+12</f>
         <v>10767</v>
       </c>
-      <c r="E10" s="117">
+      <c r="E10" s="116">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="F10" s="117">
+      <c r="F10" s="116">
         <f>E10*100/D14</f>
         <v>10.200668896321071</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="121">
+      <c r="H10" s="120">
         <f>H4*(F10/100)</f>
         <v>1050.358795986622</v>
       </c>
-      <c r="I10" s="117"/>
+      <c r="I10" s="116"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="123"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="122"/>
     </row>
     <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="117">
+      <c r="B11" s="116">
         <v>7</v>
       </c>
       <c r="C11">
         <v>13147</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="112">
         <f>C11+93</f>
         <v>13240</v>
       </c>
-      <c r="E11" s="117">
+      <c r="E11" s="116">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="F11" s="117">
+      <c r="F11" s="116">
         <f>E11*100/D14</f>
         <v>15.551839464882944</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="121">
+      <c r="H11" s="120">
         <f>H4*(F11/100)</f>
         <v>1601.3666889632107</v>
       </c>
-      <c r="I11" s="117"/>
+      <c r="I11" s="116"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="123"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="122"/>
     </row>
     <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="125"/>
-      <c r="C12" s="126">
+      <c r="B12" s="124"/>
+      <c r="C12" s="125">
         <f>SUM(C5:C11)</f>
         <v>66255</v>
       </c>
-      <c r="D12" s="126">
+      <c r="D12" s="125">
         <f>SUM(D5:D11)</f>
         <v>66853</v>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="126">
         <f>SUM(E5:E11)</f>
         <v>598</v>
       </c>
-      <c r="F12" s="126">
+      <c r="F12" s="125">
         <f>SUM(F5:F11)</f>
         <v>100.00000000000003</v>
       </c>
       <c r="G12" s="61"/>
-      <c r="H12" s="126">
+      <c r="H12" s="125">
         <f>SUM(H5:H11)</f>
         <v>10296.959999999999</v>
       </c>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="125"/>
-      <c r="L12" s="128"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="127"/>
     </row>
     <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="129"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
+      <c r="C13" s="128"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="130">
+      <c r="D14" s="129">
         <f>D12-C12</f>
         <v>598</v>
       </c>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="117"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="117"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
     </row>
     <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C19" s="131"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="134"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="132"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="133"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C20" s="135"/>
+      <c r="C20" s="134"/>
       <c r="E20" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="136">
+      <c r="H20" s="135">
         <f>D14</f>
         <v>598</v>
       </c>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
       <c r="K20" t="s">
         <v>100</v>
       </c>
-      <c r="M20" s="137"/>
+      <c r="M20" s="136"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C21" s="135"/>
+      <c r="C21" s="134"/>
       <c r="D21" t="s">
         <v>101</v>
       </c>
@@ -5140,29 +5173,29 @@
       <c r="K21" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="137"/>
+      <c r="M21" s="136"/>
     </row>
     <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="138"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="140"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="139"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K25" s="141" t="s">
+      <c r="K25" s="140" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G26" s="5"/>
-      <c r="K26" s="119"/>
+      <c r="K26" s="118"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I27" t="s">
@@ -5183,10 +5216,10 @@
       <c r="I28" s="5">
         <v>29829</v>
       </c>
-      <c r="J28" s="122">
+      <c r="J28" s="121">
         <v>16000</v>
       </c>
-      <c r="K28" s="123">
+      <c r="K28" s="122">
         <f t="shared" ref="K28" si="1">I28+J28</f>
         <v>45829</v>
       </c>
@@ -5208,7 +5241,7 @@
       </c>
     </row>
     <row r="33" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J33" s="119" t="s">
+      <c r="J33" s="118" t="s">
         <v>109</v>
       </c>
       <c r="K33">
@@ -5216,7 +5249,7 @@
       </c>
     </row>
     <row r="34" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K34" s="113">
+      <c r="K34" s="112">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
       </c>
@@ -5249,11 +5282,11 @@
       <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="207">
+      <c r="H1" s="205">
         <v>250000</v>
       </c>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
@@ -5317,13 +5350,13 @@
         <v>53</v>
       </c>
       <c r="K4" s="67"/>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="203" t="s">
         <v>60</v>
       </c>
       <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="203" t="s">
+      <c r="N4" s="201" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="21"/>
@@ -5352,11 +5385,11 @@
         <v>59</v>
       </c>
       <c r="K5" s="57"/>
-      <c r="L5" s="206"/>
+      <c r="L5" s="204"/>
       <c r="M5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="204"/>
+      <c r="N5" s="202"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -5827,46 +5860,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="209" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="211" t="s">
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="209" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="212">
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="210">
         <v>800000</v>
       </c>
-      <c r="J1" s="212"/>
+      <c r="J1" s="210"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="101"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="177" t="s">
+      <c r="A3" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="178"/>
-      <c r="C3" s="186" t="s">
+      <c r="B3" s="185"/>
+      <c r="C3" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="175" t="s">
+      <c r="D3" s="182" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5875,463 +5908,463 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="177" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="186" t="s">
+      <c r="H3" s="177" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="190" t="s">
+      <c r="I3" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="175" t="s">
+      <c r="J3" s="182" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="170" t="s">
+      <c r="K3" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="208" t="s">
+      <c r="L3" s="206" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="179"/>
-      <c r="B4" s="180"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="176"/>
+      <c r="A4" s="186"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="183"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="171" t="s">
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="209"/>
+      <c r="L4" s="207"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="181">
+      <c r="A5" s="175">
         <v>1</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="110" t="s">
+      <c r="B5" s="176"/>
+      <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="58"/>
-      <c r="E5" s="149">
+      <c r="E5" s="148">
         <v>160512.70037999999</v>
       </c>
-      <c r="F5" s="150">
+      <c r="F5" s="149">
         <f>E5</f>
         <v>160512.70037999999</v>
       </c>
-      <c r="G5" s="151">
+      <c r="G5" s="150">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="151">
+      <c r="H5" s="150">
         <f>IF(G5&gt;0,G5*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="95">
+      <c r="I5" s="94">
         <v>13.8</v>
       </c>
-      <c r="J5" s="172">
+      <c r="J5" s="171">
         <f t="shared" ref="J5:J14" si="0">D$1*I5/100</f>
         <v>0</v>
       </c>
-      <c r="K5" s="173">
+      <c r="K5" s="172">
         <f>I$1*I5/100</f>
         <v>110400</v>
       </c>
-      <c r="L5" s="103">
+      <c r="L5" s="102">
         <f>G5+H5+J5+K5</f>
         <v>110400</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="181">
+      <c r="A6" s="175">
         <v>2</v>
       </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="110" t="s">
+      <c r="B6" s="176"/>
+      <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D6" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="149">
+      <c r="E6" s="148">
         <v>137947.87148599999</v>
       </c>
-      <c r="F6" s="150">
+      <c r="F6" s="149">
         <f>343581.33-F7-F13-F14</f>
         <v>167947.86799000003</v>
       </c>
-      <c r="G6" s="151">
+      <c r="G6" s="150">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
         <v>-29999.996504000039</v>
       </c>
-      <c r="H6" s="151">
+      <c r="H6" s="150">
         <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="95">
+      <c r="I6" s="94">
         <v>11.86</v>
       </c>
-      <c r="J6" s="172">
+      <c r="J6" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="173">
+      <c r="K6" s="172">
         <f t="shared" ref="K6:K14" si="3">I$1*I6/100</f>
         <v>94880</v>
       </c>
-      <c r="L6" s="103">
+      <c r="L6" s="102">
         <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
         <v>64880.003495999961</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
+      <c r="A7" s="175">
         <v>3</v>
       </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="110" t="s">
+      <c r="B7" s="176"/>
+      <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D7" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="149">
+      <c r="E7" s="148">
         <v>144926.684546</v>
       </c>
-      <c r="F7" s="150">
+      <c r="F7" s="149">
         <f>E7</f>
         <v>144926.684546</v>
       </c>
-      <c r="G7" s="151">
+      <c r="G7" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="151">
+      <c r="H7" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="95">
+      <c r="I7" s="94">
         <v>12.46</v>
       </c>
-      <c r="J7" s="172">
+      <c r="J7" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="173">
+      <c r="K7" s="172">
         <f t="shared" si="3"/>
         <v>99680</v>
       </c>
-      <c r="L7" s="103">
+      <c r="L7" s="102">
         <f t="shared" si="4"/>
         <v>99680</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="181">
+      <c r="A8" s="175">
         <v>4</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="110" t="s">
+      <c r="B8" s="176"/>
+      <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="149">
+      <c r="E8" s="148">
         <v>171562.48772500001</v>
       </c>
-      <c r="F8" s="150">
+      <c r="F8" s="149">
         <f>E8</f>
         <v>171562.48772500001</v>
       </c>
-      <c r="G8" s="151">
+      <c r="G8" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="151">
+      <c r="H8" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="95">
+      <c r="I8" s="94">
         <v>14.75</v>
       </c>
-      <c r="J8" s="172">
+      <c r="J8" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="173">
+      <c r="K8" s="172">
         <f t="shared" si="3"/>
         <v>118000</v>
       </c>
-      <c r="L8" s="103">
+      <c r="L8" s="102">
         <f t="shared" si="4"/>
         <v>118000</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="181">
+      <c r="A9" s="175">
         <v>5</v>
       </c>
-      <c r="B9" s="182"/>
-      <c r="C9" s="110" t="s">
+      <c r="B9" s="176"/>
+      <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="149">
+      <c r="E9" s="148">
         <v>144345.11679100001</v>
       </c>
-      <c r="F9" s="150">
+      <c r="F9" s="149">
         <f>159931.14-F12</f>
         <v>144345.12416600002</v>
       </c>
-      <c r="G9" s="151">
+      <c r="G9" s="150">
         <f t="shared" si="1"/>
         <v>-7.3750000155996531E-3</v>
       </c>
-      <c r="H9" s="151">
+      <c r="H9" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="94">
         <v>12.41</v>
       </c>
-      <c r="J9" s="172">
+      <c r="J9" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="173">
+      <c r="K9" s="172">
         <f t="shared" si="3"/>
         <v>99280</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="102">
         <f>G9+H9+J9+K9</f>
         <v>99279.992624999984</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="181">
+      <c r="A10" s="175">
         <v>6</v>
       </c>
-      <c r="B10" s="182"/>
-      <c r="C10" s="110" t="s">
+      <c r="B10" s="176"/>
+      <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="72"/>
-      <c r="E10" s="149">
+      <c r="E10" s="148">
         <v>145159.311648</v>
       </c>
-      <c r="F10" s="150">
+      <c r="F10" s="149">
         <f>150000</f>
         <v>150000</v>
       </c>
-      <c r="G10" s="151">
+      <c r="G10" s="150">
         <f t="shared" si="1"/>
         <v>-4840.6883519999974</v>
       </c>
-      <c r="H10" s="151">
+      <c r="H10" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="95">
+      <c r="I10" s="94">
         <v>12.48</v>
       </c>
-      <c r="J10" s="172">
+      <c r="J10" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="173">
+      <c r="K10" s="172">
         <f t="shared" si="3"/>
         <v>99840</v>
       </c>
-      <c r="L10" s="103">
+      <c r="L10" s="102">
         <f t="shared" si="4"/>
         <v>94999.311648000003</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="181">
+      <c r="A11" s="175">
         <v>7</v>
       </c>
-      <c r="B11" s="182"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="176"/>
+      <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="72"/>
-      <c r="E11" s="149">
+      <c r="E11" s="148">
         <v>212388.54412600002</v>
       </c>
-      <c r="F11" s="150">
+      <c r="F11" s="149">
         <f>E11</f>
         <v>212388.54412600002</v>
       </c>
-      <c r="G11" s="151">
+      <c r="G11" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="151">
+      <c r="H11" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="95">
+      <c r="I11" s="94">
         <v>18.260000000000002</v>
       </c>
-      <c r="J11" s="172">
+      <c r="J11" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="173">
+      <c r="K11" s="172">
         <f t="shared" si="3"/>
         <v>146080.00000000003</v>
       </c>
-      <c r="L11" s="103">
+      <c r="L11" s="102">
         <f t="shared" si="4"/>
         <v>146080.00000000003</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="181" t="s">
+      <c r="A12" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="182"/>
-      <c r="C12" s="110" t="str">
+      <c r="B12" s="176"/>
+      <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="72"/>
-      <c r="E12" s="149">
+      <c r="E12" s="148">
         <v>15586.015834000002</v>
       </c>
-      <c r="F12" s="150">
+      <c r="F12" s="149">
         <f>E12</f>
         <v>15586.015834000002</v>
       </c>
-      <c r="G12" s="151">
+      <c r="G12" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="151">
+      <c r="H12" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="95">
+      <c r="I12" s="94">
         <v>1.34</v>
       </c>
-      <c r="J12" s="172">
+      <c r="J12" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="173">
+      <c r="K12" s="172">
         <f t="shared" si="3"/>
         <v>10720</v>
       </c>
-      <c r="L12" s="103">
+      <c r="L12" s="102">
         <f t="shared" si="4"/>
         <v>10720</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="182"/>
-      <c r="C13" s="110" t="str">
+      <c r="B13" s="176"/>
+      <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="72"/>
-      <c r="E13" s="149">
+      <c r="E13" s="148">
         <v>15353.388731999999</v>
       </c>
-      <c r="F13" s="150">
+      <c r="F13" s="149">
         <f>E13</f>
         <v>15353.388731999999</v>
       </c>
-      <c r="G13" s="151">
+      <c r="G13" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="95">
+      <c r="I13" s="94">
         <v>1.32</v>
       </c>
-      <c r="J13" s="172">
+      <c r="J13" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="173">
+      <c r="K13" s="172">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
-      <c r="L13" s="103">
+      <c r="L13" s="102">
         <f t="shared" si="4"/>
         <v>10560</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="181" t="s">
+      <c r="A14" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="182"/>
+      <c r="B14" s="176"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="72"/>
-      <c r="E14" s="149">
+      <c r="E14" s="148">
         <v>15353.388731999999</v>
       </c>
-      <c r="F14" s="150">
+      <c r="F14" s="149">
         <f>E14</f>
         <v>15353.388731999999</v>
       </c>
-      <c r="G14" s="151">
+      <c r="G14" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H14" s="151">
+      <c r="H14" s="150">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="95">
+      <c r="I14" s="94">
         <v>1.32</v>
       </c>
-      <c r="J14" s="172">
+      <c r="J14" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="173">
+      <c r="K14" s="172">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
-      <c r="L14" s="103">
+      <c r="L14" s="102">
         <f t="shared" si="4"/>
         <v>10560</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
         <v>1163135.51</v>
@@ -6348,7 +6381,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I15" s="109">
+      <c r="I15" s="108">
         <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
         <v>100</v>
       </c>
@@ -6754,345 +6787,345 @@
     <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="196" t="s">
+      <c r="E32" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="197"/>
-      <c r="G32" s="197"/>
-      <c r="H32" s="197"/>
-      <c r="I32" s="197"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="195"/>
-      <c r="L32" s="152"/>
-      <c r="M32" s="153"/>
+      <c r="F32" s="191"/>
+      <c r="G32" s="191"/>
+      <c r="H32" s="191"/>
+      <c r="I32" s="191"/>
+      <c r="J32" s="191"/>
+      <c r="K32" s="192"/>
+      <c r="L32" s="151"/>
+      <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
     <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="198" t="s">
+      <c r="E33" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="197"/>
-      <c r="G33" s="197"/>
-      <c r="H33" s="197"/>
-      <c r="I33" s="197"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="195"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="155"/>
+      <c r="F33" s="191"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="192"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="157"/>
-      <c r="J34" s="157">
+      <c r="E34" s="151"/>
+      <c r="F34" s="155"/>
+      <c r="G34" s="155"/>
+      <c r="H34" s="155"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="155"/>
-      <c r="L34" s="154"/>
-      <c r="M34" s="155"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="153"/>
+      <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="154" t="s">
+      <c r="E35" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F35" s="157"/>
-      <c r="G35" s="157"/>
-      <c r="H35" s="157"/>
-      <c r="I35" s="157"/>
-      <c r="J35" s="157"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="154"/>
-      <c r="M35" s="155"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="156"/>
+      <c r="H35" s="156"/>
+      <c r="I35" s="156"/>
+      <c r="J35" s="156"/>
+      <c r="K35" s="154"/>
+      <c r="L35" s="153"/>
+      <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="158"/>
-      <c r="F36" s="159"/>
-      <c r="G36" s="159"/>
-      <c r="H36" s="159"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="159"/>
-      <c r="K36" s="160"/>
-      <c r="L36" s="154"/>
-      <c r="M36" s="155"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="158"/>
+      <c r="G36" s="158"/>
+      <c r="H36" s="158"/>
+      <c r="I36" s="158"/>
+      <c r="J36" s="158"/>
+      <c r="K36" s="159"/>
+      <c r="L36" s="153"/>
+      <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="199" t="s">
+      <c r="E37" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="200"/>
-      <c r="I37" s="200"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="201"/>
-      <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="195"/>
+      <c r="I37" s="195"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="196"/>
+      <c r="L37" s="153"/>
+      <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="154"/>
-      <c r="F38" s="157"/>
-      <c r="G38" s="157"/>
-      <c r="H38" s="157"/>
-      <c r="I38" s="157"/>
-      <c r="J38" s="157"/>
-      <c r="K38" s="155"/>
-      <c r="L38" s="154"/>
-      <c r="M38" s="155"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="156"/>
+      <c r="G38" s="156"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="156"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="154"/>
+      <c r="L38" s="153"/>
+      <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="154" t="s">
+      <c r="E39" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157" t="str">
+      <c r="F39" s="156"/>
+      <c r="G39" s="156" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="157"/>
-      <c r="I39" s="157" t="s">
+      <c r="H39" s="156"/>
+      <c r="I39" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J39" s="161">
+      <c r="J39" s="160">
         <v>45674</v>
       </c>
-      <c r="K39" s="155"/>
-      <c r="L39" s="183" t="s">
+      <c r="K39" s="154"/>
+      <c r="L39" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="184"/>
+      <c r="M39" s="180"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="154" t="s">
+      <c r="E40" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="162">
+      <c r="F40" s="161">
         <v>3</v>
       </c>
-      <c r="G40" s="157"/>
-      <c r="H40" s="157"/>
-      <c r="I40" s="157"/>
-      <c r="J40" s="157"/>
-      <c r="K40" s="155"/>
-      <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="154"/>
+      <c r="L40" s="153"/>
+      <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
-      <c r="I41" s="157"/>
-      <c r="J41" s="157"/>
-      <c r="K41" s="155"/>
-      <c r="L41" s="185"/>
-      <c r="M41" s="184"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="156"/>
+      <c r="I41" s="156"/>
+      <c r="J41" s="156"/>
+      <c r="K41" s="154"/>
+      <c r="L41" s="181"/>
+      <c r="M41" s="180"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="154" t="s">
+      <c r="E42" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="157"/>
-      <c r="J42" s="163">
+      <c r="F42" s="156"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="156"/>
+      <c r="I42" s="156"/>
+      <c r="J42" s="162">
         <f>J7</f>
         <v>0</v>
       </c>
-      <c r="K42" s="155"/>
-      <c r="L42" s="154"/>
-      <c r="M42" s="155"/>
+      <c r="K42" s="154"/>
+      <c r="L42" s="153"/>
+      <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="164" t="s">
+      <c r="E43" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="163">
+      <c r="F43" s="156"/>
+      <c r="G43" s="156"/>
+      <c r="H43" s="156"/>
+      <c r="I43" s="156"/>
+      <c r="J43" s="162">
         <f>K7</f>
         <v>99680</v>
       </c>
-      <c r="K43" s="155"/>
-      <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="K43" s="154"/>
+      <c r="L43" s="153"/>
+      <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="164" t="s">
+      <c r="E44" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="157"/>
-      <c r="G44" s="157"/>
-      <c r="H44" s="157"/>
-      <c r="I44" s="157"/>
-      <c r="J44" s="163">
+      <c r="F44" s="156"/>
+      <c r="G44" s="156"/>
+      <c r="H44" s="156"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="162">
         <f>G7+H7</f>
         <v>0</v>
       </c>
-      <c r="K44" s="155"/>
-      <c r="L44" s="154"/>
-      <c r="M44" s="155"/>
+      <c r="K44" s="154"/>
+      <c r="L44" s="153"/>
+      <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
     <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="164"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="157"/>
-      <c r="I45" s="157"/>
-      <c r="J45" s="163"/>
-      <c r="K45" s="155"/>
-      <c r="L45" s="154"/>
-      <c r="M45" s="155"/>
+      <c r="E45" s="163"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
+      <c r="H45" s="156"/>
+      <c r="I45" s="156"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="154"/>
+      <c r="L45" s="153"/>
+      <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
     <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="164"/>
-      <c r="F46" s="157"/>
-      <c r="G46" s="157"/>
-      <c r="H46" s="157"/>
-      <c r="I46" s="157"/>
-      <c r="J46" s="163"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="154"/>
-      <c r="M46" s="155"/>
+      <c r="E46" s="163"/>
+      <c r="F46" s="156"/>
+      <c r="G46" s="156"/>
+      <c r="H46" s="156"/>
+      <c r="I46" s="156"/>
+      <c r="J46" s="162"/>
+      <c r="K46" s="154"/>
+      <c r="L46" s="153"/>
+      <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
     <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="157"/>
-      <c r="G47" s="157"/>
-      <c r="H47" s="157"/>
-      <c r="I47" s="157"/>
-      <c r="J47" s="163"/>
-      <c r="K47" s="155"/>
-      <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="F47" s="156"/>
+      <c r="G47" s="156"/>
+      <c r="H47" s="156"/>
+      <c r="I47" s="156"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="154"/>
+      <c r="L47" s="153"/>
+      <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
     <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="164"/>
-      <c r="F48" s="157"/>
-      <c r="G48" s="157"/>
-      <c r="H48" s="157"/>
-      <c r="I48" s="157"/>
-      <c r="J48" s="163"/>
-      <c r="K48" s="155"/>
-      <c r="L48" s="154"/>
-      <c r="M48" s="155"/>
+      <c r="E48" s="163"/>
+      <c r="F48" s="156"/>
+      <c r="G48" s="156"/>
+      <c r="H48" s="156"/>
+      <c r="I48" s="156"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="154"/>
+      <c r="L48" s="153"/>
+      <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
     <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="154"/>
-      <c r="F49" s="157"/>
-      <c r="G49" s="157"/>
-      <c r="H49" s="157"/>
-      <c r="I49" s="157"/>
-      <c r="J49" s="157"/>
-      <c r="K49" s="155"/>
-      <c r="L49" s="154"/>
-      <c r="M49" s="155"/>
+      <c r="E49" s="153"/>
+      <c r="F49" s="156"/>
+      <c r="G49" s="156"/>
+      <c r="H49" s="156"/>
+      <c r="I49" s="156"/>
+      <c r="J49" s="156"/>
+      <c r="K49" s="154"/>
+      <c r="L49" s="153"/>
+      <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="154" t="s">
+      <c r="E50" s="153" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="157"/>
-      <c r="G50" s="157"/>
-      <c r="H50" s="157"/>
-      <c r="I50" s="157"/>
-      <c r="J50" s="157">
+      <c r="F50" s="156"/>
+      <c r="G50" s="156"/>
+      <c r="H50" s="156"/>
+      <c r="I50" s="156"/>
+      <c r="J50" s="156">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="155"/>
-      <c r="L50" s="154"/>
-      <c r="M50" s="155"/>
+      <c r="K50" s="154"/>
+      <c r="L50" s="153"/>
+      <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
     <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="154"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="157"/>
-      <c r="I51" s="157"/>
-      <c r="J51" s="157"/>
-      <c r="K51" s="155"/>
-      <c r="L51" s="165"/>
-      <c r="M51" s="166"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="156"/>
+      <c r="G51" s="156"/>
+      <c r="H51" s="156"/>
+      <c r="I51" s="156"/>
+      <c r="J51" s="156"/>
+      <c r="K51" s="154"/>
+      <c r="L51" s="164"/>
+      <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
     <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="192" t="s">
+      <c r="E52" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="194">
+      <c r="F52" s="198"/>
+      <c r="G52" s="198"/>
+      <c r="H52" s="198"/>
+      <c r="I52" s="198"/>
+      <c r="J52" s="199">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="195"/>
-      <c r="L52" s="167"/>
-      <c r="M52" s="168"/>
+      <c r="K52" s="192"/>
+      <c r="L52" s="166"/>
+      <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.3">
@@ -7102,833 +7135,833 @@
     </row>
     <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="196" t="s">
+      <c r="E56" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="197"/>
-      <c r="G56" s="197"/>
-      <c r="H56" s="197"/>
-      <c r="I56" s="197"/>
-      <c r="J56" s="197"/>
-      <c r="K56" s="195"/>
-      <c r="L56" s="152"/>
-      <c r="M56" s="153"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="191"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="191"/>
+      <c r="J56" s="191"/>
+      <c r="K56" s="192"/>
+      <c r="L56" s="151"/>
+      <c r="M56" s="152"/>
     </row>
     <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="198" t="s">
+      <c r="E57" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="197"/>
-      <c r="G57" s="197"/>
-      <c r="H57" s="197"/>
-      <c r="I57" s="197"/>
-      <c r="J57" s="197"/>
-      <c r="K57" s="195"/>
-      <c r="L57" s="154"/>
-      <c r="M57" s="155"/>
+      <c r="F57" s="191"/>
+      <c r="G57" s="191"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="191"/>
+      <c r="J57" s="191"/>
+      <c r="K57" s="192"/>
+      <c r="L57" s="153"/>
+      <c r="M57" s="154"/>
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E58" s="152"/>
-      <c r="F58" s="156"/>
-      <c r="G58" s="156"/>
-      <c r="H58" s="156"/>
-      <c r="I58" s="157"/>
-      <c r="J58" s="157">
+      <c r="E58" s="151"/>
+      <c r="F58" s="155"/>
+      <c r="G58" s="155"/>
+      <c r="H58" s="155"/>
+      <c r="I58" s="156"/>
+      <c r="J58" s="156">
         <f>J34</f>
         <v>0</v>
       </c>
-      <c r="K58" s="155"/>
-      <c r="L58" s="154"/>
-      <c r="M58" s="155"/>
+      <c r="K58" s="154"/>
+      <c r="L58" s="153"/>
+      <c r="M58" s="154"/>
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E59" s="154" t="s">
+      <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F59" s="157"/>
-      <c r="G59" s="157"/>
-      <c r="H59" s="157"/>
-      <c r="I59" s="157"/>
-      <c r="J59" s="157"/>
-      <c r="K59" s="155"/>
-      <c r="L59" s="154"/>
-      <c r="M59" s="155"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="154"/>
+      <c r="L59" s="153"/>
+      <c r="M59" s="154"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E60" s="158"/>
-      <c r="F60" s="159"/>
-      <c r="G60" s="159"/>
-      <c r="H60" s="159"/>
-      <c r="I60" s="159"/>
-      <c r="J60" s="159"/>
-      <c r="K60" s="160"/>
-      <c r="L60" s="154"/>
-      <c r="M60" s="155"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="158"/>
+      <c r="G60" s="158"/>
+      <c r="H60" s="158"/>
+      <c r="I60" s="158"/>
+      <c r="J60" s="158"/>
+      <c r="K60" s="159"/>
+      <c r="L60" s="153"/>
+      <c r="M60" s="154"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="199" t="s">
+      <c r="E61" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="200"/>
-      <c r="G61" s="200"/>
-      <c r="H61" s="200"/>
-      <c r="I61" s="200"/>
-      <c r="J61" s="200"/>
-      <c r="K61" s="201"/>
-      <c r="L61" s="154"/>
-      <c r="M61" s="155"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="195"/>
+      <c r="I61" s="195"/>
+      <c r="J61" s="195"/>
+      <c r="K61" s="196"/>
+      <c r="L61" s="153"/>
+      <c r="M61" s="154"/>
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E62" s="154"/>
-      <c r="F62" s="157"/>
-      <c r="G62" s="157"/>
-      <c r="H62" s="157"/>
-      <c r="I62" s="157"/>
-      <c r="J62" s="157"/>
-      <c r="K62" s="155"/>
-      <c r="L62" s="154"/>
-      <c r="M62" s="155"/>
+      <c r="E62" s="153"/>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="156"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="154"/>
+      <c r="L62" s="153"/>
+      <c r="M62" s="154"/>
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E63" s="154" t="s">
+      <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F63" s="157"/>
-      <c r="G63" s="162" t="str">
+      <c r="F63" s="156"/>
+      <c r="G63" s="161" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="157"/>
-      <c r="I63" s="157" t="s">
+      <c r="H63" s="156"/>
+      <c r="I63" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J63" s="161">
+      <c r="J63" s="160">
         <v>45674</v>
       </c>
-      <c r="K63" s="155"/>
-      <c r="L63" s="183" t="s">
+      <c r="K63" s="154"/>
+      <c r="L63" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="184"/>
+      <c r="M63" s="180"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E64" s="154" t="s">
+      <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F64" s="162">
+      <c r="F64" s="161">
         <v>4</v>
       </c>
-      <c r="G64" s="157"/>
-      <c r="H64" s="157"/>
-      <c r="I64" s="157"/>
-      <c r="J64" s="157"/>
-      <c r="K64" s="155"/>
-      <c r="L64" s="154"/>
-      <c r="M64" s="155"/>
+      <c r="G64" s="156"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="156"/>
+      <c r="J64" s="156"/>
+      <c r="K64" s="154"/>
+      <c r="L64" s="153"/>
+      <c r="M64" s="154"/>
     </row>
     <row r="65" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E65" s="154"/>
-      <c r="F65" s="157"/>
-      <c r="G65" s="157"/>
-      <c r="H65" s="157"/>
-      <c r="I65" s="157"/>
-      <c r="J65" s="157"/>
-      <c r="K65" s="155"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="184"/>
+      <c r="E65" s="153"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="154"/>
+      <c r="L65" s="181"/>
+      <c r="M65" s="180"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E66" s="154" t="s">
+      <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="157"/>
-      <c r="G66" s="157"/>
-      <c r="H66" s="157"/>
-      <c r="I66" s="157"/>
-      <c r="J66" s="163">
+      <c r="F66" s="156"/>
+      <c r="G66" s="156"/>
+      <c r="H66" s="156"/>
+      <c r="I66" s="156"/>
+      <c r="J66" s="162">
         <f>J8</f>
         <v>0</v>
       </c>
-      <c r="K66" s="155"/>
-      <c r="L66" s="154"/>
-      <c r="M66" s="155"/>
+      <c r="K66" s="154"/>
+      <c r="L66" s="153"/>
+      <c r="M66" s="154"/>
     </row>
     <row r="67" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E67" s="164" t="s">
+      <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F67" s="157"/>
-      <c r="G67" s="157"/>
-      <c r="H67" s="157"/>
-      <c r="I67" s="157"/>
-      <c r="J67" s="163">
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="162">
         <f>K8</f>
         <v>118000</v>
       </c>
-      <c r="K67" s="155"/>
-      <c r="L67" s="154"/>
-      <c r="M67" s="155"/>
+      <c r="K67" s="154"/>
+      <c r="L67" s="153"/>
+      <c r="M67" s="154"/>
     </row>
     <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="164" t="s">
+      <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="F68" s="157"/>
-      <c r="G68" s="157"/>
-      <c r="H68" s="157"/>
-      <c r="I68" s="157"/>
-      <c r="J68" s="163">
+      <c r="F68" s="156"/>
+      <c r="G68" s="156"/>
+      <c r="H68" s="156"/>
+      <c r="I68" s="156"/>
+      <c r="J68" s="162">
         <f>G29+H29</f>
         <v>0</v>
       </c>
-      <c r="K68" s="155"/>
-      <c r="L68" s="154"/>
-      <c r="M68" s="155"/>
+      <c r="K68" s="154"/>
+      <c r="L68" s="153"/>
+      <c r="M68" s="154"/>
     </row>
     <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="164"/>
-      <c r="F69" s="157"/>
-      <c r="G69" s="157"/>
-      <c r="H69" s="157"/>
-      <c r="I69" s="157"/>
-      <c r="J69" s="163"/>
-      <c r="K69" s="155"/>
-      <c r="L69" s="154"/>
-      <c r="M69" s="155"/>
+      <c r="E69" s="163"/>
+      <c r="F69" s="156"/>
+      <c r="G69" s="156"/>
+      <c r="H69" s="156"/>
+      <c r="I69" s="156"/>
+      <c r="J69" s="162"/>
+      <c r="K69" s="154"/>
+      <c r="L69" s="153"/>
+      <c r="M69" s="154"/>
     </row>
     <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="164"/>
-      <c r="F70" s="157"/>
-      <c r="G70" s="157"/>
-      <c r="H70" s="157"/>
-      <c r="I70" s="157"/>
-      <c r="J70" s="163"/>
-      <c r="K70" s="155"/>
-      <c r="L70" s="154"/>
-      <c r="M70" s="155"/>
+      <c r="E70" s="163"/>
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="156"/>
+      <c r="I70" s="156"/>
+      <c r="J70" s="162"/>
+      <c r="K70" s="154"/>
+      <c r="L70" s="153"/>
+      <c r="M70" s="154"/>
     </row>
     <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="F71" s="157"/>
-      <c r="G71" s="157"/>
-      <c r="H71" s="157"/>
-      <c r="I71" s="157"/>
-      <c r="J71" s="163"/>
-      <c r="K71" s="155"/>
-      <c r="L71" s="154"/>
-      <c r="M71" s="155"/>
+      <c r="F71" s="156"/>
+      <c r="G71" s="156"/>
+      <c r="H71" s="156"/>
+      <c r="I71" s="156"/>
+      <c r="J71" s="162"/>
+      <c r="K71" s="154"/>
+      <c r="L71" s="153"/>
+      <c r="M71" s="154"/>
     </row>
     <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E72" s="164"/>
-      <c r="F72" s="157"/>
-      <c r="G72" s="157"/>
-      <c r="H72" s="157"/>
-      <c r="I72" s="157"/>
-      <c r="J72" s="163"/>
-      <c r="K72" s="155"/>
-      <c r="L72" s="154"/>
-      <c r="M72" s="155"/>
+      <c r="E72" s="163"/>
+      <c r="F72" s="156"/>
+      <c r="G72" s="156"/>
+      <c r="H72" s="156"/>
+      <c r="I72" s="156"/>
+      <c r="J72" s="162"/>
+      <c r="K72" s="154"/>
+      <c r="L72" s="153"/>
+      <c r="M72" s="154"/>
     </row>
     <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E73" s="154"/>
-      <c r="F73" s="157"/>
-      <c r="G73" s="157"/>
-      <c r="H73" s="157"/>
-      <c r="I73" s="157"/>
-      <c r="J73" s="157"/>
-      <c r="K73" s="155"/>
-      <c r="L73" s="154"/>
-      <c r="M73" s="155"/>
+      <c r="E73" s="153"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="156"/>
+      <c r="H73" s="156"/>
+      <c r="I73" s="156"/>
+      <c r="J73" s="156"/>
+      <c r="K73" s="154"/>
+      <c r="L73" s="153"/>
+      <c r="M73" s="154"/>
     </row>
     <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E74" s="154"/>
-      <c r="F74" s="157"/>
-      <c r="G74" s="157"/>
-      <c r="H74" s="157"/>
-      <c r="I74" s="157"/>
-      <c r="J74" s="157"/>
-      <c r="K74" s="155"/>
-      <c r="L74" s="154"/>
-      <c r="M74" s="155"/>
+      <c r="E74" s="153"/>
+      <c r="F74" s="156"/>
+      <c r="G74" s="156"/>
+      <c r="H74" s="156"/>
+      <c r="I74" s="156"/>
+      <c r="J74" s="156"/>
+      <c r="K74" s="154"/>
+      <c r="L74" s="153"/>
+      <c r="M74" s="154"/>
     </row>
     <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E75" s="154"/>
-      <c r="F75" s="157"/>
-      <c r="G75" s="157"/>
-      <c r="H75" s="157"/>
-      <c r="I75" s="157"/>
-      <c r="J75" s="157"/>
-      <c r="K75" s="155"/>
-      <c r="L75" s="165"/>
-      <c r="M75" s="166"/>
+      <c r="E75" s="153"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
+      <c r="H75" s="156"/>
+      <c r="I75" s="156"/>
+      <c r="J75" s="156"/>
+      <c r="K75" s="154"/>
+      <c r="L75" s="164"/>
+      <c r="M75" s="165"/>
     </row>
     <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="192" t="s">
+      <c r="E76" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="193"/>
-      <c r="G76" s="193"/>
-      <c r="H76" s="193"/>
-      <c r="I76" s="193"/>
-      <c r="J76" s="194">
+      <c r="F76" s="198"/>
+      <c r="G76" s="198"/>
+      <c r="H76" s="198"/>
+      <c r="I76" s="198"/>
+      <c r="J76" s="199">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="195"/>
-      <c r="L76" s="167"/>
-      <c r="M76" s="168"/>
+      <c r="K76" s="192"/>
+      <c r="L76" s="166"/>
+      <c r="M76" s="167"/>
     </row>
     <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="196" t="s">
+      <c r="E83" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="197"/>
-      <c r="G83" s="197"/>
-      <c r="H83" s="197"/>
-      <c r="I83" s="197"/>
-      <c r="J83" s="197"/>
-      <c r="K83" s="195"/>
-      <c r="L83" s="152"/>
-      <c r="M83" s="153"/>
+      <c r="F83" s="191"/>
+      <c r="G83" s="191"/>
+      <c r="H83" s="191"/>
+      <c r="I83" s="191"/>
+      <c r="J83" s="191"/>
+      <c r="K83" s="192"/>
+      <c r="L83" s="151"/>
+      <c r="M83" s="152"/>
     </row>
     <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="198" t="s">
+      <c r="E84" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="197"/>
-      <c r="G84" s="197"/>
-      <c r="H84" s="197"/>
-      <c r="I84" s="197"/>
-      <c r="J84" s="197"/>
-      <c r="K84" s="195"/>
-      <c r="L84" s="154"/>
-      <c r="M84" s="155"/>
+      <c r="F84" s="191"/>
+      <c r="G84" s="191"/>
+      <c r="H84" s="191"/>
+      <c r="I84" s="191"/>
+      <c r="J84" s="191"/>
+      <c r="K84" s="192"/>
+      <c r="L84" s="153"/>
+      <c r="M84" s="154"/>
     </row>
     <row r="85" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E85" s="152"/>
-      <c r="F85" s="156"/>
-      <c r="G85" s="156"/>
-      <c r="H85" s="156"/>
-      <c r="I85" s="157"/>
-      <c r="J85" s="157">
+      <c r="E85" s="151"/>
+      <c r="F85" s="155"/>
+      <c r="G85" s="155"/>
+      <c r="H85" s="155"/>
+      <c r="I85" s="156"/>
+      <c r="J85" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K85" s="155"/>
-      <c r="L85" s="154"/>
-      <c r="M85" s="155"/>
+      <c r="K85" s="154"/>
+      <c r="L85" s="153"/>
+      <c r="M85" s="154"/>
     </row>
     <row r="86" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E86" s="154" t="s">
+      <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F86" s="157"/>
-      <c r="G86" s="157"/>
-      <c r="H86" s="157"/>
-      <c r="I86" s="157"/>
-      <c r="J86" s="157"/>
-      <c r="K86" s="155"/>
-      <c r="L86" s="154"/>
-      <c r="M86" s="155"/>
+      <c r="F86" s="156"/>
+      <c r="G86" s="156"/>
+      <c r="H86" s="156"/>
+      <c r="I86" s="156"/>
+      <c r="J86" s="156"/>
+      <c r="K86" s="154"/>
+      <c r="L86" s="153"/>
+      <c r="M86" s="154"/>
     </row>
     <row r="87" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E87" s="158"/>
-      <c r="F87" s="159"/>
-      <c r="G87" s="159"/>
-      <c r="H87" s="159"/>
-      <c r="I87" s="159"/>
-      <c r="J87" s="159"/>
-      <c r="K87" s="160"/>
-      <c r="L87" s="154"/>
-      <c r="M87" s="155"/>
+      <c r="E87" s="157"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="158"/>
+      <c r="H87" s="158"/>
+      <c r="I87" s="158"/>
+      <c r="J87" s="158"/>
+      <c r="K87" s="159"/>
+      <c r="L87" s="153"/>
+      <c r="M87" s="154"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="199" t="s">
+      <c r="E88" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="200"/>
-      <c r="G88" s="200"/>
-      <c r="H88" s="200"/>
-      <c r="I88" s="200"/>
-      <c r="J88" s="200"/>
-      <c r="K88" s="201"/>
-      <c r="L88" s="154"/>
-      <c r="M88" s="155"/>
+      <c r="F88" s="195"/>
+      <c r="G88" s="195"/>
+      <c r="H88" s="195"/>
+      <c r="I88" s="195"/>
+      <c r="J88" s="195"/>
+      <c r="K88" s="196"/>
+      <c r="L88" s="153"/>
+      <c r="M88" s="154"/>
     </row>
     <row r="89" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E89" s="154"/>
-      <c r="F89" s="157"/>
-      <c r="G89" s="157"/>
-      <c r="H89" s="157"/>
-      <c r="I89" s="157"/>
-      <c r="J89" s="157"/>
-      <c r="K89" s="155"/>
-      <c r="L89" s="154"/>
-      <c r="M89" s="155"/>
+      <c r="E89" s="153"/>
+      <c r="F89" s="156"/>
+      <c r="G89" s="156"/>
+      <c r="H89" s="156"/>
+      <c r="I89" s="156"/>
+      <c r="J89" s="156"/>
+      <c r="K89" s="154"/>
+      <c r="L89" s="153"/>
+      <c r="M89" s="154"/>
     </row>
     <row r="90" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E90" s="154" t="s">
+      <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F90" s="157"/>
-      <c r="G90" s="162" t="str">
+      <c r="F90" s="156"/>
+      <c r="G90" s="161" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="157"/>
-      <c r="I90" s="157" t="s">
+      <c r="H90" s="156"/>
+      <c r="I90" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="161">
+      <c r="J90" s="160">
         <v>45674</v>
       </c>
-      <c r="K90" s="155"/>
-      <c r="L90" s="183" t="s">
+      <c r="K90" s="154"/>
+      <c r="L90" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="184"/>
+      <c r="M90" s="180"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E91" s="154" t="s">
+      <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F91" s="162">
+      <c r="F91" s="161">
         <v>6</v>
       </c>
-      <c r="G91" s="157"/>
-      <c r="H91" s="157"/>
-      <c r="I91" s="157"/>
-      <c r="J91" s="157"/>
-      <c r="K91" s="155"/>
-      <c r="L91" s="154"/>
-      <c r="M91" s="155"/>
+      <c r="G91" s="156"/>
+      <c r="H91" s="156"/>
+      <c r="I91" s="156"/>
+      <c r="J91" s="156"/>
+      <c r="K91" s="154"/>
+      <c r="L91" s="153"/>
+      <c r="M91" s="154"/>
     </row>
     <row r="92" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E92" s="154"/>
-      <c r="F92" s="157"/>
-      <c r="G92" s="157"/>
-      <c r="H92" s="157"/>
-      <c r="I92" s="157"/>
-      <c r="J92" s="157"/>
-      <c r="K92" s="155"/>
-      <c r="L92" s="185"/>
-      <c r="M92" s="184"/>
+      <c r="E92" s="153"/>
+      <c r="F92" s="156"/>
+      <c r="G92" s="156"/>
+      <c r="H92" s="156"/>
+      <c r="I92" s="156"/>
+      <c r="J92" s="156"/>
+      <c r="K92" s="154"/>
+      <c r="L92" s="181"/>
+      <c r="M92" s="180"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E93" s="154" t="s">
+      <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F93" s="157"/>
-      <c r="G93" s="157"/>
-      <c r="H93" s="157"/>
-      <c r="I93" s="157"/>
-      <c r="J93" s="163">
+      <c r="F93" s="156"/>
+      <c r="G93" s="156"/>
+      <c r="H93" s="156"/>
+      <c r="I93" s="156"/>
+      <c r="J93" s="162">
         <f>J10</f>
         <v>0</v>
       </c>
-      <c r="K93" s="155"/>
-      <c r="L93" s="154"/>
-      <c r="M93" s="155"/>
+      <c r="K93" s="154"/>
+      <c r="L93" s="153"/>
+      <c r="M93" s="154"/>
     </row>
     <row r="94" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E94" s="164" t="s">
+      <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="157"/>
-      <c r="G94" s="157"/>
-      <c r="H94" s="157"/>
-      <c r="I94" s="157"/>
-      <c r="J94" s="163">
+      <c r="F94" s="156"/>
+      <c r="G94" s="156"/>
+      <c r="H94" s="156"/>
+      <c r="I94" s="156"/>
+      <c r="J94" s="162">
         <f>K10</f>
         <v>99840</v>
       </c>
-      <c r="K94" s="155"/>
-      <c r="L94" s="154"/>
-      <c r="M94" s="155"/>
+      <c r="K94" s="154"/>
+      <c r="L94" s="153"/>
+      <c r="M94" s="154"/>
     </row>
     <row r="95" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E95" s="164" t="s">
+      <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="157"/>
-      <c r="G95" s="157"/>
-      <c r="H95" s="157"/>
-      <c r="I95" s="157"/>
-      <c r="J95" s="163">
+      <c r="F95" s="156"/>
+      <c r="G95" s="156"/>
+      <c r="H95" s="156"/>
+      <c r="I95" s="156"/>
+      <c r="J95" s="162">
         <v>23.89</v>
       </c>
-      <c r="K95" s="155"/>
-      <c r="L95" s="154"/>
-      <c r="M95" s="155"/>
+      <c r="K95" s="154"/>
+      <c r="L95" s="153"/>
+      <c r="M95" s="154"/>
     </row>
     <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="164"/>
-      <c r="F96" s="157"/>
-      <c r="G96" s="157"/>
-      <c r="H96" s="157"/>
-      <c r="I96" s="157"/>
-      <c r="J96" s="163"/>
-      <c r="K96" s="155"/>
-      <c r="L96" s="154"/>
-      <c r="M96" s="155"/>
+      <c r="E96" s="163"/>
+      <c r="F96" s="156"/>
+      <c r="G96" s="156"/>
+      <c r="H96" s="156"/>
+      <c r="I96" s="156"/>
+      <c r="J96" s="162"/>
+      <c r="K96" s="154"/>
+      <c r="L96" s="153"/>
+      <c r="M96" s="154"/>
     </row>
     <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E97" s="164"/>
-      <c r="F97" s="157"/>
-      <c r="G97" s="157"/>
-      <c r="H97" s="157"/>
-      <c r="I97" s="157"/>
-      <c r="J97" s="163"/>
-      <c r="K97" s="155"/>
-      <c r="L97" s="154"/>
-      <c r="M97" s="155"/>
+      <c r="E97" s="163"/>
+      <c r="F97" s="156"/>
+      <c r="G97" s="156"/>
+      <c r="H97" s="156"/>
+      <c r="I97" s="156"/>
+      <c r="J97" s="162"/>
+      <c r="K97" s="154"/>
+      <c r="L97" s="153"/>
+      <c r="M97" s="154"/>
     </row>
     <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F98" s="157"/>
-      <c r="G98" s="157"/>
-      <c r="H98" s="157"/>
-      <c r="I98" s="157"/>
-      <c r="J98" s="163"/>
-      <c r="K98" s="155"/>
-      <c r="L98" s="154"/>
-      <c r="M98" s="155"/>
+      <c r="F98" s="156"/>
+      <c r="G98" s="156"/>
+      <c r="H98" s="156"/>
+      <c r="I98" s="156"/>
+      <c r="J98" s="162"/>
+      <c r="K98" s="154"/>
+      <c r="L98" s="153"/>
+      <c r="M98" s="154"/>
     </row>
     <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E99" s="164"/>
-      <c r="F99" s="157"/>
-      <c r="G99" s="157"/>
-      <c r="H99" s="157"/>
-      <c r="I99" s="157"/>
-      <c r="J99" s="163"/>
-      <c r="K99" s="155"/>
-      <c r="L99" s="154"/>
-      <c r="M99" s="155"/>
+      <c r="E99" s="163"/>
+      <c r="F99" s="156"/>
+      <c r="G99" s="156"/>
+      <c r="H99" s="156"/>
+      <c r="I99" s="156"/>
+      <c r="J99" s="162"/>
+      <c r="K99" s="154"/>
+      <c r="L99" s="153"/>
+      <c r="M99" s="154"/>
     </row>
     <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E100" s="154"/>
-      <c r="F100" s="157"/>
-      <c r="G100" s="157"/>
-      <c r="H100" s="157"/>
-      <c r="I100" s="157"/>
-      <c r="J100" s="157"/>
-      <c r="K100" s="155"/>
-      <c r="L100" s="154"/>
-      <c r="M100" s="155"/>
+      <c r="E100" s="153"/>
+      <c r="F100" s="156"/>
+      <c r="G100" s="156"/>
+      <c r="H100" s="156"/>
+      <c r="I100" s="156"/>
+      <c r="J100" s="156"/>
+      <c r="K100" s="154"/>
+      <c r="L100" s="153"/>
+      <c r="M100" s="154"/>
     </row>
     <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E101" s="154"/>
-      <c r="F101" s="157"/>
-      <c r="G101" s="157"/>
-      <c r="H101" s="157"/>
-      <c r="I101" s="157"/>
-      <c r="J101" s="157"/>
-      <c r="K101" s="155"/>
-      <c r="L101" s="154"/>
-      <c r="M101" s="155"/>
+      <c r="E101" s="153"/>
+      <c r="F101" s="156"/>
+      <c r="G101" s="156"/>
+      <c r="H101" s="156"/>
+      <c r="I101" s="156"/>
+      <c r="J101" s="156"/>
+      <c r="K101" s="154"/>
+      <c r="L101" s="153"/>
+      <c r="M101" s="154"/>
     </row>
     <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="154"/>
-      <c r="F102" s="157"/>
-      <c r="G102" s="157"/>
-      <c r="H102" s="157"/>
-      <c r="I102" s="157"/>
-      <c r="J102" s="157"/>
-      <c r="K102" s="155"/>
-      <c r="L102" s="165"/>
-      <c r="M102" s="166"/>
+      <c r="E102" s="153"/>
+      <c r="F102" s="156"/>
+      <c r="G102" s="156"/>
+      <c r="H102" s="156"/>
+      <c r="I102" s="156"/>
+      <c r="J102" s="156"/>
+      <c r="K102" s="154"/>
+      <c r="L102" s="164"/>
+      <c r="M102" s="165"/>
     </row>
     <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="192" t="s">
+      <c r="E103" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="193"/>
-      <c r="G103" s="193"/>
-      <c r="H103" s="193"/>
-      <c r="I103" s="193"/>
-      <c r="J103" s="194">
+      <c r="F103" s="198"/>
+      <c r="G103" s="198"/>
+      <c r="H103" s="198"/>
+      <c r="I103" s="198"/>
+      <c r="J103" s="199">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="195"/>
-      <c r="L103" s="167"/>
-      <c r="M103" s="168"/>
+      <c r="K103" s="192"/>
+      <c r="L103" s="166"/>
+      <c r="M103" s="167"/>
     </row>
     <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="196" t="s">
+      <c r="E108" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="197"/>
-      <c r="G108" s="197"/>
-      <c r="H108" s="197"/>
-      <c r="I108" s="197"/>
-      <c r="J108" s="197"/>
-      <c r="K108" s="195"/>
-      <c r="L108" s="152"/>
-      <c r="M108" s="153"/>
+      <c r="F108" s="191"/>
+      <c r="G108" s="191"/>
+      <c r="H108" s="191"/>
+      <c r="I108" s="191"/>
+      <c r="J108" s="191"/>
+      <c r="K108" s="192"/>
+      <c r="L108" s="151"/>
+      <c r="M108" s="152"/>
     </row>
     <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="198" t="s">
+      <c r="E109" s="193" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="197"/>
-      <c r="G109" s="197"/>
-      <c r="H109" s="197"/>
-      <c r="I109" s="197"/>
-      <c r="J109" s="197"/>
-      <c r="K109" s="195"/>
-      <c r="L109" s="154"/>
-      <c r="M109" s="155"/>
+      <c r="F109" s="191"/>
+      <c r="G109" s="191"/>
+      <c r="H109" s="191"/>
+      <c r="I109" s="191"/>
+      <c r="J109" s="191"/>
+      <c r="K109" s="192"/>
+      <c r="L109" s="153"/>
+      <c r="M109" s="154"/>
     </row>
     <row r="110" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E110" s="152"/>
-      <c r="F110" s="156"/>
-      <c r="G110" s="156"/>
-      <c r="H110" s="156"/>
-      <c r="I110" s="157"/>
-      <c r="J110" s="157">
+      <c r="E110" s="151"/>
+      <c r="F110" s="155"/>
+      <c r="G110" s="155"/>
+      <c r="H110" s="155"/>
+      <c r="I110" s="156"/>
+      <c r="J110" s="156">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K110" s="155"/>
-      <c r="L110" s="154"/>
-      <c r="M110" s="155"/>
+      <c r="K110" s="154"/>
+      <c r="L110" s="153"/>
+      <c r="M110" s="154"/>
     </row>
     <row r="111" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E111" s="154" t="s">
+      <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
-      <c r="F111" s="157"/>
-      <c r="G111" s="157"/>
-      <c r="H111" s="157"/>
-      <c r="I111" s="157"/>
-      <c r="J111" s="157"/>
-      <c r="K111" s="155"/>
-      <c r="L111" s="154"/>
-      <c r="M111" s="155"/>
+      <c r="F111" s="156"/>
+      <c r="G111" s="156"/>
+      <c r="H111" s="156"/>
+      <c r="I111" s="156"/>
+      <c r="J111" s="156"/>
+      <c r="K111" s="154"/>
+      <c r="L111" s="153"/>
+      <c r="M111" s="154"/>
     </row>
     <row r="112" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E112" s="158"/>
-      <c r="F112" s="159"/>
-      <c r="G112" s="159"/>
-      <c r="H112" s="159"/>
-      <c r="I112" s="159"/>
-      <c r="J112" s="159"/>
-      <c r="K112" s="160"/>
-      <c r="L112" s="154"/>
-      <c r="M112" s="155"/>
+      <c r="E112" s="157"/>
+      <c r="F112" s="158"/>
+      <c r="G112" s="158"/>
+      <c r="H112" s="158"/>
+      <c r="I112" s="158"/>
+      <c r="J112" s="158"/>
+      <c r="K112" s="159"/>
+      <c r="L112" s="153"/>
+      <c r="M112" s="154"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="199" t="s">
+      <c r="E113" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="200"/>
-      <c r="G113" s="200"/>
-      <c r="H113" s="200"/>
-      <c r="I113" s="200"/>
-      <c r="J113" s="200"/>
-      <c r="K113" s="201"/>
-      <c r="L113" s="154"/>
-      <c r="M113" s="155"/>
+      <c r="F113" s="195"/>
+      <c r="G113" s="195"/>
+      <c r="H113" s="195"/>
+      <c r="I113" s="195"/>
+      <c r="J113" s="195"/>
+      <c r="K113" s="196"/>
+      <c r="L113" s="153"/>
+      <c r="M113" s="154"/>
     </row>
     <row r="114" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E114" s="154"/>
-      <c r="F114" s="157"/>
-      <c r="G114" s="157"/>
-      <c r="H114" s="157"/>
-      <c r="I114" s="157"/>
-      <c r="J114" s="157"/>
-      <c r="K114" s="155"/>
-      <c r="L114" s="154"/>
-      <c r="M114" s="155"/>
+      <c r="E114" s="153"/>
+      <c r="F114" s="156"/>
+      <c r="G114" s="156"/>
+      <c r="H114" s="156"/>
+      <c r="I114" s="156"/>
+      <c r="J114" s="156"/>
+      <c r="K114" s="154"/>
+      <c r="L114" s="153"/>
+      <c r="M114" s="154"/>
     </row>
     <row r="115" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E115" s="154" t="s">
+      <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="F115" s="157"/>
-      <c r="G115" s="162" t="str">
+      <c r="F115" s="156"/>
+      <c r="G115" s="161" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="157"/>
-      <c r="I115" s="157" t="s">
+      <c r="H115" s="156"/>
+      <c r="I115" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="J115" s="161">
+      <c r="J115" s="160">
         <v>45674</v>
       </c>
-      <c r="K115" s="155"/>
-      <c r="L115" s="183" t="s">
+      <c r="K115" s="154"/>
+      <c r="L115" s="179" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="184"/>
+      <c r="M115" s="180"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E116" s="154" t="s">
+      <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="F116" s="162">
+      <c r="F116" s="161">
         <v>1</v>
       </c>
-      <c r="G116" s="157"/>
-      <c r="H116" s="157"/>
-      <c r="I116" s="157"/>
-      <c r="J116" s="157"/>
-      <c r="K116" s="155"/>
-      <c r="L116" s="154"/>
-      <c r="M116" s="155"/>
+      <c r="G116" s="156"/>
+      <c r="H116" s="156"/>
+      <c r="I116" s="156"/>
+      <c r="J116" s="156"/>
+      <c r="K116" s="154"/>
+      <c r="L116" s="153"/>
+      <c r="M116" s="154"/>
     </row>
     <row r="117" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E117" s="154"/>
-      <c r="F117" s="157"/>
-      <c r="G117" s="157"/>
-      <c r="H117" s="157"/>
-      <c r="I117" s="157"/>
-      <c r="J117" s="157"/>
-      <c r="K117" s="155"/>
-      <c r="L117" s="185"/>
-      <c r="M117" s="184"/>
+      <c r="E117" s="153"/>
+      <c r="F117" s="156"/>
+      <c r="G117" s="156"/>
+      <c r="H117" s="156"/>
+      <c r="I117" s="156"/>
+      <c r="J117" s="156"/>
+      <c r="K117" s="154"/>
+      <c r="L117" s="181"/>
+      <c r="M117" s="180"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E118" s="154" t="s">
+      <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="157"/>
-      <c r="G118" s="157"/>
-      <c r="H118" s="157"/>
-      <c r="I118" s="157"/>
-      <c r="J118" s="163">
+      <c r="F118" s="156"/>
+      <c r="G118" s="156"/>
+      <c r="H118" s="156"/>
+      <c r="I118" s="156"/>
+      <c r="J118" s="162">
         <f>J5</f>
         <v>0</v>
       </c>
-      <c r="K118" s="155"/>
-      <c r="L118" s="154"/>
-      <c r="M118" s="155"/>
+      <c r="K118" s="154"/>
+      <c r="L118" s="153"/>
+      <c r="M118" s="154"/>
     </row>
     <row r="119" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E119" s="164" t="s">
+      <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="F119" s="157"/>
-      <c r="G119" s="157"/>
-      <c r="H119" s="157"/>
-      <c r="I119" s="157"/>
-      <c r="J119" s="163">
+      <c r="F119" s="156"/>
+      <c r="G119" s="156"/>
+      <c r="H119" s="156"/>
+      <c r="I119" s="156"/>
+      <c r="J119" s="162">
         <f>K5</f>
         <v>110400</v>
       </c>
-      <c r="K119" s="155"/>
-      <c r="L119" s="154"/>
-      <c r="M119" s="155"/>
+      <c r="K119" s="154"/>
+      <c r="L119" s="153"/>
+      <c r="M119" s="154"/>
     </row>
     <row r="120" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E120" s="164" t="s">
+      <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="157"/>
-      <c r="G120" s="157"/>
-      <c r="H120" s="157"/>
-      <c r="I120" s="157"/>
-      <c r="J120" s="163">
+      <c r="F120" s="156"/>
+      <c r="G120" s="156"/>
+      <c r="H120" s="156"/>
+      <c r="I120" s="156"/>
+      <c r="J120" s="162">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="155"/>
-      <c r="L120" s="154"/>
-      <c r="M120" s="155"/>
+      <c r="K120" s="154"/>
+      <c r="L120" s="153"/>
+      <c r="M120" s="154"/>
     </row>
     <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E121" s="164"/>
-      <c r="F121" s="157"/>
-      <c r="G121" s="157"/>
-      <c r="H121" s="157"/>
-      <c r="I121" s="157"/>
-      <c r="J121" s="163"/>
-      <c r="K121" s="155"/>
-      <c r="L121" s="154"/>
-      <c r="M121" s="155"/>
+      <c r="E121" s="163"/>
+      <c r="F121" s="156"/>
+      <c r="G121" s="156"/>
+      <c r="H121" s="156"/>
+      <c r="I121" s="156"/>
+      <c r="J121" s="162"/>
+      <c r="K121" s="154"/>
+      <c r="L121" s="153"/>
+      <c r="M121" s="154"/>
     </row>
     <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E122" s="164"/>
-      <c r="F122" s="157"/>
-      <c r="G122" s="157"/>
-      <c r="H122" s="157"/>
-      <c r="I122" s="157"/>
-      <c r="J122" s="163"/>
-      <c r="K122" s="155"/>
-      <c r="L122" s="154"/>
-      <c r="M122" s="155"/>
+      <c r="E122" s="163"/>
+      <c r="F122" s="156"/>
+      <c r="G122" s="156"/>
+      <c r="H122" s="156"/>
+      <c r="I122" s="156"/>
+      <c r="J122" s="162"/>
+      <c r="K122" s="154"/>
+      <c r="L122" s="153"/>
+      <c r="M122" s="154"/>
     </row>
     <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F123" s="157"/>
-      <c r="G123" s="157"/>
-      <c r="H123" s="157"/>
-      <c r="I123" s="157"/>
-      <c r="J123" s="163"/>
-      <c r="K123" s="155"/>
-      <c r="L123" s="154"/>
-      <c r="M123" s="155"/>
+      <c r="F123" s="156"/>
+      <c r="G123" s="156"/>
+      <c r="H123" s="156"/>
+      <c r="I123" s="156"/>
+      <c r="J123" s="162"/>
+      <c r="K123" s="154"/>
+      <c r="L123" s="153"/>
+      <c r="M123" s="154"/>
     </row>
     <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E124" s="164"/>
-      <c r="F124" s="157"/>
-      <c r="G124" s="157"/>
-      <c r="H124" s="157"/>
-      <c r="I124" s="157"/>
-      <c r="J124" s="163"/>
-      <c r="K124" s="155"/>
-      <c r="L124" s="154"/>
-      <c r="M124" s="155"/>
+      <c r="E124" s="163"/>
+      <c r="F124" s="156"/>
+      <c r="G124" s="156"/>
+      <c r="H124" s="156"/>
+      <c r="I124" s="156"/>
+      <c r="J124" s="162"/>
+      <c r="K124" s="154"/>
+      <c r="L124" s="153"/>
+      <c r="M124" s="154"/>
     </row>
     <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E125" s="154"/>
-      <c r="F125" s="157"/>
-      <c r="G125" s="157"/>
-      <c r="H125" s="157"/>
-      <c r="I125" s="157"/>
-      <c r="J125" s="157"/>
-      <c r="K125" s="155"/>
-      <c r="L125" s="154"/>
-      <c r="M125" s="155"/>
+      <c r="E125" s="153"/>
+      <c r="F125" s="156"/>
+      <c r="G125" s="156"/>
+      <c r="H125" s="156"/>
+      <c r="I125" s="156"/>
+      <c r="J125" s="156"/>
+      <c r="K125" s="154"/>
+      <c r="L125" s="153"/>
+      <c r="M125" s="154"/>
     </row>
     <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E126" s="154"/>
-      <c r="F126" s="157"/>
-      <c r="G126" s="157"/>
-      <c r="H126" s="157"/>
-      <c r="I126" s="157"/>
-      <c r="J126" s="157"/>
-      <c r="K126" s="155"/>
-      <c r="L126" s="154"/>
-      <c r="M126" s="155"/>
+      <c r="E126" s="153"/>
+      <c r="F126" s="156"/>
+      <c r="G126" s="156"/>
+      <c r="H126" s="156"/>
+      <c r="I126" s="156"/>
+      <c r="J126" s="156"/>
+      <c r="K126" s="154"/>
+      <c r="L126" s="153"/>
+      <c r="M126" s="154"/>
     </row>
     <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E127" s="154"/>
-      <c r="F127" s="157"/>
-      <c r="G127" s="157"/>
-      <c r="H127" s="157"/>
-      <c r="I127" s="157"/>
-      <c r="J127" s="157"/>
-      <c r="K127" s="155"/>
-      <c r="L127" s="165"/>
-      <c r="M127" s="166"/>
+      <c r="E127" s="153"/>
+      <c r="F127" s="156"/>
+      <c r="G127" s="156"/>
+      <c r="H127" s="156"/>
+      <c r="I127" s="156"/>
+      <c r="J127" s="156"/>
+      <c r="K127" s="154"/>
+      <c r="L127" s="164"/>
+      <c r="M127" s="165"/>
     </row>
     <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="192" t="s">
+      <c r="E128" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="193"/>
-      <c r="G128" s="193"/>
-      <c r="H128" s="193"/>
-      <c r="I128" s="193"/>
-      <c r="J128" s="194">
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="198"/>
+      <c r="I128" s="198"/>
+      <c r="J128" s="199">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="195"/>
-      <c r="L128" s="167"/>
-      <c r="M128" s="168"/>
+      <c r="K128" s="192"/>
+      <c r="L128" s="166"/>
+      <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="50">

--- a/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
+++ b/PATXOT 512/Noviembre/PATXOT 521 Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C405EBA-D93E-4BE8-A346-92F452FDD0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE29784-E5A6-4D73-AF21-2A241D714E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1452,7 +1452,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1722,12 +1722,37 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1740,11 +1765,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1769,26 +1789,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1805,12 +1810,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1820,14 +1819,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2198,16 +2195,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2215,114 +2212,114 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="168" t="s">
         <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
         <v>135</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="211">
+      <c r="C17" s="173">
         <v>86076.01</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="212">
+      <c r="C18" s="174">
         <f>SUM(C17:C17)</f>
         <v>86076.01</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
-      <c r="C19" s="213"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="75" t="s">
         <v>133</v>
       </c>
       <c r="B20" s="90"/>
-      <c r="C20" s="214">
+      <c r="C20" s="175">
         <v>37000</v>
       </c>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="75" t="s">
         <v>134</v>
       </c>
       <c r="B21" s="90"/>
-      <c r="C21" s="214">
+      <c r="C21" s="175">
         <v>36534.6</v>
       </c>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="75" t="s">
         <v>124</v>
       </c>
@@ -2332,7 +2329,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="88"/>
       <c r="B23" s="89"/>
       <c r="C23" s="60">
@@ -2341,7 +2338,7 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
         <v>78</v>
       </c>
@@ -2352,40 +2349,40 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C25" s="61"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="61"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="75"/>
       <c r="B27" s="75"/>
       <c r="C27" s="84"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="75"/>
       <c r="B28" s="75"/>
       <c r="C28" s="85"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="75"/>
       <c r="B29" s="75"/>
       <c r="C29" s="85"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="63"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -2396,7 +2393,7 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>15</v>
       </c>
@@ -2406,15 +2403,15 @@
         <v>159610.60999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="145" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="146"/>
       <c r="C35" s="147"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="143" t="s">
         <v>10</v>
       </c>
@@ -2425,7 +2422,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2436,7 +2433,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -2446,7 +2443,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -2455,7 +2452,7 @@
         <v>-159610.60999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>16</v>
       </c>
@@ -2466,23 +2463,23 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19"/>
       <c r="B41" s="18"/>
       <c r="C41" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
       <c r="F42" s="93"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="19"/>
       <c r="B43" s="18"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="73" t="s">
         <v>57</v>
       </c>
@@ -2491,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="75" t="s">
         <v>63</v>
       </c>
@@ -2501,17 +2498,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="75"/>
       <c r="B46" s="75"/>
       <c r="C46" s="82"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="83"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="79" t="s">
         <v>4</v>
       </c>
@@ -2521,22 +2518,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -2558,39 +2555,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="14">
         <v>159610.60999999999</v>
       </c>
-      <c r="H1" s="200" t="s">
+      <c r="H1" s="176" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="200"/>
+      <c r="I1" s="176"/>
       <c r="J1" s="14">
         <v>172630.83</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2607,15 +2604,15 @@
       <c r="K2" s="100"/>
       <c r="L2" s="101"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="184" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="177" t="s">
+      <c r="B3" s="197"/>
+      <c r="C3" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="182" t="s">
+      <c r="D3" s="194" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2624,52 +2621,52 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="177" t="s">
+      <c r="G3" s="192" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="173" t="s">
+      <c r="I3" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="188" t="s">
+      <c r="J3" s="200" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="177" t="s">
+      <c r="K3" s="192" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="186"/>
-      <c r="B4" s="187"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="183"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="198"/>
+      <c r="B4" s="199"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="195"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="178"/>
+      <c r="G4" s="193"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="174"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="178"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="190">
         <v>1</v>
       </c>
-      <c r="B5" s="176"/>
+      <c r="B5" s="191"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
@@ -2705,11 +2702,11 @@
         <v>45849.318719999996</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="175">
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="190">
         <v>2</v>
       </c>
-      <c r="B6" s="176"/>
+      <c r="B6" s="191"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
@@ -2747,11 +2744,11 @@
         <v>39403.834783999991</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="175">
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="190">
         <v>3</v>
       </c>
-      <c r="B7" s="176"/>
+      <c r="B7" s="191"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
@@ -2789,11 +2786,11 @@
         <v>41397.283423999994</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="175">
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="190">
         <v>4</v>
       </c>
-      <c r="B8" s="176"/>
+      <c r="B8" s="191"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
@@ -2831,11 +2828,11 @@
         <v>49005.612399999998</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="175">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="190">
         <v>5</v>
       </c>
-      <c r="B9" s="176"/>
+      <c r="B9" s="191"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
@@ -2873,11 +2870,11 @@
         <v>41231.162704000002</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="175">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="190">
         <v>6</v>
       </c>
-      <c r="B10" s="176"/>
+      <c r="B10" s="191"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
@@ -2913,11 +2910,11 @@
         <v>41463.731711999993</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="175">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="190">
         <v>7</v>
       </c>
-      <c r="B11" s="176"/>
+      <c r="B11" s="191"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
@@ -2953,11 +2950,11 @@
         <v>60667.286943999999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="175" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="190" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="176"/>
+      <c r="B12" s="191"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2994,11 +2991,11 @@
         <v>4452.035296</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="175" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="190" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="176"/>
+      <c r="B13" s="191"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3035,11 +3032,11 @@
         <v>4385.5870080000004</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="175" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="190" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="176"/>
+      <c r="B14" s="191"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3076,7 +3073,7 @@
         <v>4385.5870080000004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
@@ -3113,7 +3110,7 @@
         <v>332241.44</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -3121,7 +3118,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -3139,7 +3136,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3171,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3197,7 +3194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3231,7 +3228,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3265,7 +3262,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3300,7 +3297,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3331,7 +3328,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3362,7 +3359,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3393,7 +3390,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3427,7 +3424,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3461,7 +3458,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3494,44 +3491,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="190" t="s">
+      <c r="E32" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="191"/>
-      <c r="G32" s="191"/>
-      <c r="H32" s="191"/>
-      <c r="I32" s="191"/>
-      <c r="J32" s="191"/>
-      <c r="K32" s="192"/>
+      <c r="F32" s="182"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="180"/>
       <c r="L32" s="151"/>
       <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="193" t="s">
+      <c r="E33" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="191"/>
-      <c r="G33" s="191"/>
-      <c r="H33" s="191"/>
-      <c r="I33" s="191"/>
-      <c r="J33" s="191"/>
-      <c r="K33" s="192"/>
+      <c r="F33" s="182"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="182"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="180"/>
       <c r="L33" s="153"/>
       <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="151"/>
@@ -3548,7 +3545,7 @@
       <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="153" t="s">
@@ -3564,7 +3561,7 @@
       <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="157"/>
@@ -3578,23 +3575,23 @@
       <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="194" t="s">
+      <c r="E37" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
-      <c r="I37" s="195"/>
-      <c r="J37" s="195"/>
-      <c r="K37" s="196"/>
+      <c r="F37" s="185"/>
+      <c r="G37" s="185"/>
+      <c r="H37" s="185"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="186"/>
       <c r="L37" s="153"/>
       <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="153"/>
@@ -3608,7 +3605,7 @@
       <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="153" t="s">
@@ -3627,13 +3624,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="154"/>
-      <c r="L39" s="179" t="s">
+      <c r="L39" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="180"/>
+      <c r="M39" s="188"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="153" t="s">
@@ -3651,7 +3648,7 @@
       <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="153"/>
@@ -3661,11 +3658,11 @@
       <c r="I41" s="156"/>
       <c r="J41" s="156"/>
       <c r="K41" s="154"/>
-      <c r="L41" s="181"/>
-      <c r="M41" s="180"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="188"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="153" t="s">
@@ -3684,7 +3681,7 @@
       <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="163" t="s">
@@ -3703,7 +3700,7 @@
       <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="163" t="s">
@@ -3722,7 +3719,7 @@
       <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="163"/>
@@ -3736,7 +3733,7 @@
       <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="163"/>
@@ -3750,7 +3747,7 @@
       <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="156"/>
@@ -3763,7 +3760,7 @@
       <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="163"/>
@@ -3777,7 +3774,7 @@
       <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="153"/>
@@ -3791,7 +3788,7 @@
       <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="153" t="s">
@@ -3810,7 +3807,7 @@
       <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="153"/>
@@ -3824,58 +3821,58 @@
       <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="197" t="s">
+      <c r="E52" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="199">
+      <c r="F52" s="178"/>
+      <c r="G52" s="178"/>
+      <c r="H52" s="178"/>
+      <c r="I52" s="178"/>
+      <c r="J52" s="179">
         <f>SUM(J42:J51)</f>
         <v>41473.083423999997</v>
       </c>
-      <c r="K52" s="192"/>
+      <c r="K52" s="180"/>
       <c r="L52" s="166"/>
       <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="190" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="191"/>
-      <c r="G56" s="191"/>
-      <c r="H56" s="191"/>
-      <c r="I56" s="191"/>
-      <c r="J56" s="191"/>
-      <c r="K56" s="192"/>
+      <c r="F56" s="182"/>
+      <c r="G56" s="182"/>
+      <c r="H56" s="182"/>
+      <c r="I56" s="182"/>
+      <c r="J56" s="182"/>
+      <c r="K56" s="180"/>
       <c r="L56" s="151"/>
       <c r="M56" s="152"/>
     </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="193" t="s">
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="191"/>
-      <c r="G57" s="191"/>
-      <c r="H57" s="191"/>
-      <c r="I57" s="191"/>
-      <c r="J57" s="191"/>
-      <c r="K57" s="192"/>
+      <c r="F57" s="182"/>
+      <c r="G57" s="182"/>
+      <c r="H57" s="182"/>
+      <c r="I57" s="182"/>
+      <c r="J57" s="182"/>
+      <c r="K57" s="180"/>
       <c r="L57" s="153"/>
       <c r="M57" s="154"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E58" s="151"/>
       <c r="F58" s="155"/>
       <c r="G58" s="155"/>
@@ -3889,7 +3886,7 @@
       <c r="L58" s="153"/>
       <c r="M58" s="154"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
@@ -3902,7 +3899,7 @@
       <c r="L59" s="153"/>
       <c r="M59" s="154"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E60" s="157"/>
       <c r="F60" s="158"/>
       <c r="G60" s="158"/>
@@ -3913,20 +3910,20 @@
       <c r="L60" s="153"/>
       <c r="M60" s="154"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="194" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="195"/>
-      <c r="G61" s="195"/>
-      <c r="H61" s="195"/>
-      <c r="I61" s="195"/>
-      <c r="J61" s="195"/>
-      <c r="K61" s="196"/>
+      <c r="F61" s="185"/>
+      <c r="G61" s="185"/>
+      <c r="H61" s="185"/>
+      <c r="I61" s="185"/>
+      <c r="J61" s="185"/>
+      <c r="K61" s="186"/>
       <c r="L61" s="153"/>
       <c r="M61" s="154"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E62" s="153"/>
       <c r="F62" s="156"/>
       <c r="G62" s="156"/>
@@ -3937,7 +3934,7 @@
       <c r="L62" s="153"/>
       <c r="M62" s="154"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
@@ -3954,12 +3951,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="154"/>
-      <c r="L63" s="179" t="s">
+      <c r="L63" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="180"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="188"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
@@ -3974,7 +3971,7 @@
       <c r="L64" s="153"/>
       <c r="M64" s="154"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E65" s="153"/>
       <c r="F65" s="156"/>
       <c r="G65" s="156"/>
@@ -3982,10 +3979,10 @@
       <c r="I65" s="156"/>
       <c r="J65" s="156"/>
       <c r="K65" s="154"/>
-      <c r="L65" s="181"/>
-      <c r="M65" s="180"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="189"/>
+      <c r="M65" s="188"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
@@ -4001,7 +3998,7 @@
       <c r="L66" s="153"/>
       <c r="M66" s="154"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
@@ -4017,7 +4014,7 @@
       <c r="L67" s="153"/>
       <c r="M67" s="154"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
@@ -4033,7 +4030,7 @@
       <c r="L68" s="153"/>
       <c r="M68" s="154"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E69" s="163"/>
       <c r="F69" s="156"/>
       <c r="G69" s="156"/>
@@ -4044,7 +4041,7 @@
       <c r="L69" s="153"/>
       <c r="M69" s="154"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E70" s="163"/>
       <c r="F70" s="156"/>
       <c r="G70" s="156"/>
@@ -4055,7 +4052,7 @@
       <c r="L70" s="153"/>
       <c r="M70" s="154"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="F71" s="156"/>
       <c r="G71" s="156"/>
       <c r="H71" s="156"/>
@@ -4065,7 +4062,7 @@
       <c r="L71" s="153"/>
       <c r="M71" s="154"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E72" s="163"/>
       <c r="F72" s="156"/>
       <c r="G72" s="156"/>
@@ -4076,7 +4073,7 @@
       <c r="L72" s="153"/>
       <c r="M72" s="154"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E73" s="153"/>
       <c r="F73" s="156"/>
       <c r="G73" s="156"/>
@@ -4087,7 +4084,7 @@
       <c r="L73" s="153"/>
       <c r="M73" s="154"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E74" s="153"/>
       <c r="F74" s="156"/>
       <c r="G74" s="156"/>
@@ -4098,7 +4095,7 @@
       <c r="L74" s="153"/>
       <c r="M74" s="154"/>
     </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="153"/>
       <c r="F75" s="156"/>
       <c r="G75" s="156"/>
@@ -4109,50 +4106,50 @@
       <c r="L75" s="164"/>
       <c r="M75" s="165"/>
     </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="197" t="s">
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="198"/>
-      <c r="G76" s="198"/>
-      <c r="H76" s="198"/>
-      <c r="I76" s="198"/>
-      <c r="J76" s="199">
+      <c r="F76" s="178"/>
+      <c r="G76" s="178"/>
+      <c r="H76" s="178"/>
+      <c r="I76" s="178"/>
+      <c r="J76" s="179">
         <f>SUM(J66:J75)</f>
         <v>49005.612399999998</v>
       </c>
-      <c r="K76" s="192"/>
+      <c r="K76" s="180"/>
       <c r="L76" s="166"/>
       <c r="M76" s="167"/>
     </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="190" t="s">
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="191"/>
-      <c r="G83" s="191"/>
-      <c r="H83" s="191"/>
-      <c r="I83" s="191"/>
-      <c r="J83" s="191"/>
-      <c r="K83" s="192"/>
+      <c r="F83" s="182"/>
+      <c r="G83" s="182"/>
+      <c r="H83" s="182"/>
+      <c r="I83" s="182"/>
+      <c r="J83" s="182"/>
+      <c r="K83" s="180"/>
       <c r="L83" s="151"/>
       <c r="M83" s="152"/>
     </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="193" t="s">
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="191"/>
-      <c r="G84" s="191"/>
-      <c r="H84" s="191"/>
-      <c r="I84" s="191"/>
-      <c r="J84" s="191"/>
-      <c r="K84" s="192"/>
+      <c r="F84" s="182"/>
+      <c r="G84" s="182"/>
+      <c r="H84" s="182"/>
+      <c r="I84" s="182"/>
+      <c r="J84" s="182"/>
+      <c r="K84" s="180"/>
       <c r="L84" s="153"/>
       <c r="M84" s="154"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E85" s="151"/>
       <c r="F85" s="155"/>
       <c r="G85" s="155"/>
@@ -4166,7 +4163,7 @@
       <c r="L85" s="153"/>
       <c r="M85" s="154"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
@@ -4179,7 +4176,7 @@
       <c r="L86" s="153"/>
       <c r="M86" s="154"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E87" s="157"/>
       <c r="F87" s="158"/>
       <c r="G87" s="158"/>
@@ -4190,20 +4187,20 @@
       <c r="L87" s="153"/>
       <c r="M87" s="154"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="194" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="195"/>
-      <c r="G88" s="195"/>
-      <c r="H88" s="195"/>
-      <c r="I88" s="195"/>
-      <c r="J88" s="195"/>
-      <c r="K88" s="196"/>
+      <c r="F88" s="185"/>
+      <c r="G88" s="185"/>
+      <c r="H88" s="185"/>
+      <c r="I88" s="185"/>
+      <c r="J88" s="185"/>
+      <c r="K88" s="186"/>
       <c r="L88" s="153"/>
       <c r="M88" s="154"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E89" s="153"/>
       <c r="F89" s="156"/>
       <c r="G89" s="156"/>
@@ -4214,7 +4211,7 @@
       <c r="L89" s="153"/>
       <c r="M89" s="154"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
@@ -4231,12 +4228,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="154"/>
-      <c r="L90" s="179" t="s">
+      <c r="L90" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="180"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M90" s="188"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
@@ -4251,7 +4248,7 @@
       <c r="L91" s="153"/>
       <c r="M91" s="154"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E92" s="153"/>
       <c r="F92" s="156"/>
       <c r="G92" s="156"/>
@@ -4259,10 +4256,10 @@
       <c r="I92" s="156"/>
       <c r="J92" s="156"/>
       <c r="K92" s="154"/>
-      <c r="L92" s="181"/>
-      <c r="M92" s="180"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="189"/>
+      <c r="M92" s="188"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
@@ -4278,7 +4275,7 @@
       <c r="L93" s="153"/>
       <c r="M93" s="154"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
@@ -4294,7 +4291,7 @@
       <c r="L94" s="153"/>
       <c r="M94" s="154"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
@@ -4309,7 +4306,7 @@
       <c r="L95" s="153"/>
       <c r="M95" s="154"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E96" s="163"/>
       <c r="F96" s="156"/>
       <c r="G96" s="156"/>
@@ -4320,7 +4317,7 @@
       <c r="L96" s="153"/>
       <c r="M96" s="154"/>
     </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="163"/>
       <c r="F97" s="156"/>
       <c r="G97" s="156"/>
@@ -4331,7 +4328,7 @@
       <c r="L97" s="153"/>
       <c r="M97" s="154"/>
     </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F98" s="156"/>
       <c r="G98" s="156"/>
       <c r="H98" s="156"/>
@@ -4341,7 +4338,7 @@
       <c r="L98" s="153"/>
       <c r="M98" s="154"/>
     </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="163"/>
       <c r="F99" s="156"/>
       <c r="G99" s="156"/>
@@ -4352,7 +4349,7 @@
       <c r="L99" s="153"/>
       <c r="M99" s="154"/>
     </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E100" s="153"/>
       <c r="F100" s="156"/>
       <c r="G100" s="156"/>
@@ -4363,7 +4360,7 @@
       <c r="L100" s="153"/>
       <c r="M100" s="154"/>
     </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E101" s="153"/>
       <c r="F101" s="156"/>
       <c r="G101" s="156"/>
@@ -4374,7 +4371,7 @@
       <c r="L101" s="153"/>
       <c r="M101" s="154"/>
     </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E102" s="153"/>
       <c r="F102" s="156"/>
       <c r="G102" s="156"/>
@@ -4385,50 +4382,50 @@
       <c r="L102" s="164"/>
       <c r="M102" s="165"/>
     </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="197" t="s">
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="198"/>
-      <c r="G103" s="198"/>
-      <c r="H103" s="198"/>
-      <c r="I103" s="198"/>
-      <c r="J103" s="199">
+      <c r="F103" s="178"/>
+      <c r="G103" s="178"/>
+      <c r="H103" s="178"/>
+      <c r="I103" s="178"/>
+      <c r="J103" s="179">
         <f>SUM(J93:J102)</f>
         <v>41487.621711999993</v>
       </c>
-      <c r="K103" s="192"/>
+      <c r="K103" s="180"/>
       <c r="L103" s="166"/>
       <c r="M103" s="167"/>
     </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="190" t="s">
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="191"/>
-      <c r="G108" s="191"/>
-      <c r="H108" s="191"/>
-      <c r="I108" s="191"/>
-      <c r="J108" s="191"/>
-      <c r="K108" s="192"/>
+      <c r="F108" s="182"/>
+      <c r="G108" s="182"/>
+      <c r="H108" s="182"/>
+      <c r="I108" s="182"/>
+      <c r="J108" s="182"/>
+      <c r="K108" s="180"/>
       <c r="L108" s="151"/>
       <c r="M108" s="152"/>
     </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="193" t="s">
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="191"/>
-      <c r="G109" s="191"/>
-      <c r="H109" s="191"/>
-      <c r="I109" s="191"/>
-      <c r="J109" s="191"/>
-      <c r="K109" s="192"/>
+      <c r="F109" s="182"/>
+      <c r="G109" s="182"/>
+      <c r="H109" s="182"/>
+      <c r="I109" s="182"/>
+      <c r="J109" s="182"/>
+      <c r="K109" s="180"/>
       <c r="L109" s="153"/>
       <c r="M109" s="154"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E110" s="151"/>
       <c r="F110" s="155"/>
       <c r="G110" s="155"/>
@@ -4442,7 +4439,7 @@
       <c r="L110" s="153"/>
       <c r="M110" s="154"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
@@ -4455,7 +4452,7 @@
       <c r="L111" s="153"/>
       <c r="M111" s="154"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E112" s="157"/>
       <c r="F112" s="158"/>
       <c r="G112" s="158"/>
@@ -4466,20 +4463,20 @@
       <c r="L112" s="153"/>
       <c r="M112" s="154"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="194" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="195"/>
-      <c r="G113" s="195"/>
-      <c r="H113" s="195"/>
-      <c r="I113" s="195"/>
-      <c r="J113" s="195"/>
-      <c r="K113" s="196"/>
+      <c r="F113" s="185"/>
+      <c r="G113" s="185"/>
+      <c r="H113" s="185"/>
+      <c r="I113" s="185"/>
+      <c r="J113" s="185"/>
+      <c r="K113" s="186"/>
       <c r="L113" s="153"/>
       <c r="M113" s="154"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E114" s="153"/>
       <c r="F114" s="156"/>
       <c r="G114" s="156"/>
@@ -4490,7 +4487,7 @@
       <c r="L114" s="153"/>
       <c r="M114" s="154"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
@@ -4507,12 +4504,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="154"/>
-      <c r="L115" s="179" t="s">
+      <c r="L115" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="180"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="188"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
@@ -4527,7 +4524,7 @@
       <c r="L116" s="153"/>
       <c r="M116" s="154"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E117" s="153"/>
       <c r="F117" s="156"/>
       <c r="G117" s="156"/>
@@ -4535,10 +4532,10 @@
       <c r="I117" s="156"/>
       <c r="J117" s="156"/>
       <c r="K117" s="154"/>
-      <c r="L117" s="181"/>
-      <c r="M117" s="180"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="189"/>
+      <c r="M117" s="188"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
@@ -4554,7 +4551,7 @@
       <c r="L118" s="153"/>
       <c r="M118" s="154"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
@@ -4570,7 +4567,7 @@
       <c r="L119" s="153"/>
       <c r="M119" s="154"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
@@ -4586,7 +4583,7 @@
       <c r="L120" s="153"/>
       <c r="M120" s="154"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E121" s="163"/>
       <c r="F121" s="156"/>
       <c r="G121" s="156"/>
@@ -4597,7 +4594,7 @@
       <c r="L121" s="153"/>
       <c r="M121" s="154"/>
     </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E122" s="163"/>
       <c r="F122" s="156"/>
       <c r="G122" s="156"/>
@@ -4608,7 +4605,7 @@
       <c r="L122" s="153"/>
       <c r="M122" s="154"/>
     </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F123" s="156"/>
       <c r="G123" s="156"/>
       <c r="H123" s="156"/>
@@ -4618,7 +4615,7 @@
       <c r="L123" s="153"/>
       <c r="M123" s="154"/>
     </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E124" s="163"/>
       <c r="F124" s="156"/>
       <c r="G124" s="156"/>
@@ -4629,7 +4626,7 @@
       <c r="L124" s="153"/>
       <c r="M124" s="154"/>
     </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E125" s="153"/>
       <c r="F125" s="156"/>
       <c r="G125" s="156"/>
@@ -4640,7 +4637,7 @@
       <c r="L125" s="153"/>
       <c r="M125" s="154"/>
     </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E126" s="153"/>
       <c r="F126" s="156"/>
       <c r="G126" s="156"/>
@@ -4651,7 +4648,7 @@
       <c r="L126" s="153"/>
       <c r="M126" s="154"/>
     </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E127" s="153"/>
       <c r="F127" s="156"/>
       <c r="G127" s="156"/>
@@ -4662,24 +4659,54 @@
       <c r="L127" s="164"/>
       <c r="M127" s="165"/>
     </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="197" t="s">
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="198"/>
-      <c r="I128" s="198"/>
-      <c r="J128" s="199">
+      <c r="F128" s="178"/>
+      <c r="G128" s="178"/>
+      <c r="H128" s="178"/>
+      <c r="I128" s="178"/>
+      <c r="J128" s="179">
         <f>SUM(J118:J127)</f>
         <v>45796.978719999999</v>
       </c>
-      <c r="K128" s="192"/>
+      <c r="K128" s="180"/>
       <c r="L128" s="166"/>
       <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="E128:I128"/>
     <mergeCell ref="J128:K128"/>
@@ -4696,36 +4723,6 @@
     <mergeCell ref="E37:K37"/>
     <mergeCell ref="E76:I76"/>
     <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4736,16 +4733,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="110" t="s">
         <v>79</v>
       </c>
@@ -4765,12 +4762,12 @@
       <c r="K1" s="113"/>
       <c r="L1" s="114"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H2" s="115"/>
       <c r="I2" s="115"/>
       <c r="J2" s="115"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="116" t="s">
         <v>82</v>
       </c>
@@ -4797,7 +4794,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="118"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="116"/>
       <c r="C4" s="110" t="s">
         <v>88</v>
@@ -4814,7 +4811,7 @@
       <c r="I4" s="119"/>
       <c r="J4" s="119"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
@@ -4847,7 +4844,7 @@
       <c r="L5" s="121"/>
       <c r="M5" s="122"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -4880,7 +4877,7 @@
       <c r="L6" s="121"/>
       <c r="M6" s="122"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
@@ -4912,7 +4909,7 @@
       <c r="L7" s="121"/>
       <c r="M7" s="122"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
@@ -4945,7 +4942,7 @@
       <c r="L8" s="121"/>
       <c r="M8" s="122"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
@@ -4978,7 +4975,7 @@
       <c r="L9" s="121"/>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
@@ -5011,7 +5008,7 @@
       <c r="L10" s="121"/>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
@@ -5044,7 +5041,7 @@
       <c r="L11" s="121"/>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="124"/>
       <c r="C12" s="125">
         <f>SUM(C5:C11)</f>
@@ -5072,13 +5069,13 @@
       <c r="K12" s="124"/>
       <c r="L12" s="127"/>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="128"/>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
     </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>97</v>
       </c>
@@ -5090,7 +5087,7 @@
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>98</v>
       </c>
@@ -5098,7 +5095,7 @@
       <c r="I15" s="116"/>
       <c r="J15" s="116"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="116"/>
       <c r="C16" s="110"/>
       <c r="D16" s="110"/>
@@ -5109,7 +5106,7 @@
       <c r="J16" s="110"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="116"/>
       <c r="C17" s="110"/>
       <c r="D17" s="110"/>
@@ -5119,12 +5116,12 @@
       <c r="I17" s="119"/>
       <c r="J17" s="119"/>
     </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C19" s="130"/>
       <c r="D19" s="131"/>
       <c r="E19" s="131"/>
@@ -5137,7 +5134,7 @@
       <c r="L19" s="131"/>
       <c r="M19" s="133"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C20" s="134"/>
       <c r="E20" t="s">
         <v>99</v>
@@ -5153,7 +5150,7 @@
       </c>
       <c r="M20" s="136"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C21" s="134"/>
       <c r="D21" t="s">
         <v>101</v>
@@ -5175,7 +5172,7 @@
       </c>
       <c r="M21" s="136"/>
     </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="137"/>
       <c r="D22" s="138"/>
       <c r="E22" s="138"/>
@@ -5188,16 +5185,16 @@
       <c r="L22" s="138"/>
       <c r="M22" s="139"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K25" s="140" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G26" s="5"/>
       <c r="K26" s="118"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>105</v>
       </c>
@@ -5208,7 +5205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>95</v>
@@ -5224,7 +5221,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>107</v>
       </c>
@@ -5232,7 +5229,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>108</v>
       </c>
@@ -5240,7 +5237,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J33" s="118" t="s">
         <v>109</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
       <c r="K34" s="112">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5263,39 +5260,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="205">
+      <c r="H1" s="208">
         <v>250000</v>
       </c>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>56</v>
       </c>
@@ -5318,7 +5315,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5350,18 +5347,18 @@
         <v>53</v>
       </c>
       <c r="K4" s="67"/>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>60</v>
       </c>
       <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="201" t="s">
+      <c r="N4" s="204" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5385,14 +5382,14 @@
         <v>59</v>
       </c>
       <c r="K5" s="57"/>
-      <c r="L5" s="204"/>
+      <c r="L5" s="207"/>
       <c r="M5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="202"/>
+      <c r="N5" s="205"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5440,7 +5437,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5488,7 +5485,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5536,7 +5533,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5584,7 +5581,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5632,7 +5629,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5680,7 +5677,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5728,7 +5725,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5776,7 +5773,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5842,42 +5839,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="209" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="210" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="209" t="s">
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="210">
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="211">
         <v>800000</v>
       </c>
-      <c r="J1" s="210"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J1" s="211"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
@@ -5891,15 +5888,15 @@
       <c r="K2" s="100"/>
       <c r="L2" s="101"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="184" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="177" t="s">
+      <c r="B3" s="197"/>
+      <c r="C3" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="182" t="s">
+      <c r="D3" s="194" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5908,50 +5905,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="177" t="s">
+      <c r="G3" s="192" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="177" t="s">
+      <c r="H3" s="192" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="173" t="s">
+      <c r="I3" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="182" t="s">
+      <c r="J3" s="194" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="206" t="s">
+      <c r="L3" s="212" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="186"/>
-      <c r="B4" s="187"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="183"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="198"/>
+      <c r="B4" s="199"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="195"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="183"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="195"/>
       <c r="K4" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="207"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175">
+      <c r="L4" s="213"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="190">
         <v>1</v>
       </c>
-      <c r="B5" s="176"/>
+      <c r="B5" s="191"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
@@ -5987,11 +5984,11 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="175">
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="190">
         <v>2</v>
       </c>
-      <c r="B6" s="176"/>
+      <c r="B6" s="191"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
@@ -6029,11 +6026,11 @@
         <v>64880.003495999961</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="175">
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="190">
         <v>3</v>
       </c>
-      <c r="B7" s="176"/>
+      <c r="B7" s="191"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
@@ -6071,11 +6068,11 @@
         <v>99680</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="175">
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="190">
         <v>4</v>
       </c>
-      <c r="B8" s="176"/>
+      <c r="B8" s="191"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
@@ -6113,11 +6110,11 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="175">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="190">
         <v>5</v>
       </c>
-      <c r="B9" s="176"/>
+      <c r="B9" s="191"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
@@ -6155,11 +6152,11 @@
         <v>99279.992624999984</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="175">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="190">
         <v>6</v>
       </c>
-      <c r="B10" s="176"/>
+      <c r="B10" s="191"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
@@ -6195,11 +6192,11 @@
         <v>94999.311648000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="175">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="190">
         <v>7</v>
       </c>
-      <c r="B11" s="176"/>
+      <c r="B11" s="191"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
@@ -6235,11 +6232,11 @@
         <v>146080.00000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="175" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="190" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="176"/>
+      <c r="B12" s="191"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6276,11 +6273,11 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="175" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="190" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="176"/>
+      <c r="B13" s="191"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6317,11 +6314,11 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="175" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="190" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="176"/>
+      <c r="B14" s="191"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6358,7 +6355,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
@@ -6398,7 +6395,7 @@
         <v>765159.30776899995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -6406,7 +6403,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -6424,7 +6421,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6456,7 +6453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6482,7 +6479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6516,7 +6513,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6550,7 +6547,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6585,7 +6582,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6616,7 +6613,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6647,7 +6644,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6678,7 +6675,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6712,7 +6709,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6746,7 +6743,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -6779,44 +6776,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="190" t="s">
+      <c r="E32" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="191"/>
-      <c r="G32" s="191"/>
-      <c r="H32" s="191"/>
-      <c r="I32" s="191"/>
-      <c r="J32" s="191"/>
-      <c r="K32" s="192"/>
+      <c r="F32" s="182"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="180"/>
       <c r="L32" s="151"/>
       <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="193" t="s">
+      <c r="E33" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="191"/>
-      <c r="G33" s="191"/>
-      <c r="H33" s="191"/>
-      <c r="I33" s="191"/>
-      <c r="J33" s="191"/>
-      <c r="K33" s="192"/>
+      <c r="F33" s="182"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="182"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="180"/>
       <c r="L33" s="153"/>
       <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="151"/>
@@ -6833,7 +6830,7 @@
       <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="153" t="s">
@@ -6849,7 +6846,7 @@
       <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="157"/>
@@ -6863,23 +6860,23 @@
       <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="194" t="s">
+      <c r="E37" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
-      <c r="I37" s="195"/>
-      <c r="J37" s="195"/>
-      <c r="K37" s="196"/>
+      <c r="F37" s="185"/>
+      <c r="G37" s="185"/>
+      <c r="H37" s="185"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="186"/>
       <c r="L37" s="153"/>
       <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="153"/>
@@ -6893,7 +6890,7 @@
       <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="153" t="s">
@@ -6912,13 +6909,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="154"/>
-      <c r="L39" s="179" t="s">
+      <c r="L39" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="180"/>
+      <c r="M39" s="188"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="153" t="s">
@@ -6936,7 +6933,7 @@
       <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="153"/>
@@ -6946,11 +6943,11 @@
       <c r="I41" s="156"/>
       <c r="J41" s="156"/>
       <c r="K41" s="154"/>
-      <c r="L41" s="181"/>
-      <c r="M41" s="180"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="188"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="153" t="s">
@@ -6969,7 +6966,7 @@
       <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="163" t="s">
@@ -6988,7 +6985,7 @@
       <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="163" t="s">
@@ -7007,7 +7004,7 @@
       <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="163"/>
@@ -7021,7 +7018,7 @@
       <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="163"/>
@@ -7035,7 +7032,7 @@
       <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="156"/>
@@ -7048,7 +7045,7 @@
       <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="163"/>
@@ -7062,7 +7059,7 @@
       <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="153"/>
@@ -7076,7 +7073,7 @@
       <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="153" t="s">
@@ -7095,7 +7092,7 @@
       <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="153"/>
@@ -7109,58 +7106,58 @@
       <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="197" t="s">
+      <c r="E52" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="199">
+      <c r="F52" s="178"/>
+      <c r="G52" s="178"/>
+      <c r="H52" s="178"/>
+      <c r="I52" s="178"/>
+      <c r="J52" s="179">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="192"/>
+      <c r="K52" s="180"/>
       <c r="L52" s="166"/>
       <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="190" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="191"/>
-      <c r="G56" s="191"/>
-      <c r="H56" s="191"/>
-      <c r="I56" s="191"/>
-      <c r="J56" s="191"/>
-      <c r="K56" s="192"/>
+      <c r="F56" s="182"/>
+      <c r="G56" s="182"/>
+      <c r="H56" s="182"/>
+      <c r="I56" s="182"/>
+      <c r="J56" s="182"/>
+      <c r="K56" s="180"/>
       <c r="L56" s="151"/>
       <c r="M56" s="152"/>
     </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="193" t="s">
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="191"/>
-      <c r="G57" s="191"/>
-      <c r="H57" s="191"/>
-      <c r="I57" s="191"/>
-      <c r="J57" s="191"/>
-      <c r="K57" s="192"/>
+      <c r="F57" s="182"/>
+      <c r="G57" s="182"/>
+      <c r="H57" s="182"/>
+      <c r="I57" s="182"/>
+      <c r="J57" s="182"/>
+      <c r="K57" s="180"/>
       <c r="L57" s="153"/>
       <c r="M57" s="154"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E58" s="151"/>
       <c r="F58" s="155"/>
       <c r="G58" s="155"/>
@@ -7174,7 +7171,7 @@
       <c r="L58" s="153"/>
       <c r="M58" s="154"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
@@ -7187,7 +7184,7 @@
       <c r="L59" s="153"/>
       <c r="M59" s="154"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E60" s="157"/>
       <c r="F60" s="158"/>
       <c r="G60" s="158"/>
@@ -7198,20 +7195,20 @@
       <c r="L60" s="153"/>
       <c r="M60" s="154"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="194" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="195"/>
-      <c r="G61" s="195"/>
-      <c r="H61" s="195"/>
-      <c r="I61" s="195"/>
-      <c r="J61" s="195"/>
-      <c r="K61" s="196"/>
+      <c r="F61" s="185"/>
+      <c r="G61" s="185"/>
+      <c r="H61" s="185"/>
+      <c r="I61" s="185"/>
+      <c r="J61" s="185"/>
+      <c r="K61" s="186"/>
       <c r="L61" s="153"/>
       <c r="M61" s="154"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E62" s="153"/>
       <c r="F62" s="156"/>
       <c r="G62" s="156"/>
@@ -7222,7 +7219,7 @@
       <c r="L62" s="153"/>
       <c r="M62" s="154"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
@@ -7239,12 +7236,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="154"/>
-      <c r="L63" s="179" t="s">
+      <c r="L63" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="180"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="188"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
@@ -7259,7 +7256,7 @@
       <c r="L64" s="153"/>
       <c r="M64" s="154"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E65" s="153"/>
       <c r="F65" s="156"/>
       <c r="G65" s="156"/>
@@ -7267,10 +7264,10 @@
       <c r="I65" s="156"/>
       <c r="J65" s="156"/>
       <c r="K65" s="154"/>
-      <c r="L65" s="181"/>
-      <c r="M65" s="180"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="189"/>
+      <c r="M65" s="188"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
@@ -7286,7 +7283,7 @@
       <c r="L66" s="153"/>
       <c r="M66" s="154"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
@@ -7302,7 +7299,7 @@
       <c r="L67" s="153"/>
       <c r="M67" s="154"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
@@ -7318,7 +7315,7 @@
       <c r="L68" s="153"/>
       <c r="M68" s="154"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E69" s="163"/>
       <c r="F69" s="156"/>
       <c r="G69" s="156"/>
@@ -7329,7 +7326,7 @@
       <c r="L69" s="153"/>
       <c r="M69" s="154"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E70" s="163"/>
       <c r="F70" s="156"/>
       <c r="G70" s="156"/>
@@ -7340,7 +7337,7 @@
       <c r="L70" s="153"/>
       <c r="M70" s="154"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="F71" s="156"/>
       <c r="G71" s="156"/>
       <c r="H71" s="156"/>
@@ -7350,7 +7347,7 @@
       <c r="L71" s="153"/>
       <c r="M71" s="154"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E72" s="163"/>
       <c r="F72" s="156"/>
       <c r="G72" s="156"/>
@@ -7361,7 +7358,7 @@
       <c r="L72" s="153"/>
       <c r="M72" s="154"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E73" s="153"/>
       <c r="F73" s="156"/>
       <c r="G73" s="156"/>
@@ -7372,7 +7369,7 @@
       <c r="L73" s="153"/>
       <c r="M73" s="154"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E74" s="153"/>
       <c r="F74" s="156"/>
       <c r="G74" s="156"/>
@@ -7383,7 +7380,7 @@
       <c r="L74" s="153"/>
       <c r="M74" s="154"/>
     </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="153"/>
       <c r="F75" s="156"/>
       <c r="G75" s="156"/>
@@ -7394,50 +7391,50 @@
       <c r="L75" s="164"/>
       <c r="M75" s="165"/>
     </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="197" t="s">
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="198"/>
-      <c r="G76" s="198"/>
-      <c r="H76" s="198"/>
-      <c r="I76" s="198"/>
-      <c r="J76" s="199">
+      <c r="F76" s="178"/>
+      <c r="G76" s="178"/>
+      <c r="H76" s="178"/>
+      <c r="I76" s="178"/>
+      <c r="J76" s="179">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="192"/>
+      <c r="K76" s="180"/>
       <c r="L76" s="166"/>
       <c r="M76" s="167"/>
     </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="190" t="s">
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="191"/>
-      <c r="G83" s="191"/>
-      <c r="H83" s="191"/>
-      <c r="I83" s="191"/>
-      <c r="J83" s="191"/>
-      <c r="K83" s="192"/>
+      <c r="F83" s="182"/>
+      <c r="G83" s="182"/>
+      <c r="H83" s="182"/>
+      <c r="I83" s="182"/>
+      <c r="J83" s="182"/>
+      <c r="K83" s="180"/>
       <c r="L83" s="151"/>
       <c r="M83" s="152"/>
     </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="193" t="s">
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="191"/>
-      <c r="G84" s="191"/>
-      <c r="H84" s="191"/>
-      <c r="I84" s="191"/>
-      <c r="J84" s="191"/>
-      <c r="K84" s="192"/>
+      <c r="F84" s="182"/>
+      <c r="G84" s="182"/>
+      <c r="H84" s="182"/>
+      <c r="I84" s="182"/>
+      <c r="J84" s="182"/>
+      <c r="K84" s="180"/>
       <c r="L84" s="153"/>
       <c r="M84" s="154"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E85" s="151"/>
       <c r="F85" s="155"/>
       <c r="G85" s="155"/>
@@ -7451,7 +7448,7 @@
       <c r="L85" s="153"/>
       <c r="M85" s="154"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
@@ -7464,7 +7461,7 @@
       <c r="L86" s="153"/>
       <c r="M86" s="154"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E87" s="157"/>
       <c r="F87" s="158"/>
       <c r="G87" s="158"/>
@@ -7475,20 +7472,20 @@
       <c r="L87" s="153"/>
       <c r="M87" s="154"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="194" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="195"/>
-      <c r="G88" s="195"/>
-      <c r="H88" s="195"/>
-      <c r="I88" s="195"/>
-      <c r="J88" s="195"/>
-      <c r="K88" s="196"/>
+      <c r="F88" s="185"/>
+      <c r="G88" s="185"/>
+      <c r="H88" s="185"/>
+      <c r="I88" s="185"/>
+      <c r="J88" s="185"/>
+      <c r="K88" s="186"/>
       <c r="L88" s="153"/>
       <c r="M88" s="154"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E89" s="153"/>
       <c r="F89" s="156"/>
       <c r="G89" s="156"/>
@@ -7499,7 +7496,7 @@
       <c r="L89" s="153"/>
       <c r="M89" s="154"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
@@ -7516,12 +7513,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="154"/>
-      <c r="L90" s="179" t="s">
+      <c r="L90" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="180"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M90" s="188"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
@@ -7536,7 +7533,7 @@
       <c r="L91" s="153"/>
       <c r="M91" s="154"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E92" s="153"/>
       <c r="F92" s="156"/>
       <c r="G92" s="156"/>
@@ -7544,10 +7541,10 @@
       <c r="I92" s="156"/>
       <c r="J92" s="156"/>
       <c r="K92" s="154"/>
-      <c r="L92" s="181"/>
-      <c r="M92" s="180"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="189"/>
+      <c r="M92" s="188"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
@@ -7563,7 +7560,7 @@
       <c r="L93" s="153"/>
       <c r="M93" s="154"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
@@ -7579,7 +7576,7 @@
       <c r="L94" s="153"/>
       <c r="M94" s="154"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
@@ -7594,7 +7591,7 @@
       <c r="L95" s="153"/>
       <c r="M95" s="154"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E96" s="163"/>
       <c r="F96" s="156"/>
       <c r="G96" s="156"/>
@@ -7605,7 +7602,7 @@
       <c r="L96" s="153"/>
       <c r="M96" s="154"/>
     </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="163"/>
       <c r="F97" s="156"/>
       <c r="G97" s="156"/>
@@ -7616,7 +7613,7 @@
       <c r="L97" s="153"/>
       <c r="M97" s="154"/>
     </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F98" s="156"/>
       <c r="G98" s="156"/>
       <c r="H98" s="156"/>
@@ -7626,7 +7623,7 @@
       <c r="L98" s="153"/>
       <c r="M98" s="154"/>
     </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="163"/>
       <c r="F99" s="156"/>
       <c r="G99" s="156"/>
@@ -7637,7 +7634,7 @@
       <c r="L99" s="153"/>
       <c r="M99" s="154"/>
     </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E100" s="153"/>
       <c r="F100" s="156"/>
       <c r="G100" s="156"/>
@@ -7648,7 +7645,7 @@
       <c r="L100" s="153"/>
       <c r="M100" s="154"/>
     </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E101" s="153"/>
       <c r="F101" s="156"/>
       <c r="G101" s="156"/>
@@ -7659,7 +7656,7 @@
       <c r="L101" s="153"/>
       <c r="M101" s="154"/>
     </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E102" s="153"/>
       <c r="F102" s="156"/>
       <c r="G102" s="156"/>
@@ -7670,50 +7667,50 @@
       <c r="L102" s="164"/>
       <c r="M102" s="165"/>
     </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="197" t="s">
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="198"/>
-      <c r="G103" s="198"/>
-      <c r="H103" s="198"/>
-      <c r="I103" s="198"/>
-      <c r="J103" s="199">
+      <c r="F103" s="178"/>
+      <c r="G103" s="178"/>
+      <c r="H103" s="178"/>
+      <c r="I103" s="178"/>
+      <c r="J103" s="179">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="192"/>
+      <c r="K103" s="180"/>
       <c r="L103" s="166"/>
       <c r="M103" s="167"/>
     </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="190" t="s">
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="191"/>
-      <c r="G108" s="191"/>
-      <c r="H108" s="191"/>
-      <c r="I108" s="191"/>
-      <c r="J108" s="191"/>
-      <c r="K108" s="192"/>
+      <c r="F108" s="182"/>
+      <c r="G108" s="182"/>
+      <c r="H108" s="182"/>
+      <c r="I108" s="182"/>
+      <c r="J108" s="182"/>
+      <c r="K108" s="180"/>
       <c r="L108" s="151"/>
       <c r="M108" s="152"/>
     </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="193" t="s">
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="191"/>
-      <c r="G109" s="191"/>
-      <c r="H109" s="191"/>
-      <c r="I109" s="191"/>
-      <c r="J109" s="191"/>
-      <c r="K109" s="192"/>
+      <c r="F109" s="182"/>
+      <c r="G109" s="182"/>
+      <c r="H109" s="182"/>
+      <c r="I109" s="182"/>
+      <c r="J109" s="182"/>
+      <c r="K109" s="180"/>
       <c r="L109" s="153"/>
       <c r="M109" s="154"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E110" s="151"/>
       <c r="F110" s="155"/>
       <c r="G110" s="155"/>
@@ -7727,7 +7724,7 @@
       <c r="L110" s="153"/>
       <c r="M110" s="154"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
@@ -7740,7 +7737,7 @@
       <c r="L111" s="153"/>
       <c r="M111" s="154"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E112" s="157"/>
       <c r="F112" s="158"/>
       <c r="G112" s="158"/>
@@ -7751,20 +7748,20 @@
       <c r="L112" s="153"/>
       <c r="M112" s="154"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="194" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="195"/>
-      <c r="G113" s="195"/>
-      <c r="H113" s="195"/>
-      <c r="I113" s="195"/>
-      <c r="J113" s="195"/>
-      <c r="K113" s="196"/>
+      <c r="F113" s="185"/>
+      <c r="G113" s="185"/>
+      <c r="H113" s="185"/>
+      <c r="I113" s="185"/>
+      <c r="J113" s="185"/>
+      <c r="K113" s="186"/>
       <c r="L113" s="153"/>
       <c r="M113" s="154"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E114" s="153"/>
       <c r="F114" s="156"/>
       <c r="G114" s="156"/>
@@ -7775,7 +7772,7 @@
       <c r="L114" s="153"/>
       <c r="M114" s="154"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
@@ -7792,12 +7789,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="154"/>
-      <c r="L115" s="179" t="s">
+      <c r="L115" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="180"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="188"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
@@ -7812,7 +7809,7 @@
       <c r="L116" s="153"/>
       <c r="M116" s="154"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E117" s="153"/>
       <c r="F117" s="156"/>
       <c r="G117" s="156"/>
@@ -7820,10 +7817,10 @@
       <c r="I117" s="156"/>
       <c r="J117" s="156"/>
       <c r="K117" s="154"/>
-      <c r="L117" s="181"/>
-      <c r="M117" s="180"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="189"/>
+      <c r="M117" s="188"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
@@ -7839,7 +7836,7 @@
       <c r="L118" s="153"/>
       <c r="M118" s="154"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
@@ -7855,7 +7852,7 @@
       <c r="L119" s="153"/>
       <c r="M119" s="154"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
@@ -7871,7 +7868,7 @@
       <c r="L120" s="153"/>
       <c r="M120" s="154"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E121" s="163"/>
       <c r="F121" s="156"/>
       <c r="G121" s="156"/>
@@ -7882,7 +7879,7 @@
       <c r="L121" s="153"/>
       <c r="M121" s="154"/>
     </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E122" s="163"/>
       <c r="F122" s="156"/>
       <c r="G122" s="156"/>
@@ -7893,7 +7890,7 @@
       <c r="L122" s="153"/>
       <c r="M122" s="154"/>
     </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F123" s="156"/>
       <c r="G123" s="156"/>
       <c r="H123" s="156"/>
@@ -7903,7 +7900,7 @@
       <c r="L123" s="153"/>
       <c r="M123" s="154"/>
     </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E124" s="163"/>
       <c r="F124" s="156"/>
       <c r="G124" s="156"/>
@@ -7914,7 +7911,7 @@
       <c r="L124" s="153"/>
       <c r="M124" s="154"/>
     </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E125" s="153"/>
       <c r="F125" s="156"/>
       <c r="G125" s="156"/>
@@ -7925,7 +7922,7 @@
       <c r="L125" s="153"/>
       <c r="M125" s="154"/>
     </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E126" s="153"/>
       <c r="F126" s="156"/>
       <c r="G126" s="156"/>
@@ -7936,7 +7933,7 @@
       <c r="L126" s="153"/>
       <c r="M126" s="154"/>
     </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E127" s="153"/>
       <c r="F127" s="156"/>
       <c r="G127" s="156"/>
@@ -7947,58 +7944,24 @@
       <c r="L127" s="164"/>
       <c r="M127" s="165"/>
     </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="197" t="s">
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="177" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="198"/>
-      <c r="I128" s="198"/>
-      <c r="J128" s="199">
+      <c r="F128" s="178"/>
+      <c r="G128" s="178"/>
+      <c r="H128" s="178"/>
+      <c r="I128" s="178"/>
+      <c r="J128" s="179">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="192"/>
+      <c r="K128" s="180"/>
       <c r="L128" s="166"/>
       <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -8015,6 +7978,40 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
